--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880D011E-E76C-46B3-A412-BEB0B354738A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2B6F8C-105B-45F4-B9AD-6EF24A0497C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -619,10 +619,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2770,6 +2776,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="236">
   <si>
     <t>ID</t>
   </si>
@@ -353,6 +353,78 @@
     <t>同接+20，以后，每当打出A卡时，同接+10,</t>
   </si>
   <si>
+    <t>爆米</t>
+  </si>
+  <si>
+    <t>获得同接数20%的流水</t>
+  </si>
+  <si>
+    <t>爆！</t>
+  </si>
+  <si>
+    <t>参数+42</t>
+  </si>
+  <si>
+    <t>深呼吸</t>
+  </si>
+  <si>
+    <t>有好调的状态下，专注+1，好调+3</t>
+  </si>
+  <si>
+    <t>欢呼</t>
+  </si>
+  <si>
+    <t>参数+18</t>
+  </si>
+  <si>
+    <t>发呆</t>
+  </si>
+  <si>
+    <t>专注+6，神采+3</t>
+  </si>
+  <si>
+    <t>打CALL</t>
+  </si>
+  <si>
+    <t>好调+3，神采+6</t>
+  </si>
+  <si>
+    <t>观察</t>
+  </si>
+  <si>
+    <t>专注+3，神采+6</t>
+  </si>
+  <si>
+    <t>首页推送</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+4回合，神采+3</t>
+  </si>
+  <si>
+    <t>预知梦</t>
+  </si>
+  <si>
+    <t>体力消耗减少1点，神采+5</t>
+  </si>
+  <si>
+    <t>距离感</t>
+  </si>
+  <si>
+    <t>专注+4，体力回复4</t>
+  </si>
+  <si>
+    <t>亲切</t>
+  </si>
+  <si>
+    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
+  </si>
+  <si>
+    <t>最初的神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -569,6 +641,27 @@
     <t>每当使用A卡时，同接+10</t>
   </si>
   <si>
+    <t>获得同接数X%的流水</t>
+  </si>
+  <si>
+    <t>有好调时，专注+X</t>
+  </si>
+  <si>
+    <t>体力回复X点</t>
+  </si>
+  <si>
+    <t>BAStamina</t>
+  </si>
+  <si>
+    <t>亲和力大于3层时，亲和力+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，专注+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，专注+1</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -636,6 +729,15 @@
   </si>
   <si>
     <t>使用A卡时</t>
+  </si>
+  <si>
+    <t>当好调大于3层时</t>
+  </si>
+  <si>
+    <t>当专注大于4层时</t>
+  </si>
+  <si>
+    <t>当亲和力大于3层时</t>
   </si>
 </sst>
 </file>
@@ -1602,11 +1704,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="8.70833333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="44.2833333333333" customWidth="1"/>
     <col min="4" max="4" width="10.425" customWidth="1"/>
     <col min="5" max="5" width="13.425" customWidth="1"/>
@@ -3516,6 +3618,573 @@
       </c>
       <c r="AB37" s="6"/>
     </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="3">
+        <v>7</v>
+      </c>
+      <c r="I38" s="4">
+        <v>6</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="3">
+        <v>8</v>
+      </c>
+      <c r="I39" s="4">
+        <v>7</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" s="3">
+        <v>11</v>
+      </c>
+      <c r="M39">
+        <v>42</v>
+      </c>
+      <c r="N39" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="3">
+        <v>3</v>
+      </c>
+      <c r="I40" s="4">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3">
+        <v>37</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40" s="4">
+        <v>2</v>
+      </c>
+      <c r="O40" s="3">
+        <v>15</v>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="3">
+        <v>3</v>
+      </c>
+      <c r="I41" s="4">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>11</v>
+      </c>
+      <c r="M41">
+        <v>18</v>
+      </c>
+      <c r="N41" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2</v>
+      </c>
+      <c r="I42" s="4">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>7</v>
+      </c>
+      <c r="M42">
+        <v>6</v>
+      </c>
+      <c r="N42" s="4">
+        <v>8</v>
+      </c>
+      <c r="O42" s="3">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" s="3">
+        <v>3</v>
+      </c>
+      <c r="I43" s="4">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>15</v>
+      </c>
+      <c r="M43">
+        <v>3</v>
+      </c>
+      <c r="N43" s="4">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
+        <v>2</v>
+      </c>
+      <c r="P43">
+        <v>6</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" s="3">
+        <v>3</v>
+      </c>
+      <c r="I44" s="4">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>7</v>
+      </c>
+      <c r="M44">
+        <v>3</v>
+      </c>
+      <c r="N44" s="4">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
+        <v>2</v>
+      </c>
+      <c r="P44">
+        <v>6</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" s="3">
+        <v>21</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45" s="4">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2</v>
+      </c>
+      <c r="P45">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" s="3">
+        <v>5</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46" s="4">
+        <v>2</v>
+      </c>
+      <c r="O46" s="3">
+        <v>2</v>
+      </c>
+      <c r="P46">
+        <v>6</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4</v>
+      </c>
+      <c r="I47" s="4">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47" s="3">
+        <v>7</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47" s="4">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
+        <v>38</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3">
+        <v>6</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="N48" s="4">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
+        <v>39</v>
+      </c>
+      <c r="P48">
+        <v>2</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" s="3">
+        <v>4</v>
+      </c>
+      <c r="I49" s="4">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49" s="3">
+        <v>7</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49" s="4">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3">
+        <v>41</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -3526,7 +4195,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -3554,19 +4223,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="H1" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I1" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3574,13 +4243,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -3592,19 +4261,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -3615,16 +4284,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -3635,16 +4304,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -3655,13 +4324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -3672,16 +4341,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3692,13 +4361,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3712,13 +4381,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3732,13 +4401,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3752,13 +4421,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -3769,16 +4438,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -3789,16 +4458,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
         <v>140</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>141</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>117</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -3809,19 +4478,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
         <v>142</v>
-      </c>
-      <c r="C14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>118</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -3832,16 +4501,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -3852,16 +4521,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -3872,13 +4541,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -3892,16 +4561,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -3912,13 +4581,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -3932,13 +4601,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3952,16 +4621,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -3972,16 +4641,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -3992,13 +4661,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -4012,19 +4681,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -4035,13 +4704,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -4055,16 +4724,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4078,16 +4747,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -4098,13 +4767,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -4118,19 +4787,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4144,13 +4813,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -4164,19 +4833,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -4187,19 +4856,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -4210,19 +4879,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -4233,16 +4902,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -4253,16 +4922,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -4273,19 +4942,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -4299,18 +4968,150 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E37">
         <v>11</v>
       </c>
       <c r="I37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" t="s">
+        <v>197</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="I40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" t="s">
+        <v>156</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>189</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43">
+        <v>12</v>
+      </c>
+      <c r="I43">
         <v>-1</v>
       </c>
     </row>
@@ -4324,7 +5125,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -4347,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D1" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -4379,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4408,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -4431,10 +5232,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4454,10 +5255,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4477,10 +5278,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4500,10 +5301,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4523,10 +5324,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4546,10 +5347,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -4569,10 +5370,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4592,10 +5393,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4621,10 +5422,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4650,10 +5451,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4666,6 +5467,29 @@
       </c>
       <c r="G13">
         <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4678,8 +5502,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
     <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
@@ -4701,16 +5525,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="F1" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="G1" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4718,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4738,13 +5562,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="D3" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
@@ -4755,16 +5579,76 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="243">
   <si>
     <t>ID</t>
   </si>
@@ -425,6 +425,18 @@
     <t>专注+1，以后每当打出A卡时，专注+1</t>
   </si>
   <si>
+    <t>迷人</t>
+  </si>
+  <si>
+    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
+  </si>
+  <si>
+    <t>前方的闪耀</t>
+  </si>
+  <si>
+    <t>好调+2，之后4回合内，回合结束时，参数+4</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -662,6 +674,12 @@
     <t>每当使用A卡时，专注+1</t>
   </si>
   <si>
+    <t>之后X回合内，回合结束时，参数+X</t>
+  </si>
+  <si>
+    <t>获得X回合，回合结束时，参数+4</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -699,6 +717,9 @@
   </si>
   <si>
     <t>体力消耗增加50%</t>
+  </si>
+  <si>
+    <t>回合结束时，参数+4</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1704,7 +1725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4185,6 +4206,115 @@
         <v>1</v>
       </c>
     </row>
+    <row r="50" spans="1:20">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="3">
+        <v>7</v>
+      </c>
+      <c r="I50" s="4">
+        <v>4</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3">
+        <v>6</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+      <c r="N50" s="4">
+        <v>5</v>
+      </c>
+      <c r="O50" s="3">
+        <v>14</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3">
+        <v>18</v>
+      </c>
+      <c r="S50">
+        <v>0.9</v>
+      </c>
+      <c r="T50" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" s="3">
+        <v>6</v>
+      </c>
+      <c r="I51" s="4">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" s="3">
+        <v>15</v>
+      </c>
+      <c r="M51">
+        <v>2</v>
+      </c>
+      <c r="N51" s="4">
+        <v>2</v>
+      </c>
+      <c r="O51" s="3">
+        <v>42</v>
+      </c>
+      <c r="P51">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -4195,7 +4325,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4223,19 +4353,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4243,13 +4373,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4261,19 +4391,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4284,16 +4414,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
         <v>144</v>
       </c>
-      <c r="D4" t="s">
-        <v>140</v>
-      </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4304,16 +4434,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4324,13 +4454,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4341,16 +4471,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4361,13 +4491,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4381,13 +4511,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4401,13 +4531,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4421,13 +4551,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -4438,16 +4568,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -4458,16 +4588,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -4478,19 +4608,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -4501,16 +4631,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -4521,16 +4651,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -4541,13 +4671,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4561,16 +4691,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -4581,13 +4711,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -4601,13 +4731,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4621,16 +4751,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -4641,16 +4771,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -4661,13 +4791,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -4681,19 +4811,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -4704,13 +4834,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -4724,16 +4854,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4747,16 +4877,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -4767,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -4787,19 +4917,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4813,13 +4943,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -4833,19 +4963,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -4856,19 +4986,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C32" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -4879,19 +5009,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -4902,16 +5032,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E34" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -4922,16 +5052,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -4942,19 +5072,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -4968,13 +5098,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -4988,16 +5118,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E38" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5008,13 +5138,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5031,16 +5161,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5051,13 +5181,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C41" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D41" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5074,19 +5204,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D42" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5100,18 +5230,61 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E43">
         <v>12</v>
       </c>
       <c r="I43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>214</v>
+      </c>
+      <c r="C44" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44">
+        <v>13</v>
+      </c>
+      <c r="I44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:9">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+      <c r="I45">
         <v>-1</v>
       </c>
     </row>
@@ -5125,7 +5298,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -5148,13 +5321,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -5180,10 +5353,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5209,10 +5382,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -5232,10 +5405,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5255,10 +5428,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5278,10 +5451,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5301,10 +5474,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -5324,10 +5497,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5347,10 +5520,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -5370,10 +5543,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -5393,10 +5566,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -5422,10 +5595,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -5451,10 +5624,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -5474,10 +5647,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -5490,6 +5663,29 @@
       </c>
       <c r="G14">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>43</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5525,16 +5721,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5542,13 +5738,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5562,13 +5758,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
@@ -5579,13 +5775,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F4" t="s">
         <v>31</v>
@@ -5596,13 +5792,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5616,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5636,13 +5832,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" t="s">
         <v>235</v>
       </c>
-      <c r="C7" t="s">
-        <v>228</v>
-      </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
-    <sheet name="Effects" sheetId="2" r:id="rId2"/>
-    <sheet name="Buffs" sheetId="3" r:id="rId3"/>
+    <sheet name="Effect" sheetId="2" r:id="rId2"/>
+    <sheet name="Buff" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="259">
   <si>
     <t>ID</t>
   </si>
@@ -398,7 +398,7 @@
     <t>首页推送</t>
   </si>
   <si>
-    <t>体力消耗增加50%+4回合，神采+3</t>
+    <t>体力消耗减少50%+4回合，神采+3</t>
   </si>
   <si>
     <t>预知梦</t>
@@ -437,6 +437,36 @@
     <t>好调+2，之后4回合内，回合结束时，参数+4</t>
   </si>
   <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>专注+7，体力消耗增加+2回合，神采+7</t>
+  </si>
+  <si>
+    <t>哭唧唧</t>
+  </si>
+  <si>
+    <t>流水+40，同接+30，舰长+1</t>
+  </si>
+  <si>
+    <t>大航海</t>
+  </si>
+  <si>
+    <t>参数+5两次，舰长+1</t>
+  </si>
+  <si>
+    <t>晚上好</t>
+  </si>
+  <si>
+    <t>亲和力+3，坚毅+2</t>
+  </si>
+  <si>
+    <t>真情流露</t>
+  </si>
+  <si>
+    <t>坚毅+2，神采+2，之后的三回合内，回合结束时，亲和力变成1.1倍，</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -680,6 +710,21 @@
     <t>获得X回合，回合结束时，参数+4</t>
   </si>
   <si>
+    <t>神采获得量增加X</t>
+  </si>
+  <si>
+    <t>坚毅+X</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力变为X倍</t>
+  </si>
+  <si>
+    <t>VBuffAddPercentageEffect</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力变为1.1倍</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -720,6 +765,9 @@
   </si>
   <si>
     <t>回合结束时，参数+4</t>
+  </si>
+  <si>
+    <t>坚毅</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1396,11 +1444,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1725,7 +1774,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -1735,23 +1784,23 @@
     <col min="5" max="5" width="13.425" customWidth="1"/>
     <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
     <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7.14166666666667" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14" style="5" customWidth="1"/>
     <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
     <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" style="4" customWidth="1"/>
     <col min="13" max="13" width="12.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.7083333333333" style="4" customWidth="1"/>
-    <col min="15" max="15" width="11" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="15" max="15" width="11" style="4" customWidth="1"/>
     <col min="16" max="16" width="12.2833333333333" customWidth="1"/>
-    <col min="17" max="17" width="17.1416666666667" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9" style="3"/>
-    <col min="20" max="20" width="17.7083333333333" style="4" customWidth="1"/>
-    <col min="21" max="21" width="10.7083333333333" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.1416666666667" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9" style="4"/>
+    <col min="20" max="20" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="21" max="21" width="10.7083333333333" style="4" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="17.7083333333333" style="4" customWidth="1"/>
-    <col min="24" max="24" width="12.425" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12.425" style="4" customWidth="1"/>
+    <col min="23" max="23" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="24" max="24" width="12.425" style="4" customWidth="1"/>
+    <col min="25" max="25" width="12.425" style="5" customWidth="1"/>
     <col min="26" max="26" width="12.2833333333333" customWidth="1"/>
     <col min="28" max="28" width="4.28333333333333" customWidth="1"/>
   </cols>
@@ -1778,10 +1827,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1790,46 +1839,46 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
@@ -1861,10 +1910,10 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>4</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="5">
         <v>3</v>
       </c>
       <c r="J2">
@@ -1873,16 +1922,16 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="4">
         <v>11</v>
       </c>
       <c r="M2">
         <v>7</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="5">
         <v>7</v>
       </c>
-      <c r="AB2" s="5"/>
+      <c r="AB2" s="6"/>
     </row>
     <row r="3" spans="1:28">
       <c r="A3">
@@ -1903,10 +1952,10 @@
       <c r="F3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3">
@@ -1915,16 +1964,16 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="4">
         <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="5">
         <v>4</v>
       </c>
-      <c r="AB3" s="5"/>
+      <c r="AB3" s="6"/>
     </row>
     <row r="4" spans="1:28">
       <c r="A4">
@@ -1945,10 +1994,10 @@
       <c r="F4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>5</v>
       </c>
       <c r="J4">
@@ -1957,16 +2006,16 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="4">
         <v>11</v>
       </c>
       <c r="M4">
         <v>15</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="5">
         <v>15</v>
       </c>
-      <c r="AB4" s="5"/>
+      <c r="AB4" s="6"/>
     </row>
     <row r="5" spans="1:28">
       <c r="A5">
@@ -1987,10 +2036,10 @@
       <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>3</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <v>3</v>
       </c>
       <c r="J5">
@@ -1999,25 +2048,25 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <v>11</v>
       </c>
       <c r="M5">
         <v>5</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="5">
         <v>5</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <v>2</v>
       </c>
       <c r="P5">
         <v>2</v>
       </c>
-      <c r="Q5" s="4">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="5"/>
+      <c r="Q5" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="6"/>
     </row>
     <row r="6" spans="1:28">
       <c r="A6">
@@ -2041,10 +2090,10 @@
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2053,10 +2102,10 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="5"/>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="6"/>
     </row>
     <row r="7" spans="1:28">
       <c r="A7">
@@ -2077,10 +2126,10 @@
       <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>5</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <v>5</v>
       </c>
       <c r="J7">
@@ -2089,10 +2138,10 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="4">
         <v>4</v>
       </c>
-      <c r="AB7" s="5"/>
+      <c r="AB7" s="6"/>
     </row>
     <row r="8" spans="1:28">
       <c r="A8">
@@ -2116,10 +2165,10 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2128,34 +2177,34 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="4">
         <v>2</v>
       </c>
       <c r="M8">
         <v>7</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="5">
         <v>7</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="4">
         <v>3</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4">
         <v>14</v>
       </c>
       <c r="S8">
         <v>1</v>
       </c>
-      <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="5"/>
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="6"/>
     </row>
     <row r="9" spans="1:28">
       <c r="A9">
@@ -2176,10 +2225,10 @@
       <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
         <v>0</v>
       </c>
       <c r="J9">
@@ -2188,25 +2237,25 @@
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="4">
         <v>17</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4">
         <v>2</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="5">
         <v>6</v>
       </c>
-      <c r="AB9" s="5"/>
+      <c r="AB9" s="6"/>
     </row>
     <row r="10" spans="1:28">
       <c r="A10">
@@ -2227,10 +2276,10 @@
       <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="H10" s="4">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2239,25 +2288,25 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="4">
         <v>6</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="5">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="4">
         <v>2</v>
       </c>
       <c r="P10">
         <v>3</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="Q10" s="5">
         <v>4</v>
       </c>
-      <c r="AB10" s="5"/>
+      <c r="AB10" s="6"/>
     </row>
     <row r="11" spans="1:28">
       <c r="A11">
@@ -2278,10 +2327,10 @@
       <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="3">
-        <v>2</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="H11" s="4">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2290,25 +2339,25 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="4">
         <v>7</v>
       </c>
       <c r="M11">
         <v>2</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="5">
         <v>3</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="4">
         <v>2</v>
       </c>
       <c r="P11">
         <v>2</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="Q11" s="5">
         <v>3</v>
       </c>
-      <c r="AB11" s="5"/>
+      <c r="AB11" s="6"/>
     </row>
     <row r="12" spans="1:28">
       <c r="A12">
@@ -2329,10 +2378,10 @@
       <c r="F12" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="3">
-        <v>2</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="H12" s="4">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
         <v>2</v>
       </c>
       <c r="J12">
@@ -2341,25 +2390,25 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="4">
         <v>15</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="5">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="4">
         <v>2</v>
       </c>
       <c r="P12">
         <v>2</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="5">
         <v>3</v>
       </c>
-      <c r="AB12" s="5"/>
+      <c r="AB12" s="6"/>
     </row>
     <row r="13" spans="1:29">
       <c r="A13">
@@ -2380,10 +2429,10 @@
       <c r="F13" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <v>6</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="5">
         <v>6</v>
       </c>
       <c r="J13">
@@ -2392,25 +2441,25 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="4">
         <v>11</v>
       </c>
       <c r="M13">
         <v>9</v>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="5">
         <v>13</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="4">
         <v>11</v>
       </c>
       <c r="P13">
         <v>9</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="5">
         <v>13</v>
       </c>
-      <c r="AB13" s="5"/>
+      <c r="AB13" s="6"/>
       <c r="AC13" t="s">
         <v>59</v>
       </c>
@@ -2434,10 +2483,10 @@
       <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <v>5</v>
       </c>
       <c r="J14">
@@ -2446,25 +2495,25 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="4">
         <v>11</v>
       </c>
       <c r="M14">
         <v>11</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="5">
         <v>15</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="4">
         <v>2</v>
       </c>
       <c r="P14">
         <v>7</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="5">
         <v>9</v>
       </c>
-      <c r="AB14" s="5"/>
+      <c r="AB14" s="6"/>
     </row>
     <row r="15" spans="1:28">
       <c r="A15">
@@ -2485,10 +2534,10 @@
       <c r="F15" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="5">
         <v>4</v>
       </c>
       <c r="J15">
@@ -2497,16 +2546,16 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="4">
         <v>6</v>
       </c>
       <c r="M15">
         <v>6</v>
       </c>
-      <c r="N15" s="4">
+      <c r="N15" s="5">
         <v>8</v>
       </c>
-      <c r="AB15" s="5"/>
+      <c r="AB15" s="6"/>
     </row>
     <row r="16" spans="1:28">
       <c r="A16">
@@ -2527,10 +2576,10 @@
       <c r="F16" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>4</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>4</v>
       </c>
       <c r="J16">
@@ -2539,16 +2588,16 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="4">
         <v>18</v>
       </c>
       <c r="M16">
         <v>1.4</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="5">
         <v>1.8</v>
       </c>
-      <c r="AB16" s="5"/>
+      <c r="AB16" s="6"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17">
@@ -2569,10 +2618,10 @@
       <c r="F17" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <v>6</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="5">
         <v>5</v>
       </c>
       <c r="J17">
@@ -2581,25 +2630,25 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="4">
         <v>6</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N17" s="5">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="4">
         <v>18</v>
       </c>
       <c r="P17">
         <v>0.8</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="5">
         <v>1.1</v>
       </c>
-      <c r="AB17" s="5"/>
+      <c r="AB17" s="6"/>
     </row>
     <row r="18" spans="1:28">
       <c r="A18">
@@ -2620,10 +2669,10 @@
       <c r="F18" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <v>3</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <v>3</v>
       </c>
       <c r="J18">
@@ -2632,34 +2681,34 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="4">
         <v>19</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
-      <c r="N18" s="4">
-        <v>1</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="N18" s="5">
+        <v>1</v>
+      </c>
+      <c r="O18" s="4">
         <v>2</v>
       </c>
       <c r="P18">
         <v>4</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="5">
         <v>6</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="4">
         <v>21</v>
       </c>
       <c r="S18">
         <v>2</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="5">
         <v>3</v>
       </c>
-      <c r="AB18" s="6"/>
+      <c r="AB18" s="7"/>
     </row>
     <row r="19" spans="1:28">
       <c r="A19">
@@ -2680,10 +2729,10 @@
       <c r="F19" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <v>6</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="5">
         <v>5</v>
       </c>
       <c r="J19">
@@ -2692,10 +2741,10 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="5"/>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="6"/>
     </row>
     <row r="20" spans="1:28">
       <c r="A20">
@@ -2716,10 +2765,10 @@
       <c r="F20" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <v>4</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="5">
         <v>3</v>
       </c>
       <c r="J20">
@@ -2728,16 +2777,16 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="4">
         <v>15</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="5">
         <v>7</v>
       </c>
-      <c r="AB20" s="5"/>
+      <c r="AB20" s="6"/>
     </row>
     <row r="21" spans="1:28">
       <c r="A21">
@@ -2758,10 +2807,10 @@
       <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <v>5</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="5">
         <v>4</v>
       </c>
       <c r="J21">
@@ -2770,25 +2819,25 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="4">
         <v>23</v>
       </c>
       <c r="M21">
         <v>1</v>
       </c>
-      <c r="N21" s="4">
-        <v>1</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="N21" s="5">
+        <v>1</v>
+      </c>
+      <c r="O21" s="4">
         <v>7</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
-      <c r="Q21" s="4">
-        <v>2</v>
-      </c>
-      <c r="AB21" s="5"/>
+      <c r="Q21" s="5">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="6"/>
     </row>
     <row r="22" spans="1:28">
       <c r="A22">
@@ -2809,10 +2858,10 @@
       <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="4">
         <v>6</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="5">
         <v>6</v>
       </c>
       <c r="J22">
@@ -2821,16 +2870,16 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="4">
         <v>24</v>
       </c>
       <c r="M22">
         <v>24</v>
       </c>
-      <c r="N22" s="4">
+      <c r="N22" s="5">
         <v>30</v>
       </c>
-      <c r="AB22" s="6"/>
+      <c r="AB22" s="7"/>
     </row>
     <row r="23" spans="1:28">
       <c r="A23">
@@ -2851,10 +2900,10 @@
       <c r="F23" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="4">
         <v>8</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <v>6</v>
       </c>
       <c r="J23">
@@ -2863,34 +2912,34 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="4">
         <v>15</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="5">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="4">
         <v>7</v>
       </c>
       <c r="P23">
         <v>5</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="Q23" s="5">
         <v>6</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="4">
         <v>21</v>
       </c>
       <c r="S23">
         <v>2</v>
       </c>
-      <c r="T23" s="4">
+      <c r="T23" s="5">
         <v>3</v>
       </c>
-      <c r="AB23" s="5"/>
+      <c r="AB23" s="6"/>
     </row>
     <row r="24" spans="1:28">
       <c r="A24">
@@ -2911,10 +2960,10 @@
       <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <v>5</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="5">
         <v>4</v>
       </c>
       <c r="J24">
@@ -2923,34 +2972,34 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="4">
         <v>26</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
-      <c r="N24" s="4">
-        <v>2</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="N24" s="5">
+        <v>2</v>
+      </c>
+      <c r="O24" s="4">
         <v>11</v>
       </c>
       <c r="P24">
         <v>30</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="Q24" s="5">
         <v>42</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="4">
         <v>2</v>
       </c>
       <c r="S24">
         <v>5</v>
       </c>
-      <c r="T24" s="4">
+      <c r="T24" s="5">
         <v>7</v>
       </c>
-      <c r="AB24" s="5"/>
+      <c r="AB24" s="6"/>
     </row>
     <row r="25" spans="1:28">
       <c r="A25">
@@ -2971,10 +3020,10 @@
       <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="4">
         <v>4</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="5">
         <v>4</v>
       </c>
       <c r="J25">
@@ -2983,25 +3032,25 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="4">
         <v>6</v>
       </c>
       <c r="M25">
         <v>2</v>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="5">
         <v>4</v>
       </c>
-      <c r="O25" s="3">
+      <c r="O25" s="4">
         <v>28</v>
       </c>
       <c r="P25">
         <v>1</v>
       </c>
-      <c r="Q25" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="5"/>
+      <c r="Q25" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="6"/>
     </row>
     <row r="26" spans="1:28">
       <c r="A26">
@@ -3022,10 +3071,10 @@
       <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4">
+      <c r="H26" s="4">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5">
         <v>1</v>
       </c>
       <c r="J26">
@@ -3034,25 +3083,25 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="4">
         <v>6</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="5">
         <v>7</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="4">
         <v>2</v>
       </c>
       <c r="P26">
         <v>1</v>
       </c>
-      <c r="Q26" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="5"/>
+      <c r="Q26" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="6"/>
     </row>
     <row r="27" spans="1:28">
       <c r="A27">
@@ -3073,10 +3122,10 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="4">
         <v>4</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="5">
         <v>4</v>
       </c>
       <c r="J27">
@@ -3085,25 +3134,25 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="4">
         <v>15</v>
       </c>
       <c r="M27">
         <v>3</v>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="5">
         <v>4</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="4">
         <v>11</v>
       </c>
       <c r="P27">
         <v>8</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="Q27" s="5">
         <v>11</v>
       </c>
-      <c r="AB27" s="5"/>
+      <c r="AB27" s="6"/>
     </row>
     <row r="28" spans="1:28">
       <c r="A28">
@@ -3124,10 +3173,10 @@
       <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="4">
         <v>3</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="5">
         <v>2</v>
       </c>
       <c r="J28">
@@ -3136,16 +3185,16 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="4">
         <v>7</v>
       </c>
       <c r="M28">
         <v>3</v>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="5">
         <v>5</v>
       </c>
-      <c r="AB28" s="5"/>
+      <c r="AB28" s="6"/>
     </row>
     <row r="29" spans="1:28">
       <c r="A29">
@@ -3166,10 +3215,10 @@
       <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="4">
         <v>3</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="5">
         <v>2</v>
       </c>
       <c r="J29">
@@ -3178,25 +3227,25 @@
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="4">
         <v>7</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
-      <c r="N29" s="4">
+      <c r="N29" s="5">
         <v>4</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="4">
         <v>2</v>
       </c>
       <c r="P29">
         <v>4</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="Q29" s="5">
         <v>6</v>
       </c>
-      <c r="AB29" s="5"/>
+      <c r="AB29" s="6"/>
     </row>
     <row r="30" spans="1:28">
       <c r="A30">
@@ -3220,10 +3269,10 @@
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="4">
         <v>3</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="5">
         <v>2</v>
       </c>
       <c r="J30">
@@ -3232,34 +3281,34 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="4">
         <v>15</v>
       </c>
       <c r="M30">
         <v>3</v>
       </c>
-      <c r="N30" s="4">
+      <c r="N30" s="5">
         <v>4</v>
       </c>
-      <c r="O30" s="3">
+      <c r="O30" s="4">
         <v>11</v>
       </c>
       <c r="P30">
         <v>9</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="Q30" s="5">
         <v>14</v>
       </c>
-      <c r="R30" s="3">
+      <c r="R30" s="4">
         <v>14</v>
       </c>
       <c r="S30">
         <v>1</v>
       </c>
-      <c r="T30" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="5"/>
+      <c r="T30" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="6"/>
     </row>
     <row r="31" spans="1:28">
       <c r="A31">
@@ -3283,10 +3332,10 @@
       <c r="G31">
         <v>3</v>
       </c>
-      <c r="H31" s="3">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4">
+      <c r="H31" s="4">
+        <v>2</v>
+      </c>
+      <c r="I31" s="5">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3295,25 +3344,25 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="L31" s="3">
+      <c r="L31" s="4">
         <v>7</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="5">
         <v>6</v>
       </c>
-      <c r="O31" s="3">
+      <c r="O31" s="4">
         <v>14</v>
       </c>
       <c r="P31">
         <v>1</v>
       </c>
-      <c r="Q31" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="5"/>
+      <c r="Q31" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="6"/>
     </row>
     <row r="32" spans="1:28">
       <c r="A32">
@@ -3334,10 +3383,10 @@
       <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="4">
         <v>10</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="5">
         <v>8</v>
       </c>
       <c r="J32">
@@ -3346,34 +3395,34 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="4">
         <v>15</v>
       </c>
       <c r="M32">
         <v>5</v>
       </c>
-      <c r="N32" s="4">
+      <c r="N32" s="5">
         <v>7</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="4">
         <v>30</v>
       </c>
       <c r="P32">
         <v>1</v>
       </c>
-      <c r="Q32" s="4">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="5">
+        <v>1</v>
+      </c>
+      <c r="R32" s="4">
         <v>31</v>
       </c>
       <c r="S32">
         <v>1</v>
       </c>
-      <c r="T32" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="6"/>
+      <c r="T32" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="7"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33">
@@ -3394,10 +3443,10 @@
       <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" s="4">
+      <c r="H33" s="4">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5">
         <v>0</v>
       </c>
       <c r="J33">
@@ -3406,16 +3455,16 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="4">
         <v>2</v>
       </c>
       <c r="M33">
         <v>6</v>
       </c>
-      <c r="N33" s="4">
+      <c r="N33" s="5">
         <v>8</v>
       </c>
-      <c r="AB33" s="5"/>
+      <c r="AB33" s="6"/>
     </row>
     <row r="34" spans="1:28">
       <c r="A34">
@@ -3436,10 +3485,10 @@
       <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="4">
         <v>6</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="5">
         <v>5</v>
       </c>
       <c r="J34">
@@ -3448,34 +3497,34 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34" s="4">
         <v>19</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
-      <c r="N34" s="4">
-        <v>1</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="N34" s="5">
+        <v>1</v>
+      </c>
+      <c r="O34" s="4">
         <v>11</v>
       </c>
       <c r="P34">
         <v>4</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="5">
         <v>7</v>
       </c>
-      <c r="R34" s="3">
+      <c r="R34" s="4">
         <v>14</v>
       </c>
       <c r="S34">
         <v>1</v>
       </c>
-      <c r="T34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="6"/>
+      <c r="T34" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="7"/>
     </row>
     <row r="35" spans="1:28">
       <c r="A35">
@@ -3496,10 +3545,10 @@
       <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="4">
         <v>5</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="5">
         <v>5</v>
       </c>
       <c r="J35">
@@ -3508,34 +3557,34 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="4">
         <v>32</v>
       </c>
       <c r="M35">
         <v>30</v>
       </c>
-      <c r="N35" s="4">
+      <c r="N35" s="5">
         <v>30</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="4">
         <v>2</v>
       </c>
       <c r="P35">
         <v>3</v>
       </c>
-      <c r="Q35" s="4">
+      <c r="Q35" s="5">
         <v>5</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="4">
         <v>21</v>
       </c>
       <c r="S35">
         <v>2</v>
       </c>
-      <c r="T35" s="4">
+      <c r="T35" s="5">
         <v>3</v>
       </c>
-      <c r="AB35" s="5"/>
+      <c r="AB35" s="6"/>
     </row>
     <row r="36" spans="1:28">
       <c r="A36">
@@ -3556,10 +3605,10 @@
       <c r="F36" t="s">
         <v>32</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="4">
         <v>4</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="5">
         <v>4</v>
       </c>
       <c r="J36">
@@ -3568,25 +3617,25 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="4">
         <v>33</v>
       </c>
       <c r="M36">
         <v>50</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="5">
         <v>70</v>
       </c>
-      <c r="O36" s="3">
+      <c r="O36" s="4">
         <v>2</v>
       </c>
       <c r="P36">
         <v>2</v>
       </c>
-      <c r="Q36" s="4">
+      <c r="Q36" s="5">
         <v>4</v>
       </c>
-      <c r="AB36" s="6"/>
+      <c r="AB36" s="7"/>
     </row>
     <row r="37" spans="1:28">
       <c r="A37">
@@ -3607,10 +3656,10 @@
       <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="4">
         <v>4</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="5">
         <v>3</v>
       </c>
       <c r="J37">
@@ -3619,25 +3668,25 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="4">
         <v>33</v>
       </c>
       <c r="M37">
         <v>20</v>
       </c>
-      <c r="N37" s="4">
+      <c r="N37" s="5">
         <v>30</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O37" s="4">
         <v>35</v>
       </c>
       <c r="P37">
         <v>1</v>
       </c>
-      <c r="Q37" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="6"/>
+      <c r="Q37" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
@@ -3658,10 +3707,10 @@
       <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="4">
         <v>7</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="5">
         <v>6</v>
       </c>
       <c r="J38">
@@ -3690,10 +3739,10 @@
       <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="4">
         <v>8</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="5">
         <v>7</v>
       </c>
       <c r="J39">
@@ -3702,13 +3751,13 @@
       <c r="K39">
         <v>1</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="4">
         <v>11</v>
       </c>
       <c r="M39">
         <v>42</v>
       </c>
-      <c r="N39" s="4">
+      <c r="N39" s="5">
         <v>54</v>
       </c>
     </row>
@@ -3731,10 +3780,10 @@
       <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="4">
         <v>3</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40" s="5">
         <v>3</v>
       </c>
       <c r="J40">
@@ -3743,22 +3792,22 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="3">
+      <c r="L40" s="4">
         <v>37</v>
       </c>
       <c r="M40">
         <v>1</v>
       </c>
-      <c r="N40" s="4">
-        <v>2</v>
-      </c>
-      <c r="O40" s="3">
+      <c r="N40" s="5">
+        <v>2</v>
+      </c>
+      <c r="O40" s="4">
         <v>15</v>
       </c>
       <c r="P40">
         <v>3</v>
       </c>
-      <c r="Q40" s="4">
+      <c r="Q40" s="5">
         <v>4</v>
       </c>
     </row>
@@ -3781,10 +3830,10 @@
       <c r="F41" t="s">
         <v>32</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="4">
         <v>3</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I41" s="5">
         <v>3</v>
       </c>
       <c r="J41">
@@ -3793,13 +3842,13 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="4">
         <v>11</v>
       </c>
       <c r="M41">
         <v>18</v>
       </c>
-      <c r="N41" s="4">
+      <c r="N41" s="5">
         <v>22</v>
       </c>
     </row>
@@ -3825,10 +3874,10 @@
       <c r="G42">
         <v>3</v>
       </c>
-      <c r="H42" s="3">
-        <v>2</v>
-      </c>
-      <c r="I42" s="4">
+      <c r="H42" s="4">
+        <v>2</v>
+      </c>
+      <c r="I42" s="5">
         <v>2</v>
       </c>
       <c r="J42">
@@ -3837,22 +3886,22 @@
       <c r="K42">
         <v>0</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="4">
         <v>7</v>
       </c>
       <c r="M42">
         <v>6</v>
       </c>
-      <c r="N42" s="4">
+      <c r="N42" s="5">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="4">
         <v>2</v>
       </c>
       <c r="P42">
         <v>3</v>
       </c>
-      <c r="Q42" s="4">
+      <c r="Q42" s="5">
         <v>4</v>
       </c>
     </row>
@@ -3875,10 +3924,10 @@
       <c r="F43" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="4">
         <v>3</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="5">
         <v>3</v>
       </c>
       <c r="J43">
@@ -3887,22 +3936,22 @@
       <c r="K43">
         <v>0</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="4">
         <v>15</v>
       </c>
       <c r="M43">
         <v>3</v>
       </c>
-      <c r="N43" s="4">
+      <c r="N43" s="5">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="4">
         <v>2</v>
       </c>
       <c r="P43">
         <v>6</v>
       </c>
-      <c r="Q43" s="4">
+      <c r="Q43" s="5">
         <v>8</v>
       </c>
     </row>
@@ -3925,10 +3974,10 @@
       <c r="F44" t="s">
         <v>32</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="4">
         <v>3</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="5">
         <v>3</v>
       </c>
       <c r="J44">
@@ -3937,22 +3986,22 @@
       <c r="K44">
         <v>0</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="4">
         <v>7</v>
       </c>
       <c r="M44">
         <v>3</v>
       </c>
-      <c r="N44" s="4">
+      <c r="N44" s="5">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="4">
         <v>2</v>
       </c>
       <c r="P44">
         <v>6</v>
       </c>
-      <c r="Q44" s="4">
+      <c r="Q44" s="5">
         <v>8</v>
       </c>
     </row>
@@ -3975,10 +4024,10 @@
       <c r="F45" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="3">
-        <v>1</v>
-      </c>
-      <c r="I45" s="4">
+      <c r="H45" s="4">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5">
         <v>1</v>
       </c>
       <c r="J45">
@@ -3987,22 +4036,22 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="4">
         <v>21</v>
       </c>
       <c r="M45">
         <v>4</v>
       </c>
-      <c r="N45" s="4">
+      <c r="N45" s="5">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="4">
         <v>2</v>
       </c>
       <c r="P45">
         <v>3</v>
       </c>
-      <c r="Q45" s="4">
+      <c r="Q45" s="5">
         <v>5</v>
       </c>
     </row>
@@ -4025,10 +4074,10 @@
       <c r="F46" t="s">
         <v>32</v>
       </c>
-      <c r="H46" s="3">
-        <v>1</v>
-      </c>
-      <c r="I46" s="4">
+      <c r="H46" s="4">
+        <v>1</v>
+      </c>
+      <c r="I46" s="5">
         <v>1</v>
       </c>
       <c r="J46">
@@ -4037,22 +4086,22 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="4">
         <v>5</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
-      <c r="N46" s="4">
-        <v>2</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="N46" s="5">
+        <v>2</v>
+      </c>
+      <c r="O46" s="4">
         <v>2</v>
       </c>
       <c r="P46">
         <v>6</v>
       </c>
-      <c r="Q46" s="4">
+      <c r="Q46" s="5">
         <v>7</v>
       </c>
     </row>
@@ -4075,10 +4124,10 @@
       <c r="F47" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="4">
         <v>4</v>
       </c>
-      <c r="I47" s="4">
+      <c r="I47" s="5">
         <v>3</v>
       </c>
       <c r="J47">
@@ -4087,22 +4136,22 @@
       <c r="K47">
         <v>1</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="4">
         <v>7</v>
       </c>
       <c r="M47">
         <v>4</v>
       </c>
-      <c r="N47" s="4">
+      <c r="N47" s="5">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="4">
         <v>38</v>
       </c>
       <c r="P47">
         <v>4</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="Q47" s="5">
         <v>5</v>
       </c>
     </row>
@@ -4125,10 +4174,10 @@
       <c r="F48" t="s">
         <v>32</v>
       </c>
-      <c r="H48" s="3">
-        <v>2</v>
-      </c>
-      <c r="I48" s="4">
+      <c r="H48" s="4">
+        <v>2</v>
+      </c>
+      <c r="I48" s="5">
         <v>2</v>
       </c>
       <c r="J48">
@@ -4137,22 +4186,22 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="4">
         <v>6</v>
       </c>
       <c r="M48">
         <v>3</v>
       </c>
-      <c r="N48" s="4">
+      <c r="N48" s="5">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="4">
         <v>39</v>
       </c>
       <c r="P48">
         <v>2</v>
       </c>
-      <c r="Q48" s="4">
+      <c r="Q48" s="5">
         <v>3</v>
       </c>
     </row>
@@ -4175,10 +4224,10 @@
       <c r="F49" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="4">
         <v>4</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49" s="5">
         <v>3</v>
       </c>
       <c r="J49">
@@ -4187,22 +4236,22 @@
       <c r="K49">
         <v>1</v>
       </c>
-      <c r="L49" s="3">
+      <c r="L49" s="4">
         <v>7</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
-      <c r="N49" s="4">
+      <c r="N49" s="5">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
+      <c r="O49" s="4">
         <v>41</v>
       </c>
       <c r="P49">
         <v>1</v>
       </c>
-      <c r="Q49" s="4">
+      <c r="Q49" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4225,10 +4274,10 @@
       <c r="F50" t="s">
         <v>32</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="4">
         <v>7</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="5">
         <v>4</v>
       </c>
       <c r="J50">
@@ -4237,31 +4286,31 @@
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="L50" s="3">
+      <c r="L50" s="4">
         <v>6</v>
       </c>
       <c r="M50">
         <v>5</v>
       </c>
-      <c r="N50" s="4">
+      <c r="N50" s="5">
         <v>5</v>
       </c>
-      <c r="O50" s="3">
+      <c r="O50" s="4">
         <v>14</v>
       </c>
       <c r="P50">
         <v>1</v>
       </c>
-      <c r="Q50" s="4">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3">
+      <c r="Q50" s="5">
+        <v>1</v>
+      </c>
+      <c r="R50" s="4">
         <v>18</v>
       </c>
       <c r="S50">
         <v>0.9</v>
       </c>
-      <c r="T50" s="4">
+      <c r="T50" s="5">
         <v>1.2</v>
       </c>
     </row>
@@ -4284,10 +4333,10 @@
       <c r="F51" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="4">
         <v>6</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="5">
         <v>4</v>
       </c>
       <c r="J51">
@@ -4296,23 +4345,312 @@
       <c r="K51">
         <v>1</v>
       </c>
-      <c r="L51" s="3">
+      <c r="L51" s="4">
         <v>15</v>
       </c>
       <c r="M51">
         <v>2</v>
       </c>
-      <c r="N51" s="4">
-        <v>2</v>
-      </c>
-      <c r="O51" s="3">
+      <c r="N51" s="5">
+        <v>2</v>
+      </c>
+      <c r="O51" s="4">
         <v>42</v>
       </c>
       <c r="P51">
         <v>3</v>
       </c>
-      <c r="Q51" s="4">
+      <c r="Q51" s="5">
         <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52" s="4">
+        <v>5</v>
+      </c>
+      <c r="I52" s="5">
+        <v>4</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4">
+        <v>7</v>
+      </c>
+      <c r="M52">
+        <v>7</v>
+      </c>
+      <c r="N52" s="5">
+        <v>9</v>
+      </c>
+      <c r="O52" s="4">
+        <v>26</v>
+      </c>
+      <c r="P52">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>2</v>
+      </c>
+      <c r="R52" s="4">
+        <v>2</v>
+      </c>
+      <c r="S52">
+        <v>7</v>
+      </c>
+      <c r="T52" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" s="4">
+        <v>10</v>
+      </c>
+      <c r="I53" s="5">
+        <v>6</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53" s="4">
+        <v>32</v>
+      </c>
+      <c r="M53">
+        <v>40</v>
+      </c>
+      <c r="N53" s="5">
+        <v>40</v>
+      </c>
+      <c r="O53" s="4">
+        <v>33</v>
+      </c>
+      <c r="P53">
+        <v>30</v>
+      </c>
+      <c r="Q53" s="5">
+        <v>30</v>
+      </c>
+      <c r="R53" s="4">
+        <v>19</v>
+      </c>
+      <c r="S53">
+        <v>1</v>
+      </c>
+      <c r="T53" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54" s="4">
+        <v>1</v>
+      </c>
+      <c r="I54" s="5">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54" s="4">
+        <v>11</v>
+      </c>
+      <c r="M54">
+        <v>5</v>
+      </c>
+      <c r="N54" s="5">
+        <v>5</v>
+      </c>
+      <c r="O54" s="4">
+        <v>11</v>
+      </c>
+      <c r="P54">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>5</v>
+      </c>
+      <c r="R54" s="4">
+        <v>19</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
+      <c r="T54" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" s="4">
+        <v>4</v>
+      </c>
+      <c r="I55" s="5">
+        <v>4</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4">
+        <v>6</v>
+      </c>
+      <c r="M55">
+        <v>3</v>
+      </c>
+      <c r="N55" s="5">
+        <v>4</v>
+      </c>
+      <c r="O55" s="4">
+        <v>45</v>
+      </c>
+      <c r="P55">
+        <v>2</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>143</v>
+      </c>
+      <c r="C56" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" t="s">
+        <v>42</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="4">
+        <v>5</v>
+      </c>
+      <c r="I56" s="5">
+        <v>5</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56" s="4">
+        <v>45</v>
+      </c>
+      <c r="M56">
+        <v>2</v>
+      </c>
+      <c r="N56" s="5">
+        <v>3</v>
+      </c>
+      <c r="O56" s="4">
+        <v>2</v>
+      </c>
+      <c r="P56">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>4</v>
+      </c>
+      <c r="R56" s="4">
+        <v>47</v>
+      </c>
+      <c r="S56">
+        <v>3</v>
+      </c>
+      <c r="T56" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4325,7 +4663,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4353,19 +4691,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4373,37 +4711,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4414,16 +4752,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4434,16 +4772,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4454,13 +4792,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4471,16 +4809,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4491,13 +4829,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4511,13 +4849,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4531,13 +4869,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4551,13 +4889,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -4568,16 +4906,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E12" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -4588,16 +4926,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -4608,19 +4946,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" t="s">
         <v>170</v>
       </c>
-      <c r="C14" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" t="s">
-        <v>160</v>
-      </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -4631,16 +4969,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -4651,16 +4989,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -4671,13 +5009,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4691,16 +5029,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -4711,13 +5049,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -4731,13 +5069,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4751,16 +5089,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -4771,16 +5109,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E22" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -4791,13 +5129,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -4811,19 +5149,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -4834,13 +5172,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -4854,16 +5192,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4877,16 +5215,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -4897,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -4917,19 +5255,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4943,13 +5281,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -4963,19 +5301,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F31" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -4986,19 +5324,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5009,19 +5347,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5032,16 +5370,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5052,16 +5390,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5072,19 +5410,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" t="s">
         <v>203</v>
-      </c>
-      <c r="F36" t="s">
-        <v>193</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5098,13 +5436,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C37" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5118,16 +5456,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5138,13 +5476,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5161,16 +5499,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5181,13 +5519,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5204,19 +5542,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5230,13 +5568,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C43" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5250,13 +5588,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C44" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5270,21 +5608,104 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" t="s">
+        <v>159</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" t="s">
+        <v>227</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47">
+        <v>14</v>
+      </c>
+      <c r="I47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D48" t="s">
+        <v>229</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>156</v>
+      </c>
+      <c r="I48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>230</v>
+      </c>
+      <c r="C49" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="I49">
         <v>-1</v>
       </c>
     </row>
@@ -5298,7 +5719,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -5321,13 +5742,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D1" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -5353,10 +5774,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5382,10 +5803,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -5405,10 +5826,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5428,10 +5849,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5451,10 +5872,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5474,10 +5895,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -5497,10 +5918,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5520,10 +5941,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -5543,10 +5964,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -5566,10 +5987,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -5595,10 +6016,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -5624,10 +6045,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -5647,10 +6068,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -5670,10 +6091,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -5686,6 +6107,52 @@
       </c>
       <c r="G15">
         <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>44</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>46</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -5721,16 +6188,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E1" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="G1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5738,13 +6205,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5758,13 +6225,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D3" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
@@ -5775,13 +6242,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="F4" t="s">
         <v>31</v>
@@ -5792,13 +6259,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5812,13 +6279,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5832,13 +6299,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D7" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
-    <sheet name="Effect" sheetId="2" r:id="rId2"/>
-    <sheet name="Buff" sheetId="3" r:id="rId3"/>
+    <sheet name="Effects" sheetId="2" r:id="rId2"/>
+    <sheet name="Buffs" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1774,7 +1774,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4653,6 +4653,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -6152,7 +6157,7 @@
         <v>46</v>
       </c>
       <c r="G17" s="2">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -12,6 +12,9 @@
     <sheet name="Buffs" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AC$61</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="274">
   <si>
     <t>ID</t>
   </si>
@@ -116,6 +119,9 @@
     <t>功能是否正常</t>
   </si>
   <si>
+    <t>TAG</t>
+  </si>
+  <si>
     <t>互动</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
     <t>Stamina</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
     <t>喝水</t>
   </si>
   <si>
@@ -179,6 +188,9 @@
     <t>获得一个额外回合，神采+7，出牌次数+1</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>渐入佳境</t>
   </si>
   <si>
@@ -197,6 +209,9 @@
     <t>专注+2，神采+2</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>这个好诶</t>
   </si>
   <si>
@@ -458,7 +473,7 @@
     <t>晚上好</t>
   </si>
   <si>
-    <t>亲和力+3，坚毅+2</t>
+    <t>亲和力+3，坚毅+2，开场</t>
   </si>
   <si>
     <t>真情流露</t>
@@ -467,6 +482,33 @@
     <t>坚毅+2，神采+2，之后的三回合内，回合结束时，亲和力变成1.1倍，</t>
   </si>
   <si>
+    <t>耶！</t>
+  </si>
+  <si>
+    <t>参数+10</t>
+  </si>
+  <si>
+    <t>参数+8，亲和力+3</t>
+  </si>
+  <si>
+    <t>应援</t>
+  </si>
+  <si>
+    <t>参数+7，坚毅+2</t>
+  </si>
+  <si>
+    <t>盯~</t>
+  </si>
+  <si>
+    <t>亲和力+5，获得亲和力110%的参数</t>
+  </si>
+  <si>
+    <t>氛围感</t>
+  </si>
+  <si>
+    <t>亲和力+1，以后，回合结束时，亲和力+3</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -723,6 +765,12 @@
   </si>
   <si>
     <t>回合结束时，亲和力变为1.1倍</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力+X</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力+3</t>
   </si>
   <si>
     <t>BuffType</t>
@@ -1774,7 +1822,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -1805,7 +1853,7 @@
     <col min="28" max="28" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1890,25 +1938,28 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="4">
         <v>4</v>
@@ -1932,25 +1983,28 @@
         <v>7</v>
       </c>
       <c r="AB2" s="6"/>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="AD2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -1974,25 +2028,28 @@
         <v>4</v>
       </c>
       <c r="AB3" s="6"/>
-    </row>
-    <row r="4" spans="1:28">
+      <c r="AD3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="4">
         <v>5</v>
@@ -2016,25 +2073,28 @@
         <v>15</v>
       </c>
       <c r="AB4" s="6"/>
-    </row>
-    <row r="5" spans="1:28">
+      <c r="AD4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4">
         <v>3</v>
@@ -2067,25 +2127,28 @@
         <v>2</v>
       </c>
       <c r="AB5" s="6"/>
-    </row>
-    <row r="6" spans="1:28">
+      <c r="AD5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2106,25 +2169,28 @@
         <v>0</v>
       </c>
       <c r="AB6" s="6"/>
-    </row>
-    <row r="7" spans="1:28">
+      <c r="AD6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="4">
         <v>5</v>
@@ -2142,25 +2208,28 @@
         <v>4</v>
       </c>
       <c r="AB7" s="6"/>
-    </row>
-    <row r="8" spans="1:28">
+      <c r="AD7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2205,25 +2274,28 @@
         <v>1</v>
       </c>
       <c r="AB8" s="6"/>
-    </row>
-    <row r="9" spans="1:28">
+      <c r="AD8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -2256,25 +2328,28 @@
         <v>6</v>
       </c>
       <c r="AB9" s="6"/>
-    </row>
-    <row r="10" spans="1:28">
+      <c r="AD9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -2307,25 +2382,28 @@
         <v>4</v>
       </c>
       <c r="AB10" s="6"/>
-    </row>
-    <row r="11" spans="1:28">
+      <c r="AD10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -2358,25 +2436,28 @@
         <v>3</v>
       </c>
       <c r="AB11" s="6"/>
-    </row>
-    <row r="12" spans="1:28">
+      <c r="AD11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -2409,25 +2490,28 @@
         <v>3</v>
       </c>
       <c r="AB12" s="6"/>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="4">
         <v>6</v>
@@ -2461,27 +2545,30 @@
       </c>
       <c r="AB13" s="6"/>
       <c r="AC13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
+        <v>63</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="4">
         <v>5</v>
@@ -2514,25 +2601,28 @@
         <v>9</v>
       </c>
       <c r="AB14" s="6"/>
-    </row>
-    <row r="15" spans="1:28">
+      <c r="AD14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="4">
         <v>5</v>
@@ -2556,25 +2646,28 @@
         <v>8</v>
       </c>
       <c r="AB15" s="6"/>
-    </row>
-    <row r="16" spans="1:28">
+      <c r="AD15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="4">
         <v>4</v>
@@ -2598,25 +2691,28 @@
         <v>1.8</v>
       </c>
       <c r="AB16" s="6"/>
-    </row>
-    <row r="17" spans="1:28">
+      <c r="AD16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H17" s="4">
         <v>6</v>
@@ -2649,25 +2745,28 @@
         <v>1.1</v>
       </c>
       <c r="AB17" s="6"/>
-    </row>
-    <row r="18" spans="1:28">
+      <c r="AD17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="4">
         <v>3</v>
@@ -2709,25 +2808,28 @@
         <v>3</v>
       </c>
       <c r="AB18" s="7"/>
-    </row>
-    <row r="19" spans="1:28">
+      <c r="AD18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="4">
         <v>6</v>
@@ -2745,25 +2847,28 @@
         <v>0</v>
       </c>
       <c r="AB19" s="6"/>
-    </row>
-    <row r="20" spans="1:28">
+      <c r="AD19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="4">
         <v>4</v>
@@ -2787,25 +2892,28 @@
         <v>7</v>
       </c>
       <c r="AB20" s="6"/>
-    </row>
-    <row r="21" spans="1:28">
+      <c r="AD20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H21" s="4">
         <v>5</v>
@@ -2838,25 +2946,28 @@
         <v>2</v>
       </c>
       <c r="AB21" s="6"/>
-    </row>
-    <row r="22" spans="1:28">
+      <c r="AD21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H22" s="4">
         <v>6</v>
@@ -2880,25 +2991,28 @@
         <v>30</v>
       </c>
       <c r="AB22" s="7"/>
-    </row>
-    <row r="23" spans="1:28">
+      <c r="AD22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="4">
         <v>8</v>
@@ -2940,25 +3054,28 @@
         <v>3</v>
       </c>
       <c r="AB23" s="6"/>
-    </row>
-    <row r="24" spans="1:28">
+      <c r="AD23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="4">
         <v>5</v>
@@ -3000,25 +3117,28 @@
         <v>7</v>
       </c>
       <c r="AB24" s="6"/>
-    </row>
-    <row r="25" spans="1:28">
+      <c r="AD24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="4">
         <v>4</v>
@@ -3051,25 +3171,28 @@
         <v>1</v>
       </c>
       <c r="AB25" s="6"/>
-    </row>
-    <row r="26" spans="1:28">
+      <c r="AD25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="4">
         <v>1</v>
@@ -3102,25 +3225,28 @@
         <v>1</v>
       </c>
       <c r="AB26" s="6"/>
-    </row>
-    <row r="27" spans="1:28">
+      <c r="AD26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27" s="4">
         <v>4</v>
@@ -3153,25 +3279,28 @@
         <v>11</v>
       </c>
       <c r="AB27" s="6"/>
-    </row>
-    <row r="28" spans="1:28">
+      <c r="AD27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H28" s="4">
         <v>3</v>
@@ -3195,25 +3324,28 @@
         <v>5</v>
       </c>
       <c r="AB28" s="6"/>
-    </row>
-    <row r="29" spans="1:28">
+      <c r="AD28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="4">
         <v>3</v>
@@ -3246,25 +3378,28 @@
         <v>6</v>
       </c>
       <c r="AB29" s="6"/>
-    </row>
-    <row r="30" spans="1:28">
+      <c r="AD29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3309,25 +3444,28 @@
         <v>1</v>
       </c>
       <c r="AB30" s="6"/>
-    </row>
-    <row r="31" spans="1:28">
+      <c r="AD30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -3363,25 +3501,28 @@
         <v>1</v>
       </c>
       <c r="AB31" s="6"/>
-    </row>
-    <row r="32" spans="1:28">
+      <c r="AD31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="4">
         <v>10</v>
@@ -3423,25 +3564,28 @@
         <v>1</v>
       </c>
       <c r="AB32" s="7"/>
-    </row>
-    <row r="33" spans="1:28">
+      <c r="AD32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="4">
         <v>1</v>
@@ -3465,25 +3609,28 @@
         <v>8</v>
       </c>
       <c r="AB33" s="6"/>
-    </row>
-    <row r="34" spans="1:28">
+      <c r="AD33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H34" s="4">
         <v>6</v>
@@ -3525,25 +3672,28 @@
         <v>1</v>
       </c>
       <c r="AB34" s="7"/>
-    </row>
-    <row r="35" spans="1:28">
+      <c r="AD34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35" s="4">
         <v>5</v>
@@ -3585,25 +3735,28 @@
         <v>3</v>
       </c>
       <c r="AB35" s="6"/>
-    </row>
-    <row r="36" spans="1:28">
+      <c r="AD35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36" s="4">
         <v>4</v>
@@ -3636,25 +3789,28 @@
         <v>4</v>
       </c>
       <c r="AB36" s="7"/>
-    </row>
-    <row r="37" spans="1:28">
+      <c r="AD36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37" s="4">
         <v>4</v>
@@ -3687,25 +3843,28 @@
         <v>1</v>
       </c>
       <c r="AB37" s="7"/>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="AD37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38" s="4">
         <v>7</v>
@@ -3719,25 +3878,28 @@
       <c r="K38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="AD38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39" s="4">
         <v>8</v>
@@ -3760,25 +3922,28 @@
       <c r="N39" s="5">
         <v>54</v>
       </c>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="AD39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H40" s="4">
         <v>3</v>
@@ -3810,25 +3975,28 @@
       <c r="Q40" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="AD40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41" s="4">
         <v>3</v>
@@ -3851,25 +4019,28 @@
       <c r="N41" s="5">
         <v>22</v>
       </c>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="AD41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -3904,25 +4075,28 @@
       <c r="Q42" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="AD42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H43" s="4">
         <v>3</v>
@@ -3954,25 +4128,28 @@
       <c r="Q43" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="AD43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44" s="4">
         <v>3</v>
@@ -4004,25 +4181,28 @@
       <c r="Q44" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="AD44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45" s="4">
         <v>1</v>
@@ -4054,25 +4234,28 @@
       <c r="Q45" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="AD45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H46" s="4">
         <v>1</v>
@@ -4104,25 +4287,28 @@
       <c r="Q46" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:17">
+      <c r="AD46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H47" s="4">
         <v>4</v>
@@ -4154,25 +4340,28 @@
       <c r="Q47" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="AD47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H48" s="4">
         <v>2</v>
@@ -4204,25 +4393,28 @@
       <c r="Q48" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="AD48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H49" s="4">
         <v>4</v>
@@ -4254,25 +4446,28 @@
       <c r="Q49" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="AD49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H50" s="4">
         <v>7</v>
@@ -4313,25 +4508,28 @@
       <c r="T50" s="5">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="51" spans="1:17">
+      <c r="AD50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51" s="4">
         <v>6</v>
@@ -4363,25 +4561,28 @@
       <c r="Q51" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="AD51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H52" s="4">
         <v>5</v>
@@ -4422,25 +4623,28 @@
       <c r="T52" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="AD52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H53" s="4">
         <v>10</v>
@@ -4481,25 +4685,28 @@
       <c r="T53" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="AD53" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G54">
         <v>3</v>
@@ -4543,25 +4750,28 @@
       <c r="T54" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:17">
+      <c r="AD54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H55" s="4">
         <v>4</v>
@@ -4593,25 +4803,28 @@
       <c r="Q55" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="AD55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H56" s="4">
         <v>5</v>
@@ -4652,13 +4865,268 @@
       <c r="T56" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="AD56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
       <c r="A57">
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="4">
+        <v>2</v>
+      </c>
+      <c r="I57" s="5">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4">
+        <v>11</v>
+      </c>
+      <c r="M57">
+        <v>10</v>
+      </c>
+      <c r="N57" s="5">
+        <v>14</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58"/>
+      <c r="C58" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="4">
+        <v>4</v>
+      </c>
+      <c r="I58" s="5">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58" s="4">
+        <v>11</v>
+      </c>
+      <c r="M58">
+        <v>8</v>
+      </c>
+      <c r="N58" s="5">
+        <v>11</v>
+      </c>
+      <c r="O58" s="4">
+        <v>6</v>
+      </c>
+      <c r="P58">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>3</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="4">
+        <v>4</v>
+      </c>
+      <c r="I59" s="5">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59" s="4">
+        <v>11</v>
+      </c>
+      <c r="M59">
+        <v>7</v>
+      </c>
+      <c r="N59" s="5">
+        <v>11</v>
+      </c>
+      <c r="O59" s="4">
+        <v>45</v>
+      </c>
+      <c r="P59">
+        <v>2</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>3</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="4">
+        <v>5</v>
+      </c>
+      <c r="I60" s="5">
+        <v>4</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" s="4">
+        <v>6</v>
+      </c>
+      <c r="M60">
+        <v>5</v>
+      </c>
+      <c r="N60" s="5">
+        <v>7</v>
+      </c>
+      <c r="O60" s="4">
+        <v>18</v>
+      </c>
+      <c r="P60">
+        <v>1.1</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="4">
+        <v>9</v>
+      </c>
+      <c r="I61" s="5">
+        <v>6</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61" s="4">
+        <v>6</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="N61" s="5">
+        <v>3</v>
+      </c>
+      <c r="O61" s="4">
+        <v>49</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AC61" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
@@ -4668,7 +5136,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4696,19 +5164,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4716,13 +5184,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4734,19 +5202,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4757,16 +5225,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4777,16 +5245,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4797,13 +5265,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4814,16 +5282,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4834,13 +5302,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4854,13 +5322,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4874,13 +5342,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4894,13 +5362,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -4911,16 +5379,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -4931,16 +5399,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -4951,19 +5419,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -4974,16 +5442,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -4994,16 +5462,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5014,13 +5482,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5034,16 +5502,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5054,13 +5522,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5074,13 +5542,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5094,16 +5562,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5114,16 +5582,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E22" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5134,13 +5602,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D23" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5154,19 +5622,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C24" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D24" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5177,13 +5645,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C25" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D25" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5197,16 +5665,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C26" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5220,16 +5688,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C27" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D27" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5240,13 +5708,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C28" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5260,19 +5728,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C29" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5286,13 +5754,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5306,19 +5774,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F31" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5329,19 +5797,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5352,19 +5820,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5375,16 +5843,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5395,16 +5863,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5415,19 +5883,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C36" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E36" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F36" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5441,13 +5909,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5461,16 +5929,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5481,13 +5949,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5504,16 +5972,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5524,13 +5992,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5547,19 +6015,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D42" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5573,13 +6041,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C43" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D43" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5593,13 +6061,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D44" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5613,19 +6081,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E45" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5636,16 +6104,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D46" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="E46" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5656,13 +6124,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5676,19 +6144,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C48" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5699,18 +6167,61 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="E49">
         <v>15</v>
       </c>
       <c r="I49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>169</v>
+      </c>
+      <c r="I50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" t="s">
+        <v>245</v>
+      </c>
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51">
+        <v>16</v>
+      </c>
+      <c r="I51">
         <v>-1</v>
       </c>
     </row>
@@ -5724,7 +6235,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -5747,13 +6258,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D1" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -5779,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5808,10 +6319,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -5831,10 +6342,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5854,10 +6365,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5877,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5900,10 +6411,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -5923,10 +6434,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5946,10 +6457,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -5969,10 +6480,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C10" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -5992,10 +6503,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6021,10 +6532,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6050,10 +6561,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6073,10 +6584,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6096,10 +6607,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6119,10 +6630,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6142,10 +6653,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C17" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6158,6 +6669,29 @@
       </c>
       <c r="G17" s="2">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>48</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6193,16 +6727,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6210,13 +6744,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6230,16 +6764,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C3" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1" spans="1:6">
@@ -6247,16 +6781,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6264,13 +6798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6284,13 +6818,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D6" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6304,13 +6838,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4917,7 +4917,6 @@
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58"/>
       <c r="C58" t="s">
         <v>151</v>
       </c>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>亲和力+1，以后，回合结束时，亲和力+3</t>
+  </si>
+  <si>
+    <t>摘花</t>
+  </si>
+  <si>
+    <t>抽两张牌，体力消耗减少+2回合</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -1822,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5122,6 +5128,56 @@
         <v>51</v>
       </c>
     </row>
+    <row r="62" spans="1:17">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="4">
+        <v>1</v>
+      </c>
+      <c r="I62" s="5">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62" s="4">
+        <v>9</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62" s="5">
+        <v>2</v>
+      </c>
+      <c r="O62" s="4">
+        <v>21</v>
+      </c>
+      <c r="P62">
+        <v>2</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AC61" etc:filterBottomFollowUsedRange="0">
     <extLst/>
@@ -5163,19 +5219,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5183,13 +5239,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5201,19 +5257,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5224,16 +5280,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5244,16 +5300,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5264,13 +5320,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5281,16 +5337,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5301,13 +5357,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5321,13 +5377,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5341,13 +5397,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
         <v>185</v>
-      </c>
-      <c r="C10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" t="s">
-        <v>183</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5361,13 +5417,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5378,16 +5434,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5398,16 +5454,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5418,19 +5474,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5441,16 +5497,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D15" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5461,16 +5517,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5481,13 +5537,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5501,16 +5557,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5521,13 +5577,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5541,13 +5597,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5561,16 +5617,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5581,16 +5637,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5601,13 +5657,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5621,19 +5677,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5644,13 +5700,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5664,16 +5720,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5687,16 +5743,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D27" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5707,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5727,19 +5783,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5753,13 +5809,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5773,19 +5829,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5796,19 +5852,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5819,19 +5875,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5842,16 +5898,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5862,16 +5918,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5882,19 +5938,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5908,13 +5964,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5928,16 +5984,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5948,13 +6004,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5971,16 +6027,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5991,13 +6047,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6014,19 +6070,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6040,13 +6096,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6060,13 +6116,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6080,19 +6136,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F45" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6103,16 +6159,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C46" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6123,13 +6179,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6143,19 +6199,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6166,13 +6222,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C49" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6186,19 +6242,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6209,13 +6265,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6257,13 +6313,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -6289,10 +6345,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6318,10 +6374,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6341,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" t="s">
         <v>252</v>
-      </c>
-      <c r="C4" t="s">
-        <v>250</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6364,10 +6420,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6387,10 +6443,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6410,10 +6466,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" t="s">
         <v>256</v>
-      </c>
-      <c r="C7" t="s">
-        <v>254</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6433,10 +6489,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6456,10 +6512,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6479,10 +6535,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6502,10 +6558,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6531,10 +6587,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6560,10 +6616,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6583,10 +6639,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6606,10 +6662,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6629,10 +6685,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6652,10 +6708,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6675,10 +6731,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6726,16 +6782,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6743,13 +6799,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6763,13 +6819,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" t="s">
         <v>269</v>
-      </c>
-      <c r="D3" t="s">
-        <v>267</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>
@@ -6780,13 +6836,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
         <v>269</v>
-      </c>
-      <c r="D4" t="s">
-        <v>267</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -6797,13 +6853,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6817,13 +6873,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6837,13 +6893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AC$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AD$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -137,7 +137,7 @@
     <t>Stamina</t>
   </si>
   <si>
-    <t>T</t>
+    <t>F</t>
   </si>
   <si>
     <t>喝水</t>
@@ -188,7 +188,7 @@
     <t>获得一个额外回合，神采+7，出牌次数+1</t>
   </si>
   <si>
-    <t>L</t>
+    <t>I</t>
   </si>
   <si>
     <t>渐入佳境</t>
@@ -209,13 +209,13 @@
     <t>专注+2，神采+2</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>这个好诶</t>
-  </si>
-  <si>
-    <t>好调+2，神采+2</t>
+    <t>C</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
   </si>
   <si>
     <t>二次推流</t>
@@ -260,10 +260,10 @@
     <t>再一次</t>
   </si>
   <si>
-    <t>KIRAKIRA</t>
-  </si>
-  <si>
-    <t>好调+5</t>
+    <t>攻击弹幕</t>
+  </si>
+  <si>
+    <t>红温+5</t>
   </si>
   <si>
     <t>神降临</t>
@@ -272,16 +272,16 @@
     <t>专注+1，以后，每回合结束时，专注+2</t>
   </si>
   <si>
-    <t>试麦</t>
-  </si>
-  <si>
-    <t>在有好调的状态下可使用，参数+24</t>
-  </si>
-  <si>
-    <t>全心全力</t>
-  </si>
-  <si>
-    <t>好调+4，专注+5，体力消耗减少+2回合</t>
+    <t>点名弹幕</t>
+  </si>
+  <si>
+    <t>在有红温的状态下可使用，参数+24</t>
+  </si>
+  <si>
+    <t>对线</t>
+  </si>
+  <si>
+    <t>红温+4，专注+5，体力消耗减少+2回合</t>
   </si>
   <si>
     <t>红温</t>
@@ -305,7 +305,7 @@
     <t>冲刺！</t>
   </si>
   <si>
-    <t>好调+3，参数+8</t>
+    <t>红温+3，参数+8</t>
   </si>
   <si>
     <t>闭眼</t>
@@ -320,10 +320,10 @@
     <t>专注+3，神采+4</t>
   </si>
   <si>
-    <t>休息完毕</t>
-  </si>
-  <si>
-    <t>好调+3，参数+9，卡牌使用次数+1</t>
+    <t>激怒</t>
+  </si>
+  <si>
+    <t>红温+3，参数+9，卡牌使用次数+1</t>
   </si>
   <si>
     <t>进入状态</t>
@@ -335,7 +335,7 @@
     <t>状态火热</t>
   </si>
   <si>
-    <t>好调+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
+    <t>红温+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
   </si>
   <si>
     <t>躺</t>
@@ -380,10 +380,10 @@
     <t>参数+42</t>
   </si>
   <si>
-    <t>深呼吸</t>
-  </si>
-  <si>
-    <t>有好调的状态下，专注+1，好调+3</t>
+    <t>越想越气</t>
+  </si>
+  <si>
+    <t>有红温的状态下，专注+1，红温+3</t>
   </si>
   <si>
     <t>欢呼</t>
@@ -398,10 +398,7 @@
     <t>专注+6，神采+3</t>
   </si>
   <si>
-    <t>打CALL</t>
-  </si>
-  <si>
-    <t>好调+3，神采+6</t>
+    <t>红温+3，神采+6</t>
   </si>
   <si>
     <t>观察</t>
@@ -446,10 +443,10 @@
     <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
   </si>
   <si>
-    <t>前方的闪耀</t>
-  </si>
-  <si>
-    <t>好调+2，之后4回合内，回合结束时，参数+4</t>
+    <t>申请对线</t>
+  </si>
+  <si>
+    <t>红温+2，之后4回合内，回合结束时，参数+4</t>
   </si>
   <si>
     <t>子弹时间</t>
@@ -470,18 +467,6 @@
     <t>参数+5两次，舰长+1</t>
   </si>
   <si>
-    <t>晚上好</t>
-  </si>
-  <si>
-    <t>亲和力+3，坚毅+2，开场</t>
-  </si>
-  <si>
-    <t>真情流露</t>
-  </si>
-  <si>
-    <t>坚毅+2，神采+2，之后的三回合内，回合结束时，亲和力变成1.1倍，</t>
-  </si>
-  <si>
     <t>耶！</t>
   </si>
   <si>
@@ -494,7 +479,7 @@
     <t>应援</t>
   </si>
   <si>
-    <t>参数+7，坚毅+2</t>
+    <t>参数+7，幽默+2</t>
   </si>
   <si>
     <t>盯~</t>
@@ -515,6 +500,12 @@
     <t>抽两张牌，体力消耗减少+2回合</t>
   </si>
   <si>
+    <t>点炮仗</t>
+  </si>
+  <si>
+    <t>减少</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -638,7 +629,7 @@
     <t>BAPlayLeft</t>
   </si>
   <si>
-    <t>好调+X</t>
+    <t>红温+X</t>
   </si>
   <si>
     <t>参数获得量+X</t>
@@ -677,7 +668,7 @@
     <t>以后回合结束时专注+X</t>
   </si>
   <si>
-    <t>在有好调时，参数+X</t>
+    <t>在有红温时，参数+X</t>
   </si>
   <si>
     <t>体力消耗增加X%</t>
@@ -734,7 +725,7 @@
     <t>获得同接数X%的流水</t>
   </si>
   <si>
-    <t>有好调时，专注+X</t>
+    <t>有红温时，专注+X</t>
   </si>
   <si>
     <t>体力回复X点</t>
@@ -761,7 +752,7 @@
     <t>神采获得量增加X</t>
   </si>
   <si>
-    <t>坚毅+X</t>
+    <t>幽默+X</t>
   </si>
   <si>
     <t>回合结束时，亲和力变为X倍</t>
@@ -779,6 +770,12 @@
     <t>回合结束时，亲和力+3</t>
   </si>
   <si>
+    <t>获得红温X%的参数</t>
+  </si>
+  <si>
+    <t>减少X%的红温</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -800,9 +797,6 @@
     <t>积极</t>
   </si>
   <si>
-    <t>好调</t>
-  </si>
-  <si>
     <t>Persistent</t>
   </si>
   <si>
@@ -821,7 +815,13 @@
     <t>回合结束时，参数+4</t>
   </si>
   <si>
-    <t>坚毅</t>
+    <t>幽默</t>
+  </si>
+  <si>
+    <t>营业</t>
+  </si>
+  <si>
+    <t>盐</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1828,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD62"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4089,11 +4089,11 @@
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43">
+        <v>144</v>
+      </c>
+      <c r="C43" t="s">
         <v>121</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
       </c>
       <c r="D43" t="s">
         <v>48</v>
@@ -4143,10 +4143,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" t="s">
         <v>123</v>
-      </c>
-      <c r="C44" t="s">
-        <v>124</v>
       </c>
       <c r="D44" t="s">
         <v>48</v>
@@ -4196,10 +4196,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" t="s">
         <v>125</v>
-      </c>
-      <c r="C45" t="s">
-        <v>126</v>
       </c>
       <c r="D45" t="s">
         <v>44</v>
@@ -4249,10 +4249,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" t="s">
         <v>127</v>
-      </c>
-      <c r="C46" t="s">
-        <v>128</v>
       </c>
       <c r="D46" t="s">
         <v>44</v>
@@ -4302,10 +4302,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" t="s">
         <v>129</v>
-      </c>
-      <c r="C47" t="s">
-        <v>130</v>
       </c>
       <c r="D47" t="s">
         <v>44</v>
@@ -4355,10 +4355,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" t="s">
         <v>131</v>
-      </c>
-      <c r="C48" t="s">
-        <v>132</v>
       </c>
       <c r="D48" t="s">
         <v>31</v>
@@ -4408,10 +4408,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" t="s">
         <v>133</v>
-      </c>
-      <c r="C49" t="s">
-        <v>134</v>
       </c>
       <c r="D49" t="s">
         <v>48</v>
@@ -4461,10 +4461,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" t="s">
         <v>135</v>
-      </c>
-      <c r="C50" t="s">
-        <v>136</v>
       </c>
       <c r="D50" t="s">
         <v>48</v>
@@ -4523,10 +4523,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" t="s">
         <v>137</v>
-      </c>
-      <c r="C51" t="s">
-        <v>138</v>
       </c>
       <c r="D51" t="s">
         <v>44</v>
@@ -4576,10 +4576,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
         <v>139</v>
-      </c>
-      <c r="C52" t="s">
-        <v>140</v>
       </c>
       <c r="D52" t="s">
         <v>48</v>
@@ -4638,10 +4638,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" t="s">
         <v>141</v>
-      </c>
-      <c r="C53" t="s">
-        <v>142</v>
       </c>
       <c r="D53" t="s">
         <v>44</v>
@@ -4700,10 +4700,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
         <v>143</v>
-      </c>
-      <c r="C54" t="s">
-        <v>144</v>
       </c>
       <c r="D54" t="s">
         <v>44</v>
@@ -4765,110 +4765,89 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
-      </c>
-      <c r="C55" t="s">
-        <v>146</v>
       </c>
       <c r="D55" t="s">
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
         <v>33</v>
       </c>
       <c r="H55" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55" s="4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N55" s="5">
-        <v>4</v>
-      </c>
-      <c r="O55" s="4">
-        <v>45</v>
-      </c>
-      <c r="P55">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AD55" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:30">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
-        <v>147</v>
-      </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I56" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N56" s="5">
+        <v>11</v>
+      </c>
+      <c r="O56" s="4">
+        <v>6</v>
+      </c>
+      <c r="P56">
         <v>3</v>
       </c>
-      <c r="O56" s="4">
-        <v>2</v>
-      </c>
-      <c r="P56">
-        <v>2</v>
-      </c>
       <c r="Q56" s="5">
-        <v>4</v>
-      </c>
-      <c r="R56" s="4">
-        <v>47</v>
-      </c>
-      <c r="S56">
-        <v>3</v>
-      </c>
-      <c r="T56" s="5">
         <v>3</v>
       </c>
       <c r="AD56" t="s">
@@ -4880,10 +4859,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D57" t="s">
         <v>31</v>
@@ -4895,10 +4874,10 @@
         <v>33</v>
       </c>
       <c r="H57" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4910,24 +4889,36 @@
         <v>11</v>
       </c>
       <c r="M57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N57" s="5">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="O57" s="4">
+        <v>45</v>
+      </c>
+      <c r="P57">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>3</v>
       </c>
       <c r="AD57" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:30">
       <c r="A58">
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>149</v>
+      </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
         <v>32</v>
@@ -4936,34 +4927,34 @@
         <v>33</v>
       </c>
       <c r="H58" s="4">
+        <v>5</v>
+      </c>
+      <c r="I58" s="5">
         <v>4</v>
       </c>
-      <c r="I58" s="5">
-        <v>3</v>
-      </c>
       <c r="J58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M58">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N58" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O58" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="Q58" s="5">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AD58" t="s">
         <v>51</v>
@@ -4974,78 +4965,78 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" t="s">
         <v>152</v>
       </c>
-      <c r="C59" t="s">
-        <v>153</v>
-      </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F59" t="s">
         <v>33</v>
       </c>
       <c r="H59" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I59" s="5">
+        <v>6</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59" s="4">
+        <v>6</v>
+      </c>
+      <c r="M59">
+        <v>1</v>
+      </c>
+      <c r="N59" s="5">
         <v>3</v>
       </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4">
-        <v>11</v>
-      </c>
-      <c r="M59">
-        <v>7</v>
-      </c>
-      <c r="N59" s="5">
-        <v>11</v>
-      </c>
       <c r="O59" s="4">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD59" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:30">
+    <row r="60" spans="1:17">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
         <v>154</v>
       </c>
-      <c r="C60" t="s">
-        <v>155</v>
-      </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F60" t="s">
         <v>33</v>
       </c>
       <c r="H60" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -5054,132 +5045,58 @@
         <v>1</v>
       </c>
       <c r="L60" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N60" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O60" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P60">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
         <v>156</v>
-      </c>
-      <c r="C61" t="s">
-        <v>157</v>
       </c>
       <c r="D61" t="s">
         <v>44</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
         <v>33</v>
       </c>
       <c r="H61" s="4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I61" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
-      <c r="L61" s="4">
-        <v>6</v>
-      </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-      <c r="N61" s="5">
-        <v>3</v>
-      </c>
-      <c r="O61" s="4">
-        <v>49</v>
-      </c>
-      <c r="P61">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD61" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62" t="s">
-        <v>158</v>
-      </c>
-      <c r="C62" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H62" s="4">
-        <v>1</v>
-      </c>
-      <c r="I62" s="5">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4">
-        <v>9</v>
-      </c>
-      <c r="M62">
-        <v>2</v>
-      </c>
-      <c r="N62" s="5">
-        <v>2</v>
-      </c>
-      <c r="O62" s="4">
-        <v>21</v>
-      </c>
-      <c r="P62">
-        <v>2</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AC61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AD62" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5191,7 +5108,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5219,19 +5136,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" t="s">
         <v>161</v>
-      </c>
-      <c r="G1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5239,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5257,19 +5174,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" t="s">
         <v>167</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>168</v>
-      </c>
-      <c r="D3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" t="s">
-        <v>171</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5280,16 +5197,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5300,16 +5217,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5320,13 +5237,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5337,16 +5254,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5357,13 +5274,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5377,13 +5294,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5397,13 +5314,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5417,13 +5334,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5434,16 +5351,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5454,16 +5371,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5474,19 +5391,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5497,16 +5414,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5517,16 +5434,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5537,13 +5454,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5557,16 +5474,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5577,13 +5494,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5597,13 +5514,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5617,16 +5534,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E21" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5637,16 +5554,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5657,13 +5574,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5677,19 +5594,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5700,13 +5617,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5720,16 +5637,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5743,16 +5660,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E27" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5763,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5783,19 +5700,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5809,13 +5726,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C30" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5829,19 +5746,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5852,19 +5769,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5875,19 +5792,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5898,16 +5815,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5918,16 +5835,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5938,19 +5855,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5964,13 +5881,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5984,16 +5901,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E38" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6004,13 +5921,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6027,16 +5944,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E40" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6047,13 +5964,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6070,19 +5987,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6096,13 +6013,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6116,13 +6033,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C44" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6136,19 +6053,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" t="s">
         <v>167</v>
       </c>
-      <c r="D45" t="s">
-        <v>169</v>
-      </c>
-      <c r="E45" t="s">
-        <v>170</v>
-      </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6159,16 +6076,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D46" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E46" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6179,13 +6096,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C47" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D47" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6199,19 +6116,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D48" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6222,13 +6139,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6242,19 +6159,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C50" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6265,19 +6182,47 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E51">
         <v>16</v>
       </c>
       <c r="I51">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>245</v>
+      </c>
+      <c r="C52" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -6290,7 +6235,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -6313,13 +6258,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" t="s">
         <v>248</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -6345,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" t="s">
         <v>251</v>
-      </c>
-      <c r="C2" t="s">
-        <v>252</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6374,10 +6319,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6397,10 +6342,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6420,10 +6365,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6443,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6466,10 +6411,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6489,10 +6434,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6512,10 +6457,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6535,10 +6480,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6558,10 +6503,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6587,10 +6532,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6616,10 +6561,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6639,10 +6584,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6662,10 +6607,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6685,10 +6630,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6708,10 +6653,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6731,10 +6676,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6747,6 +6692,22 @@
       </c>
       <c r="G18">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="275">
   <si>
     <t>ID</t>
   </si>
@@ -771,9 +771,6 @@
   </si>
   <si>
     <t>获得红温X%的参数</t>
-  </si>
-  <si>
-    <t>减少X%的红温</t>
   </si>
   <si>
     <t>BuffType</t>
@@ -5108,7 +5105,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -6215,14 +6212,6 @@
       </c>
       <c r="I52">
         <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -6258,13 +6247,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1" t="s">
         <v>247</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -6290,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" t="s">
         <v>250</v>
-      </c>
-      <c r="C2" t="s">
-        <v>251</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6319,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6342,10 +6331,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6368,7 +6357,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6388,10 +6377,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6411,10 +6400,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6434,10 +6423,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6457,10 +6446,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6483,7 +6472,7 @@
         <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6506,7 +6495,7 @@
         <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6535,7 +6524,7 @@
         <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6564,7 +6553,7 @@
         <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6587,7 +6576,7 @@
         <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6607,10 +6596,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6630,10 +6619,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6656,7 +6645,7 @@
         <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6679,7 +6668,7 @@
         <v>244</v>
       </c>
       <c r="C18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6694,20 +6683,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>260</v>
+      </c>
+      <c r="C19" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>261</v>
+      </c>
+      <c r="C20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6743,16 +6750,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" t="s">
         <v>263</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>264</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>265</v>
-      </c>
-      <c r="G1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6760,13 +6767,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" t="s">
         <v>267</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>268</v>
-      </c>
-      <c r="D2" t="s">
-        <v>269</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6780,13 +6787,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" t="s">
         <v>270</v>
       </c>
-      <c r="C3" t="s">
-        <v>271</v>
-      </c>
       <c r="D3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>
@@ -6797,13 +6804,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -6814,13 +6821,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" t="s">
         <v>268</v>
-      </c>
-      <c r="D5" t="s">
-        <v>269</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6834,13 +6841,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" t="s">
         <v>268</v>
-      </c>
-      <c r="D6" t="s">
-        <v>269</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6854,13 +6861,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" t="s">
         <v>268</v>
-      </c>
-      <c r="D7" t="s">
-        <v>269</v>
       </c>
       <c r="E7">
         <v>0</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AD$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="270">
   <si>
     <t>ID</t>
   </si>
@@ -209,15 +209,15 @@
     <t>专注+2，神采+2</t>
   </si>
   <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>红温+2，神采+2</t>
-  </si>
-  <si>
     <t>二次推流</t>
   </si>
   <si>
@@ -278,12 +278,6 @@
     <t>在有红温的状态下可使用，参数+24</t>
   </si>
   <si>
-    <t>对线</t>
-  </si>
-  <si>
-    <t>红温+4，专注+5，体力消耗减少+2回合</t>
-  </si>
-  <si>
     <t>红温</t>
   </si>
   <si>
@@ -320,18 +314,6 @@
     <t>专注+3，神采+4</t>
   </si>
   <si>
-    <t>激怒</t>
-  </si>
-  <si>
-    <t>红温+3，参数+9，卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>进入状态</t>
-  </si>
-  <si>
-    <t>专注+4，卡牌使用次数+1</t>
-  </si>
-  <si>
     <t>状态火热</t>
   </si>
   <si>
@@ -392,12 +374,6 @@
     <t>参数+18</t>
   </si>
   <si>
-    <t>发呆</t>
-  </si>
-  <si>
-    <t>专注+6，神采+3</t>
-  </si>
-  <si>
     <t>红温+3，神采+6</t>
   </si>
   <si>
@@ -461,12 +437,6 @@
     <t>流水+40，同接+30，舰长+1</t>
   </si>
   <si>
-    <t>大航海</t>
-  </si>
-  <si>
-    <t>参数+5两次，舰长+1</t>
-  </si>
-  <si>
     <t>耶！</t>
   </si>
   <si>
@@ -503,7 +473,7 @@
     <t>点炮仗</t>
   </si>
   <si>
-    <t>减少</t>
+    <t>红温&gt;10层时可使用，获得红温200%的参数，红温减少50%</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -773,6 +743,18 @@
     <t>获得红温X%的参数</t>
   </si>
   <si>
+    <t>减少X%的红温</t>
+  </si>
+  <si>
+    <t>当红温&gt;10层时，获得红温X%的参数</t>
+  </si>
+  <si>
+    <t>当红温&gt;10层时，减少X%的红温</t>
+  </si>
+  <si>
+    <t>同接增加X%</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -833,7 +815,7 @@
     <t>TargetDelta</t>
   </si>
   <si>
-    <t>有好调时</t>
+    <t>有红温时</t>
   </si>
   <si>
     <t>VBuffLayerCondition</t>
@@ -851,13 +833,16 @@
     <t>使用A卡时</t>
   </si>
   <si>
-    <t>当好调大于3层时</t>
+    <t>当红温大于3层时</t>
   </si>
   <si>
     <t>当专注大于4层时</t>
   </si>
   <si>
     <t>当亲和力大于3层时</t>
+  </si>
+  <si>
+    <t>当红温大于10层时</t>
   </si>
 </sst>
 </file>
@@ -1825,7 +1810,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -1839,24 +1824,25 @@
     <col min="9" max="9" width="14" style="5" customWidth="1"/>
     <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
     <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" style="4" customWidth="1"/>
-    <col min="13" max="13" width="12.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="15" max="15" width="11" style="4" customWidth="1"/>
-    <col min="16" max="16" width="12.2833333333333" customWidth="1"/>
-    <col min="17" max="17" width="17.1416666666667" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9" style="4"/>
-    <col min="20" max="20" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="21" max="21" width="10.7083333333333" style="4" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="24" max="24" width="12.425" style="4" customWidth="1"/>
-    <col min="25" max="25" width="12.425" style="5" customWidth="1"/>
-    <col min="26" max="26" width="12.2833333333333" customWidth="1"/>
-    <col min="28" max="28" width="4.28333333333333" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" customWidth="1"/>
+    <col min="13" max="13" width="9.70833333333333" style="4" customWidth="1"/>
+    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
+    <col min="15" max="15" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="16" max="16" width="11" style="4" customWidth="1"/>
+    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
+    <col min="18" max="18" width="17.1416666666667" style="5" customWidth="1"/>
+    <col min="19" max="19" width="9" style="4"/>
+    <col min="21" max="21" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="22" max="22" width="10.7083333333333" style="4" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="17.7083333333333" style="5" customWidth="1"/>
+    <col min="25" max="25" width="12.425" style="4" customWidth="1"/>
+    <col min="26" max="26" width="12.425" style="5" customWidth="1"/>
+    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
+    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1890,62 +1876,62 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1976,21 +1962,21 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2" s="4">
+      <c r="M2" s="4">
         <v>11</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>7</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AD2" t="s">
+      <c r="AC2" s="6"/>
+      <c r="AE2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2021,21 +2007,21 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3">
+      <c r="M3" s="4">
+        <v>2</v>
+      </c>
+      <c r="N3">
         <v>4</v>
       </c>
-      <c r="N3" s="5">
+      <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="AB3" s="6"/>
-      <c r="AD3" t="s">
+      <c r="AC3" s="6"/>
+      <c r="AE3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2066,21 +2052,21 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>11</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>15</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>15</v>
       </c>
-      <c r="AB4" s="6"/>
-      <c r="AD4" t="s">
+      <c r="AC4" s="6"/>
+      <c r="AE4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2111,30 +2097,30 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>11</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>5</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>5</v>
       </c>
-      <c r="O5" s="4">
-        <v>2</v>
-      </c>
-      <c r="P5">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="6"/>
-      <c r="AD5" t="s">
+      <c r="P5" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="6"/>
+      <c r="AE5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2168,15 +2154,15 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6"/>
-      <c r="AD6" t="s">
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="6"/>
+      <c r="AE6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2207,15 +2193,15 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>4</v>
       </c>
-      <c r="AB7" s="6"/>
-      <c r="AD7" t="s">
+      <c r="AC7" s="6"/>
+      <c r="AE7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2249,39 +2235,39 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8" s="4">
-        <v>2</v>
-      </c>
-      <c r="M8">
+      <c r="M8" s="4">
+        <v>2</v>
+      </c>
+      <c r="N8">
         <v>7</v>
       </c>
-      <c r="N8" s="5">
+      <c r="O8" s="5">
         <v>7</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>3</v>
       </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4">
         <v>14</v>
       </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="6"/>
-      <c r="AD8" t="s">
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="6"/>
+      <c r="AE8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2312,30 +2298,30 @@
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>17</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" s="5">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4">
-        <v>2</v>
-      </c>
-      <c r="P9">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q9">
         <v>4</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="R9" s="5">
         <v>6</v>
       </c>
-      <c r="AB9" s="6"/>
-      <c r="AD9" t="s">
+      <c r="AC9" s="6"/>
+      <c r="AE9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2366,30 +2352,30 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>6</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>3</v>
       </c>
-      <c r="N10" s="5">
+      <c r="O10" s="5">
         <v>4</v>
       </c>
-      <c r="O10" s="4">
-        <v>2</v>
-      </c>
-      <c r="P10">
+      <c r="P10" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q10">
         <v>3</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="R10" s="5">
         <v>4</v>
       </c>
-      <c r="AB10" s="6"/>
-      <c r="AD10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="AC10" s="6"/>
+      <c r="AE10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2420,38 +2406,38 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <v>7</v>
       </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-      <c r="N11" s="5">
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" s="5">
         <v>3</v>
       </c>
-      <c r="O11" s="4">
-        <v>2</v>
-      </c>
-      <c r="P11">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="5">
+      <c r="P11" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>2</v>
+      </c>
+      <c r="R11" s="5">
         <v>3</v>
       </c>
-      <c r="AB11" s="6"/>
-      <c r="AD11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
+      <c r="AC11" s="6"/>
+      <c r="AE11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -2474,30 +2460,30 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <v>15</v>
       </c>
-      <c r="M12">
-        <v>2</v>
-      </c>
-      <c r="N12" s="5">
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" s="5">
         <v>3</v>
       </c>
-      <c r="O12" s="4">
-        <v>2</v>
-      </c>
-      <c r="P12">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="5">
+      <c r="P12" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12" s="5">
         <v>3</v>
       </c>
-      <c r="AB12" s="6"/>
-      <c r="AD12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30">
+      <c r="AC12" s="6"/>
+      <c r="AE12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2528,33 +2514,33 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
         <v>11</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>9</v>
       </c>
-      <c r="N13" s="5">
+      <c r="O13" s="5">
         <v>13</v>
       </c>
-      <c r="O13" s="4">
+      <c r="P13" s="4">
         <v>11</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>9</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="R13" s="5">
         <v>13</v>
       </c>
-      <c r="AB13" s="6"/>
-      <c r="AC13" t="s">
+      <c r="AC13" s="6"/>
+      <c r="AD13" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2585,30 +2571,30 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <v>11</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>11</v>
       </c>
-      <c r="N14" s="5">
+      <c r="O14" s="5">
         <v>15</v>
       </c>
-      <c r="O14" s="4">
-        <v>2</v>
-      </c>
-      <c r="P14">
+      <c r="P14" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q14">
         <v>7</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="R14" s="5">
         <v>9</v>
       </c>
-      <c r="AB14" s="6"/>
-      <c r="AD14" t="s">
+      <c r="AC14" s="6"/>
+      <c r="AE14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2639,21 +2625,21 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <v>6</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>6</v>
       </c>
-      <c r="N15" s="5">
+      <c r="O15" s="5">
         <v>8</v>
       </c>
-      <c r="AB15" s="6"/>
-      <c r="AD15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30">
+      <c r="AC15" s="6"/>
+      <c r="AE15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2684,21 +2670,21 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16" s="4">
+      <c r="M16" s="4">
         <v>18</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1.4</v>
       </c>
-      <c r="N16" s="5">
+      <c r="O16" s="5">
         <v>1.8</v>
       </c>
-      <c r="AB16" s="6"/>
-      <c r="AD16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30">
+      <c r="AC16" s="6"/>
+      <c r="AE16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2729,30 +2715,30 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
         <v>6</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>4</v>
       </c>
-      <c r="N17" s="5">
+      <c r="O17" s="5">
         <v>5</v>
       </c>
-      <c r="O17" s="4">
+      <c r="P17" s="4">
         <v>18</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.8</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="R17" s="5">
         <v>1.1</v>
       </c>
-      <c r="AB17" s="6"/>
-      <c r="AD17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30">
+      <c r="AC17" s="6"/>
+      <c r="AE17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2783,39 +2769,39 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="4">
         <v>19</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" s="5">
-        <v>1</v>
-      </c>
-      <c r="O18" s="4">
-        <v>2</v>
-      </c>
-      <c r="P18">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5">
+        <v>1</v>
+      </c>
+      <c r="P18" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q18">
         <v>4</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="R18" s="5">
         <v>6</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <v>21</v>
       </c>
-      <c r="S18">
-        <v>2</v>
-      </c>
-      <c r="T18" s="5">
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18" s="5">
         <v>3</v>
       </c>
-      <c r="AB18" s="7"/>
-      <c r="AD18" t="s">
+      <c r="AC18" s="7"/>
+      <c r="AE18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:31">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2846,15 +2832,15 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="6"/>
-      <c r="AD19" t="s">
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6"/>
+      <c r="AE19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:31">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2885,21 +2871,21 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="4">
         <v>15</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>5</v>
       </c>
-      <c r="N20" s="5">
+      <c r="O20" s="5">
         <v>7</v>
       </c>
-      <c r="AB20" s="6"/>
-      <c r="AD20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30">
+      <c r="AC20" s="6"/>
+      <c r="AE20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2930,30 +2916,30 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="4">
         <v>23</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21" s="5">
-        <v>1</v>
-      </c>
-      <c r="O21" s="4">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1</v>
+      </c>
+      <c r="P21" s="4">
         <v>7</v>
       </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB21" s="6"/>
-      <c r="AD21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30">
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="6"/>
+      <c r="AE21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2984,92 +2970,43 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" s="4">
+      <c r="M22" s="4">
         <v>24</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>24</v>
       </c>
-      <c r="N22" s="5">
+      <c r="O22" s="5">
         <v>30</v>
       </c>
-      <c r="AB22" s="7"/>
-      <c r="AD22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30">
+      <c r="AC22" s="7"/>
+      <c r="AE22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="4">
-        <v>8</v>
-      </c>
-      <c r="I23" s="5">
-        <v>6</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4">
-        <v>15</v>
-      </c>
-      <c r="M23">
-        <v>4</v>
-      </c>
-      <c r="N23" s="5">
-        <v>5</v>
-      </c>
-      <c r="O23" s="4">
-        <v>7</v>
-      </c>
-      <c r="P23">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>6</v>
-      </c>
-      <c r="R23" s="4">
-        <v>21</v>
-      </c>
-      <c r="S23">
-        <v>2</v>
-      </c>
-      <c r="T23" s="5">
-        <v>3</v>
-      </c>
-      <c r="AB23" s="6"/>
-      <c r="AD23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30">
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="AC23" s="6"/>
+      <c r="AE23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
@@ -3092,47 +3029,47 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="L24" s="4">
+      <c r="M24" s="4">
         <v>26</v>
       </c>
-      <c r="M24">
-        <v>2</v>
-      </c>
-      <c r="N24" s="5">
-        <v>2</v>
-      </c>
-      <c r="O24" s="4">
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24" s="5">
+        <v>2</v>
+      </c>
+      <c r="P24" s="4">
         <v>11</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>30</v>
       </c>
-      <c r="Q24" s="5">
+      <c r="R24" s="5">
         <v>42</v>
       </c>
-      <c r="R24" s="4">
-        <v>2</v>
-      </c>
-      <c r="S24">
+      <c r="S24" s="4">
+        <v>2</v>
+      </c>
+      <c r="T24">
         <v>5</v>
       </c>
-      <c r="T24" s="5">
+      <c r="U24" s="5">
         <v>7</v>
       </c>
-      <c r="AB24" s="6"/>
-      <c r="AD24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30">
+      <c r="AC24" s="6"/>
+      <c r="AE24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
@@ -3155,38 +3092,38 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="L25" s="4">
+      <c r="M25" s="4">
         <v>6</v>
       </c>
-      <c r="M25">
-        <v>2</v>
-      </c>
-      <c r="N25" s="5">
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" s="5">
         <v>4</v>
       </c>
-      <c r="O25" s="4">
+      <c r="P25" s="4">
         <v>28</v>
       </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="6"/>
-      <c r="AD25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30">
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="6"/>
+      <c r="AE25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
@@ -3209,38 +3146,38 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="4">
+      <c r="M26" s="4">
         <v>6</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>5</v>
       </c>
-      <c r="N26" s="5">
+      <c r="O26" s="5">
         <v>7</v>
       </c>
-      <c r="O26" s="4">
-        <v>2</v>
-      </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="6"/>
-      <c r="AD26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30">
+      <c r="P26" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="6"/>
+      <c r="AE26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
@@ -3263,38 +3200,38 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27" s="4">
+      <c r="M27" s="4">
         <v>15</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>3</v>
       </c>
-      <c r="N27" s="5">
+      <c r="O27" s="5">
         <v>4</v>
       </c>
-      <c r="O27" s="4">
+      <c r="P27" s="4">
         <v>11</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>8</v>
       </c>
-      <c r="Q27" s="5">
+      <c r="R27" s="5">
         <v>11</v>
       </c>
-      <c r="AB27" s="6"/>
-      <c r="AD27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30">
+      <c r="AC27" s="6"/>
+      <c r="AE27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -3317,29 +3254,29 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="4">
+      <c r="M28" s="4">
         <v>7</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>3</v>
       </c>
-      <c r="N28" s="5">
+      <c r="O28" s="5">
         <v>5</v>
       </c>
-      <c r="AB28" s="6"/>
-      <c r="AD28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30">
+      <c r="AC28" s="6"/>
+      <c r="AE28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>31</v>
@@ -3362,161 +3299,146 @@
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="L29" s="4">
+      <c r="M29" s="4">
         <v>7</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>3</v>
       </c>
-      <c r="N29" s="5">
+      <c r="O29" s="5">
         <v>4</v>
       </c>
-      <c r="O29" s="4">
-        <v>2</v>
-      </c>
-      <c r="P29">
+      <c r="P29" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q29">
         <v>4</v>
       </c>
-      <c r="Q29" s="5">
+      <c r="R29" s="5">
         <v>6</v>
       </c>
-      <c r="AB29" s="6"/>
-      <c r="AD29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30">
+      <c r="AC29" s="6"/>
+      <c r="AE29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H30" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I30" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30" s="4">
+      <c r="M30" s="4">
         <v>15</v>
       </c>
-      <c r="M30">
-        <v>3</v>
-      </c>
-      <c r="N30" s="5">
-        <v>4</v>
-      </c>
-      <c r="O30" s="4">
-        <v>11</v>
-      </c>
-      <c r="P30">
-        <v>9</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>14</v>
-      </c>
-      <c r="R30" s="4">
-        <v>14</v>
-      </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
-      <c r="T30" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="6"/>
-      <c r="AD30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30">
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30" s="5">
+        <v>7</v>
+      </c>
+      <c r="P30" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+      <c r="R30" s="5">
+        <v>1</v>
+      </c>
+      <c r="S30" s="4">
+        <v>31</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="7"/>
+      <c r="AE30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E31" t="s">
         <v>37</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H31" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31" s="4">
-        <v>7</v>
-      </c>
-      <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31" s="5">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4">
+        <v>2</v>
+      </c>
+      <c r="N31">
         <v>6</v>
       </c>
-      <c r="O31" s="4">
-        <v>14</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="6"/>
-      <c r="AD31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30">
+      <c r="O31" s="5">
+        <v>8</v>
+      </c>
+      <c r="AC31" s="6"/>
+      <c r="AE31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
         <v>44</v>
@@ -3528,10 +3450,10 @@
         <v>33</v>
       </c>
       <c r="H32" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I32" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3539,50 +3461,50 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" s="4">
-        <v>15</v>
-      </c>
-      <c r="M32">
-        <v>5</v>
-      </c>
-      <c r="N32" s="5">
+      <c r="M32" s="4">
+        <v>19</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5">
+        <v>1</v>
+      </c>
+      <c r="P32" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q32">
+        <v>4</v>
+      </c>
+      <c r="R32" s="5">
         <v>7</v>
       </c>
-      <c r="O32" s="4">
-        <v>30</v>
-      </c>
-      <c r="P32">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="5">
-        <v>1</v>
-      </c>
-      <c r="R32" s="4">
-        <v>31</v>
-      </c>
-      <c r="S32">
-        <v>1</v>
-      </c>
-      <c r="T32" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="7"/>
-      <c r="AD32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30">
+      <c r="S32" s="4">
+        <v>14</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="7"/>
+      <c r="AE32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
         <v>37</v>
@@ -3591,106 +3513,115 @@
         <v>33</v>
       </c>
       <c r="H33" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I33" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4">
-        <v>2</v>
-      </c>
-      <c r="M33">
-        <v>6</v>
-      </c>
-      <c r="N33" s="5">
-        <v>8</v>
-      </c>
-      <c r="AB33" s="6"/>
-      <c r="AD33" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
+        <v>32</v>
+      </c>
+      <c r="N33">
+        <v>30</v>
+      </c>
+      <c r="O33" s="5">
+        <v>30</v>
+      </c>
+      <c r="P33" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q33">
+        <v>3</v>
+      </c>
+      <c r="R33" s="5">
+        <v>5</v>
+      </c>
+      <c r="S33" s="4">
+        <v>21</v>
+      </c>
+      <c r="T33">
+        <v>2</v>
+      </c>
+      <c r="U33" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="6"/>
+      <c r="AE33" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:30">
+    <row r="34" spans="1:31">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34" s="4">
-        <v>19</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" s="5">
-        <v>1</v>
-      </c>
-      <c r="O34" s="4">
-        <v>11</v>
-      </c>
-      <c r="P34">
+      <c r="M34" s="4">
+        <v>33</v>
+      </c>
+      <c r="N34">
+        <v>50</v>
+      </c>
+      <c r="O34" s="5">
+        <v>70</v>
+      </c>
+      <c r="P34" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34" s="5">
         <v>4</v>
       </c>
-      <c r="Q34" s="5">
-        <v>7</v>
-      </c>
-      <c r="R34" s="4">
-        <v>14</v>
-      </c>
-      <c r="S34">
-        <v>1</v>
-      </c>
-      <c r="T34" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="7"/>
-      <c r="AD34" t="s">
+      <c r="AC34" s="7"/>
+      <c r="AE34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:30">
+    <row r="35" spans="1:31">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
         <v>37</v>
@@ -3699,10 +3630,10 @@
         <v>33</v>
       </c>
       <c r="H35" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I35" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3710,47 +3641,38 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35" s="4">
-        <v>32</v>
-      </c>
-      <c r="M35">
+      <c r="M35" s="4">
+        <v>33</v>
+      </c>
+      <c r="N35">
+        <v>20</v>
+      </c>
+      <c r="O35" s="5">
         <v>30</v>
       </c>
-      <c r="N35" s="5">
-        <v>30</v>
-      </c>
-      <c r="O35" s="4">
-        <v>2</v>
-      </c>
-      <c r="P35">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="5">
-        <v>5</v>
-      </c>
-      <c r="R35" s="4">
-        <v>21</v>
-      </c>
-      <c r="S35">
-        <v>2</v>
-      </c>
-      <c r="T35" s="5">
-        <v>3</v>
-      </c>
-      <c r="AB35" s="6"/>
-      <c r="AD35" t="s">
+      <c r="P35" s="4">
+        <v>35</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="R35" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="7"/>
+      <c r="AE35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:30">
+    <row r="36" spans="1:31">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>48</v>
@@ -3762,106 +3684,77 @@
         <v>33</v>
       </c>
       <c r="H36" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I36" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36" s="4">
-        <v>33</v>
-      </c>
-      <c r="M36">
-        <v>50</v>
-      </c>
-      <c r="N36" s="5">
-        <v>70</v>
-      </c>
-      <c r="O36" s="4">
-        <v>2</v>
-      </c>
-      <c r="P36">
-        <v>2</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>4</v>
-      </c>
-      <c r="AB36" s="7"/>
-      <c r="AD36" t="s">
+      <c r="AE36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:30">
+    <row r="37" spans="1:31">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
       </c>
       <c r="H37" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I37" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="L37" s="4">
-        <v>33</v>
-      </c>
-      <c r="M37">
-        <v>20</v>
-      </c>
-      <c r="N37" s="5">
-        <v>30</v>
-      </c>
-      <c r="O37" s="4">
-        <v>35</v>
-      </c>
-      <c r="P37">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="7"/>
-      <c r="AD37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30">
+      <c r="M37" s="4">
+        <v>11</v>
+      </c>
+      <c r="N37">
+        <v>42</v>
+      </c>
+      <c r="O37" s="5">
+        <v>54</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
         <v>37</v>
@@ -3870,33 +3763,51 @@
         <v>33</v>
       </c>
       <c r="H38" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I38" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4">
+        <v>37</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5">
+        <v>2</v>
+      </c>
+      <c r="P38" s="4">
+        <v>15</v>
+      </c>
+      <c r="Q38">
+        <v>3</v>
+      </c>
+      <c r="R38" s="5">
+        <v>4</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E39" t="s">
         <v>32</v>
@@ -3905,42 +3816,42 @@
         <v>33</v>
       </c>
       <c r="H39" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I39" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4">
         <v>11</v>
       </c>
-      <c r="M39">
-        <v>42</v>
-      </c>
-      <c r="N39" s="5">
-        <v>54</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30">
+      <c r="N39">
+        <v>18</v>
+      </c>
+      <c r="O39" s="5">
+        <v>22</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
-        <v>115</v>
+      <c r="B40">
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
         <v>37</v>
@@ -3955,48 +3866,48 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="4">
-        <v>37</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40" s="5">
-        <v>2</v>
-      </c>
-      <c r="O40" s="4">
+      <c r="M40" s="4">
         <v>15</v>
       </c>
-      <c r="P40">
+      <c r="N40">
         <v>3</v>
       </c>
-      <c r="Q40" s="5">
+      <c r="O40" s="5">
         <v>4</v>
       </c>
-      <c r="AD40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30">
+      <c r="P40" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q40">
+        <v>6</v>
+      </c>
+      <c r="R40" s="5">
+        <v>8</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F41" t="s">
         <v>33</v>
@@ -4013,87 +3924,93 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="L41" s="4">
-        <v>11</v>
-      </c>
-      <c r="M41">
-        <v>18</v>
-      </c>
-      <c r="N41" s="5">
-        <v>22</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30">
+      <c r="M41" s="4">
+        <v>7</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="O41" s="5">
+        <v>4</v>
+      </c>
+      <c r="P41" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q41">
+        <v>6</v>
+      </c>
+      <c r="R41" s="5">
+        <v>8</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
         <v>37</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G42">
+        <v>33</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>21</v>
+      </c>
+      <c r="N42">
+        <v>4</v>
+      </c>
+      <c r="O42" s="5">
+        <v>5</v>
+      </c>
+      <c r="P42" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q42">
         <v>3</v>
       </c>
-      <c r="H42" s="4">
-        <v>2</v>
-      </c>
-      <c r="I42" s="5">
-        <v>2</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4">
-        <v>7</v>
-      </c>
-      <c r="M42">
-        <v>6</v>
-      </c>
-      <c r="N42" s="5">
-        <v>8</v>
-      </c>
-      <c r="O42" s="4">
-        <v>2</v>
-      </c>
-      <c r="P42">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>4</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30">
+      <c r="R42" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>144</v>
+      <c r="B43" t="s">
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
         <v>37</v>
@@ -4102,51 +4019,51 @@
         <v>33</v>
       </c>
       <c r="H43" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4">
-        <v>15</v>
-      </c>
-      <c r="M43">
-        <v>3</v>
-      </c>
-      <c r="N43" s="5">
-        <v>4</v>
-      </c>
-      <c r="O43" s="4">
-        <v>2</v>
-      </c>
-      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <v>5</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" s="5">
+        <v>2</v>
+      </c>
+      <c r="P43" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q43">
         <v>6</v>
       </c>
-      <c r="Q43" s="5">
-        <v>8</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30">
+      <c r="R43" s="5">
+        <v>7</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
         <v>37</v>
@@ -4155,7 +4072,7 @@
         <v>33</v>
       </c>
       <c r="H44" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="5">
         <v>3</v>
@@ -4164,42 +4081,42 @@
         <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4">
         <v>7</v>
       </c>
-      <c r="M44">
-        <v>3</v>
-      </c>
-      <c r="N44" s="5">
+      <c r="N44">
         <v>4</v>
       </c>
-      <c r="O44" s="4">
-        <v>2</v>
-      </c>
-      <c r="P44">
-        <v>6</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>8</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30">
+      <c r="O44" s="5">
+        <v>5</v>
+      </c>
+      <c r="P44" s="4">
+        <v>38</v>
+      </c>
+      <c r="Q44">
+        <v>4</v>
+      </c>
+      <c r="R44" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
         <v>37</v>
@@ -4208,51 +4125,51 @@
         <v>33</v>
       </c>
       <c r="H45" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="L45" s="4">
-        <v>21</v>
-      </c>
-      <c r="M45">
-        <v>4</v>
-      </c>
-      <c r="N45" s="5">
-        <v>5</v>
-      </c>
-      <c r="O45" s="4">
-        <v>2</v>
-      </c>
-      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4">
+        <v>6</v>
+      </c>
+      <c r="N45">
         <v>3</v>
       </c>
-      <c r="Q45" s="5">
-        <v>5</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30">
+      <c r="O45" s="5">
+        <v>3</v>
+      </c>
+      <c r="P45" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q45">
+        <v>2</v>
+      </c>
+      <c r="R45" s="5">
+        <v>3</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E46" t="s">
         <v>37</v>
@@ -4261,10 +4178,10 @@
         <v>33</v>
       </c>
       <c r="H46" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -4272,143 +4189,152 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="L46" s="4">
-        <v>5</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46" s="5">
-        <v>2</v>
-      </c>
-      <c r="O46" s="4">
-        <v>2</v>
-      </c>
-      <c r="P46">
-        <v>6</v>
-      </c>
-      <c r="Q46" s="5">
+      <c r="M46" s="4">
         <v>7</v>
       </c>
-      <c r="AD46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30">
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5">
+        <v>3</v>
+      </c>
+      <c r="P46" s="4">
+        <v>41</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
         <v>33</v>
       </c>
       <c r="H47" s="4">
+        <v>7</v>
+      </c>
+      <c r="I47" s="5">
         <v>4</v>
       </c>
-      <c r="I47" s="5">
-        <v>3</v>
-      </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>1</v>
       </c>
-      <c r="L47" s="4">
-        <v>7</v>
-      </c>
-      <c r="M47">
-        <v>4</v>
-      </c>
-      <c r="N47" s="5">
+      <c r="M47" s="4">
+        <v>6</v>
+      </c>
+      <c r="N47">
         <v>5</v>
       </c>
-      <c r="O47" s="4">
-        <v>38</v>
-      </c>
-      <c r="P47">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="5">
+      <c r="O47" s="5">
         <v>5</v>
       </c>
-      <c r="AD47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:30">
+      <c r="P47" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47" s="5">
+        <v>1</v>
+      </c>
+      <c r="S47" s="4">
+        <v>18</v>
+      </c>
+      <c r="T47">
+        <v>0.9</v>
+      </c>
+      <c r="U47" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
         <v>33</v>
       </c>
       <c r="H48" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I48" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4">
-        <v>6</v>
-      </c>
-      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="M48" s="4">
+        <v>15</v>
+      </c>
+      <c r="N48">
+        <v>2</v>
+      </c>
+      <c r="O48" s="5">
+        <v>2</v>
+      </c>
+      <c r="P48" s="4">
+        <v>42</v>
+      </c>
+      <c r="Q48">
         <v>3</v>
       </c>
-      <c r="N48" s="5">
-        <v>3</v>
-      </c>
-      <c r="O48" s="4">
-        <v>39</v>
-      </c>
-      <c r="P48">
-        <v>2</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>3</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:30">
+      <c r="R48" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D49" t="s">
         <v>48</v>
@@ -4420,113 +4346,122 @@
         <v>33</v>
       </c>
       <c r="H49" s="4">
+        <v>5</v>
+      </c>
+      <c r="I49" s="5">
         <v>4</v>
       </c>
-      <c r="I49" s="5">
-        <v>3</v>
-      </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>1</v>
       </c>
-      <c r="L49" s="4">
+      <c r="M49" s="4">
         <v>7</v>
       </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49" s="5">
-        <v>3</v>
-      </c>
-      <c r="O49" s="4">
-        <v>41</v>
-      </c>
-      <c r="P49">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30">
+      <c r="N49">
+        <v>7</v>
+      </c>
+      <c r="O49" s="5">
+        <v>9</v>
+      </c>
+      <c r="P49" s="4">
+        <v>26</v>
+      </c>
+      <c r="Q49">
+        <v>2</v>
+      </c>
+      <c r="R49" s="5">
+        <v>2</v>
+      </c>
+      <c r="S49" s="4">
+        <v>2</v>
+      </c>
+      <c r="T49">
+        <v>7</v>
+      </c>
+      <c r="U49" s="5">
+        <v>8</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F50" t="s">
         <v>33</v>
       </c>
       <c r="H50" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I50" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="L50" s="4">
-        <v>6</v>
-      </c>
-      <c r="M50">
-        <v>5</v>
-      </c>
-      <c r="N50" s="5">
-        <v>5</v>
-      </c>
-      <c r="O50" s="4">
-        <v>14</v>
-      </c>
-      <c r="P50">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>1</v>
-      </c>
-      <c r="R50" s="4">
-        <v>18</v>
-      </c>
-      <c r="S50">
-        <v>0.9</v>
-      </c>
-      <c r="T50" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="AD50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30">
+      <c r="M50" s="4">
+        <v>32</v>
+      </c>
+      <c r="N50">
+        <v>40</v>
+      </c>
+      <c r="O50" s="5">
+        <v>40</v>
+      </c>
+      <c r="P50" s="4">
+        <v>33</v>
+      </c>
+      <c r="Q50">
+        <v>30</v>
+      </c>
+      <c r="R50" s="5">
+        <v>30</v>
+      </c>
+      <c r="S50" s="4">
+        <v>19</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
@@ -4535,172 +4470,142 @@
         <v>33</v>
       </c>
       <c r="H51" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I51" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51" s="4">
-        <v>15</v>
-      </c>
-      <c r="M51">
-        <v>2</v>
-      </c>
-      <c r="N51" s="5">
-        <v>2</v>
-      </c>
-      <c r="O51" s="4">
-        <v>42</v>
-      </c>
-      <c r="P51">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="5">
-        <v>5</v>
-      </c>
-      <c r="AD51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4">
+        <v>11</v>
+      </c>
+      <c r="N51">
+        <v>10</v>
+      </c>
+      <c r="O51" s="5">
+        <v>14</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31">
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
-        <v>138</v>
-      </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
         <v>33</v>
       </c>
       <c r="H52" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I52" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4">
-        <v>7</v>
-      </c>
-      <c r="M52">
-        <v>7</v>
-      </c>
-      <c r="N52" s="5">
-        <v>9</v>
-      </c>
-      <c r="O52" s="4">
-        <v>26</v>
-      </c>
-      <c r="P52">
-        <v>2</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>2</v>
-      </c>
-      <c r="R52" s="4">
-        <v>2</v>
-      </c>
-      <c r="S52">
-        <v>7</v>
-      </c>
-      <c r="T52" s="5">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4">
+        <v>11</v>
+      </c>
+      <c r="N52">
         <v>8</v>
       </c>
-      <c r="AD52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30">
+      <c r="O52" s="5">
+        <v>11</v>
+      </c>
+      <c r="P52" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q52">
+        <v>3</v>
+      </c>
+      <c r="R52" s="5">
+        <v>3</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F53" t="s">
         <v>33</v>
       </c>
       <c r="H53" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I53" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4">
-        <v>32</v>
-      </c>
-      <c r="M53">
-        <v>40</v>
-      </c>
-      <c r="N53" s="5">
-        <v>40</v>
-      </c>
-      <c r="O53" s="4">
-        <v>33</v>
-      </c>
-      <c r="P53">
-        <v>30</v>
-      </c>
-      <c r="Q53" s="5">
-        <v>30</v>
-      </c>
-      <c r="R53" s="4">
-        <v>19</v>
-      </c>
-      <c r="S53">
-        <v>1</v>
-      </c>
-      <c r="T53" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4">
+        <v>11</v>
+      </c>
+      <c r="N53">
+        <v>7</v>
+      </c>
+      <c r="O53" s="5">
+        <v>11</v>
+      </c>
+      <c r="P53" s="4">
+        <v>45</v>
+      </c>
+      <c r="Q53">
+        <v>2</v>
+      </c>
+      <c r="R53" s="5">
+        <v>3</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>44</v>
@@ -4709,160 +4614,157 @@
         <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H54" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I54" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="L54" s="4">
-        <v>11</v>
-      </c>
-      <c r="M54">
+      <c r="M54" s="4">
+        <v>6</v>
+      </c>
+      <c r="N54">
         <v>5</v>
       </c>
-      <c r="N54" s="5">
-        <v>5</v>
-      </c>
-      <c r="O54" s="4">
-        <v>11</v>
-      </c>
-      <c r="P54">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>5</v>
-      </c>
-      <c r="R54" s="4">
-        <v>19</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-      <c r="T54" s="5">
-        <v>2</v>
-      </c>
-      <c r="AD54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30">
+      <c r="O54" s="5">
+        <v>7</v>
+      </c>
+      <c r="P54" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q54">
+        <v>1.1</v>
+      </c>
+      <c r="R54" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
         <v>33</v>
       </c>
       <c r="H55" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I55" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4">
-        <v>11</v>
-      </c>
-      <c r="M55">
-        <v>10</v>
-      </c>
-      <c r="N55" s="5">
-        <v>14</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30">
+        <v>1</v>
+      </c>
+      <c r="M55" s="4">
+        <v>6</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55" s="5">
+        <v>3</v>
+      </c>
+      <c r="P55" s="4">
+        <v>49</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56">
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>143</v>
+      </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
         <v>33</v>
       </c>
       <c r="H56" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I56" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4">
-        <v>11</v>
-      </c>
-      <c r="M56">
-        <v>8</v>
-      </c>
-      <c r="N56" s="5">
-        <v>11</v>
-      </c>
-      <c r="O56" s="4">
-        <v>6</v>
-      </c>
-      <c r="P56">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>3</v>
-      </c>
-      <c r="AD56" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30">
+        <v>1</v>
+      </c>
+      <c r="M56" s="4">
+        <v>9</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
+      <c r="O56" s="5">
+        <v>2</v>
+      </c>
+      <c r="P56" s="4">
+        <v>21</v>
+      </c>
+      <c r="Q56">
+        <v>2</v>
+      </c>
+      <c r="R56" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E57" t="s">
         <v>32</v>
@@ -4871,229 +4773,38 @@
         <v>33</v>
       </c>
       <c r="H57" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I57" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4">
-        <v>11</v>
-      </c>
-      <c r="M57">
-        <v>7</v>
-      </c>
-      <c r="N57" s="5">
-        <v>11</v>
-      </c>
-      <c r="O57" s="4">
-        <v>45</v>
-      </c>
-      <c r="P57">
-        <v>2</v>
-      </c>
-      <c r="Q57" s="5">
-        <v>3</v>
-      </c>
-      <c r="AD57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:30">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" t="s">
-        <v>150</v>
-      </c>
-      <c r="D58" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" t="s">
-        <v>32</v>
-      </c>
-      <c r="F58" t="s">
-        <v>33</v>
-      </c>
-      <c r="H58" s="4">
-        <v>5</v>
-      </c>
-      <c r="I58" s="5">
-        <v>4</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58" s="4">
-        <v>6</v>
-      </c>
-      <c r="M58">
-        <v>5</v>
-      </c>
-      <c r="N58" s="5">
-        <v>7</v>
-      </c>
-      <c r="O58" s="4">
-        <v>18</v>
-      </c>
-      <c r="P58">
-        <v>1.1</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="AD58" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59" t="s">
-        <v>151</v>
-      </c>
-      <c r="C59" t="s">
-        <v>152</v>
-      </c>
-      <c r="D59" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" t="s">
-        <v>37</v>
-      </c>
-      <c r="F59" t="s">
-        <v>33</v>
-      </c>
-      <c r="H59" s="4">
-        <v>9</v>
-      </c>
-      <c r="I59" s="5">
-        <v>6</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
-      <c r="L59" s="4">
-        <v>6</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-      <c r="N59" s="5">
-        <v>3</v>
-      </c>
-      <c r="O59" s="4">
-        <v>49</v>
-      </c>
-      <c r="P59">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD59" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60" t="s">
-        <v>153</v>
-      </c>
-      <c r="C60" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" t="s">
-        <v>37</v>
-      </c>
-      <c r="F60" t="s">
-        <v>33</v>
-      </c>
-      <c r="H60" s="4">
-        <v>1</v>
-      </c>
-      <c r="I60" s="5">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60" s="4">
-        <v>9</v>
-      </c>
-      <c r="M60">
-        <v>2</v>
-      </c>
-      <c r="N60" s="5">
-        <v>2</v>
-      </c>
-      <c r="O60" s="4">
-        <v>21</v>
-      </c>
-      <c r="P60">
-        <v>2</v>
-      </c>
-      <c r="Q60" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" t="s">
-        <v>44</v>
-      </c>
-      <c r="E61" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" t="s">
-        <v>33</v>
-      </c>
-      <c r="H61" s="4">
-        <v>3</v>
-      </c>
-      <c r="I61" s="5">
-        <v>3</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M57" s="4">
+        <v>52</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="P57" s="4">
+        <v>53</v>
+      </c>
+      <c r="Q57">
+        <v>0.5</v>
+      </c>
+      <c r="R57" s="5">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AD62" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5105,7 +4816,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5133,19 +4844,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="G1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5153,13 +4864,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5171,19 +4882,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5194,16 +4905,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5214,16 +4925,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5234,13 +4945,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5251,16 +4962,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5271,13 +4982,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5291,13 +5002,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5311,13 +5022,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5331,13 +5042,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5348,16 +5059,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5368,16 +5079,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5388,19 +5099,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5411,16 +5122,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E15" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5431,16 +5142,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5451,13 +5162,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5471,16 +5182,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5491,13 +5202,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5511,13 +5222,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5531,16 +5242,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5551,16 +5262,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E22" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5571,13 +5282,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5591,19 +5302,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5614,13 +5325,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5634,16 +5345,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C26" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5657,16 +5368,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C27" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D27" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E27" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5677,13 +5388,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5697,19 +5408,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5723,13 +5434,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5743,19 +5454,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E31" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F31" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5766,19 +5477,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C32" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5789,19 +5500,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5812,16 +5523,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5832,16 +5543,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5852,19 +5563,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F36" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5878,13 +5589,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5898,16 +5609,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C38" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5918,13 +5629,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5941,16 +5652,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C40" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5961,13 +5672,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5984,19 +5695,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C42" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6010,13 +5721,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6030,13 +5741,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6050,19 +5761,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E45" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F45" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6073,16 +5784,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D46" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E46" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6093,13 +5804,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C47" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D47" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6113,19 +5824,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6136,13 +5847,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6156,19 +5867,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C50" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6179,13 +5890,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C51" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6199,19 +5910,96 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C52" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E52">
         <v>3</v>
       </c>
       <c r="I52">
         <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" t="s">
+        <v>236</v>
+      </c>
+      <c r="D53" t="s">
+        <v>231</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:9">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" t="s">
+        <v>237</v>
+      </c>
+      <c r="D54" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:9">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>6</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -6247,13 +6035,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -6279,10 +6067,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6308,10 +6096,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6331,10 +6119,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6354,10 +6142,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6377,10 +6165,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6400,10 +6188,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6423,10 +6211,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6446,10 +6234,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6469,10 +6257,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6492,10 +6280,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6521,10 +6309,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6550,10 +6338,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6573,10 +6361,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6596,10 +6384,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6619,10 +6407,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6642,10 +6430,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6665,10 +6453,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" t="s">
         <v>244</v>
-      </c>
-      <c r="C18" t="s">
-        <v>250</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6688,10 +6476,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6705,10 +6493,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6727,8 +6515,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
     <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
@@ -6750,16 +6538,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6767,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6787,13 +6575,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>
@@ -6804,13 +6592,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -6821,13 +6609,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6841,13 +6629,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6861,19 +6649,39 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -68,6 +68,9 @@
     <t>NotRepeatable</t>
   </si>
   <si>
+    <t>Condition</t>
+  </si>
+  <si>
     <t>Effect1</t>
   </si>
   <si>
@@ -744,15 +747,6 @@
   </si>
   <si>
     <t>减少X%的红温</t>
-  </si>
-  <si>
-    <t>当红温&gt;10层时，获得红温X%的参数</t>
-  </si>
-  <si>
-    <t>当红温&gt;10层时，减少X%的红温</t>
-  </si>
-  <si>
-    <t>同接增加X%</t>
   </si>
   <si>
     <t>BuffType</t>
@@ -1810,7 +1804,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AE56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -1876,59 +1870,62 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -1936,19 +1933,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="4">
         <v>4</v>
@@ -1973,7 +1970,7 @@
       </c>
       <c r="AC2" s="6"/>
       <c r="AE2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -1981,19 +1978,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -2018,7 +2015,7 @@
       </c>
       <c r="AC3" s="6"/>
       <c r="AE3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -2026,19 +2023,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="4">
         <v>5</v>
@@ -2063,7 +2060,7 @@
       </c>
       <c r="AC4" s="6"/>
       <c r="AE4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -2071,19 +2068,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" s="4">
         <v>3</v>
@@ -2117,7 +2114,7 @@
       </c>
       <c r="AC5" s="6"/>
       <c r="AE5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -2125,19 +2122,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2159,7 +2156,7 @@
       </c>
       <c r="AC6" s="6"/>
       <c r="AE6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -2167,19 +2164,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="4">
         <v>5</v>
@@ -2198,7 +2195,7 @@
       </c>
       <c r="AC7" s="6"/>
       <c r="AE7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -2206,19 +2203,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2264,7 +2261,7 @@
       </c>
       <c r="AC8" s="6"/>
       <c r="AE8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -2272,19 +2269,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -2318,7 +2315,7 @@
       </c>
       <c r="AC9" s="6"/>
       <c r="AE9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -2326,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -2372,7 +2369,7 @@
       </c>
       <c r="AC10" s="6"/>
       <c r="AE10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -2380,19 +2377,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -2426,7 +2423,7 @@
       </c>
       <c r="AC11" s="6"/>
       <c r="AE11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -2434,19 +2431,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -2480,7 +2477,7 @@
       </c>
       <c r="AC12" s="6"/>
       <c r="AE12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -2488,19 +2485,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13" s="4">
         <v>6</v>
@@ -2534,10 +2531,10 @@
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -2545,19 +2542,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" s="4">
         <v>5</v>
@@ -2591,7 +2588,7 @@
       </c>
       <c r="AC14" s="6"/>
       <c r="AE14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -2599,19 +2596,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="4">
         <v>5</v>
@@ -2636,7 +2633,7 @@
       </c>
       <c r="AC15" s="6"/>
       <c r="AE15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -2644,19 +2641,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="4">
         <v>4</v>
@@ -2681,7 +2678,7 @@
       </c>
       <c r="AC16" s="6"/>
       <c r="AE16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -2689,19 +2686,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="4">
         <v>6</v>
@@ -2735,7 +2732,7 @@
       </c>
       <c r="AC17" s="6"/>
       <c r="AE17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -2743,19 +2740,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="4">
         <v>3</v>
@@ -2798,7 +2795,7 @@
       </c>
       <c r="AC18" s="7"/>
       <c r="AE18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -2806,19 +2803,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="4">
         <v>6</v>
@@ -2837,7 +2834,7 @@
       </c>
       <c r="AC19" s="6"/>
       <c r="AE19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -2845,19 +2842,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H20" s="4">
         <v>4</v>
@@ -2882,7 +2879,7 @@
       </c>
       <c r="AC20" s="6"/>
       <c r="AE20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -2890,19 +2887,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="4">
         <v>5</v>
@@ -2936,7 +2933,7 @@
       </c>
       <c r="AC21" s="6"/>
       <c r="AE21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -2944,19 +2941,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H22" s="4">
         <v>6</v>
@@ -2981,21 +2978,70 @@
       </c>
       <c r="AC22" s="7"/>
       <c r="AE22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:31">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="4">
+        <v>5</v>
+      </c>
+      <c r="I23" s="5">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4">
+        <v>26</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" s="5">
+        <v>2</v>
+      </c>
+      <c r="P23" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q23">
+        <v>30</v>
+      </c>
+      <c r="R23" s="5">
+        <v>42</v>
+      </c>
+      <c r="S23" s="4">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>5</v>
+      </c>
+      <c r="U23" s="5">
+        <v>7</v>
+      </c>
       <c r="AC23" s="6"/>
       <c r="AE23" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:31">
@@ -3003,62 +3049,53 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H24" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24" s="5">
         <v>4</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>1</v>
       </c>
       <c r="M24" s="4">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>2</v>
       </c>
       <c r="O24" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P24" s="4">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="Q24">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R24" s="5">
-        <v>42</v>
-      </c>
-      <c r="S24" s="4">
-        <v>2</v>
-      </c>
-      <c r="T24">
-        <v>5</v>
-      </c>
-      <c r="U24" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC24" s="6"/>
       <c r="AE24" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:31">
@@ -3066,43 +3103,43 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H25" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="4">
         <v>6</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O25" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P25" s="4">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <v>1</v>
@@ -3112,7 +3149,7 @@
       </c>
       <c r="AC25" s="6"/>
       <c r="AE25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:31">
@@ -3120,53 +3157,53 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H26" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="M26" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O26" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R26" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC26" s="6"/>
       <c r="AE26" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:31">
@@ -3174,25 +3211,25 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3201,26 +3238,17 @@
         <v>0</v>
       </c>
       <c r="M27" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>3</v>
       </c>
       <c r="O27" s="5">
-        <v>4</v>
-      </c>
-      <c r="P27" s="4">
-        <v>11</v>
-      </c>
-      <c r="Q27">
-        <v>8</v>
-      </c>
-      <c r="R27" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC27" s="6"/>
       <c r="AE27" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:31">
@@ -3228,19 +3256,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H28" s="4">
         <v>3</v>
@@ -3261,11 +3289,20 @@
         <v>3</v>
       </c>
       <c r="O28" s="5">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="P28" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28" s="5">
+        <v>6</v>
       </c>
       <c r="AC28" s="6"/>
       <c r="AE28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:31">
@@ -3273,53 +3310,62 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="4">
+        <v>10</v>
+      </c>
+      <c r="I29" s="5">
+        <v>8</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="M29" s="4">
+        <v>15</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29" s="5">
+        <v>7</v>
+      </c>
+      <c r="P29" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="5">
+        <v>1</v>
+      </c>
+      <c r="S29" s="4">
         <v>31</v>
       </c>
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="4">
-        <v>3</v>
-      </c>
-      <c r="I29" s="5">
-        <v>2</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4">
-        <v>7</v>
-      </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29" s="5">
-        <v>4</v>
-      </c>
-      <c r="P29" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q29">
-        <v>4</v>
-      </c>
-      <c r="R29" s="5">
-        <v>6</v>
-      </c>
-      <c r="AC29" s="6"/>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="7"/>
       <c r="AE29" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:31">
@@ -3327,62 +3373,44 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>6</v>
+      </c>
+      <c r="O30" s="5">
         <v>8</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="M30" s="4">
-        <v>15</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30" s="5">
-        <v>7</v>
-      </c>
-      <c r="P30" s="4">
-        <v>30</v>
-      </c>
-      <c r="Q30">
-        <v>1</v>
-      </c>
-      <c r="R30" s="5">
-        <v>1</v>
-      </c>
-      <c r="S30" s="4">
-        <v>31</v>
-      </c>
-      <c r="T30">
-        <v>1</v>
-      </c>
-      <c r="U30" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="7"/>
+      <c r="AC30" s="6"/>
       <c r="AE30" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:31">
@@ -3390,44 +3418,62 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H31" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I31" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O31" s="5">
-        <v>8</v>
-      </c>
-      <c r="AC31" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="P31" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q31">
+        <v>4</v>
+      </c>
+      <c r="R31" s="5">
+        <v>7</v>
+      </c>
+      <c r="S31" s="4">
+        <v>14</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="7"/>
       <c r="AE31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:31">
@@ -3435,22 +3481,22 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H32" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" s="5">
         <v>5</v>
@@ -3462,35 +3508,35 @@
         <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O32" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="P32" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R32" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S32" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="AC32" s="6"/>
       <c r="AE32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:31">
@@ -3498,62 +3544,53 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="4">
+        <v>4</v>
+      </c>
+      <c r="I33" s="5">
+        <v>4</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
         <v>33</v>
       </c>
-      <c r="H33" s="4">
-        <v>5</v>
-      </c>
-      <c r="I33" s="5">
-        <v>5</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="M33" s="4">
-        <v>32</v>
-      </c>
       <c r="N33">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O33" s="5">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P33" s="4">
         <v>2</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R33" s="5">
-        <v>5</v>
-      </c>
-      <c r="S33" s="4">
-        <v>21</v>
-      </c>
-      <c r="T33">
-        <v>2</v>
-      </c>
-      <c r="U33" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC33" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="AC33" s="7"/>
       <c r="AE33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:31">
@@ -3561,28 +3598,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H34" s="4">
         <v>4</v>
       </c>
       <c r="I34" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3591,23 +3628,23 @@
         <v>33</v>
       </c>
       <c r="N34">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O34" s="5">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="P34" s="4">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC34" s="7"/>
       <c r="AE34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:31">
@@ -3615,25 +3652,25 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H35" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I35" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3641,27 +3678,8 @@
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="M35" s="4">
-        <v>33</v>
-      </c>
-      <c r="N35">
-        <v>20</v>
-      </c>
-      <c r="O35" s="5">
-        <v>30</v>
-      </c>
-      <c r="P35" s="4">
+      <c r="AE35" t="s">
         <v>35</v>
-      </c>
-      <c r="Q35">
-        <v>1</v>
-      </c>
-      <c r="R35" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="7"/>
-      <c r="AE35" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:31">
@@ -3669,34 +3687,43 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H36" s="4">
+        <v>8</v>
+      </c>
+      <c r="I36" s="5">
         <v>7</v>
       </c>
-      <c r="I36" s="5">
-        <v>6</v>
-      </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
+      <c r="M36" s="4">
+        <v>11</v>
+      </c>
+      <c r="N36">
+        <v>42</v>
+      </c>
+      <c r="O36" s="5">
+        <v>54</v>
+      </c>
       <c r="AE36" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:31">
@@ -3704,43 +3731,52 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H37" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I37" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="4">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="N37">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="O37" s="5">
-        <v>54</v>
+        <v>2</v>
+      </c>
+      <c r="P37" s="4">
+        <v>15</v>
+      </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
+      <c r="R37" s="5">
+        <v>4</v>
       </c>
       <c r="AE37" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:31">
@@ -3748,19 +3784,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H38" s="4">
         <v>3</v>
@@ -3769,51 +3805,42 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="M38" s="4">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O38" s="5">
-        <v>2</v>
-      </c>
-      <c r="P38" s="4">
-        <v>15</v>
-      </c>
-      <c r="Q38">
-        <v>3</v>
-      </c>
-      <c r="R38" s="5">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AE38" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:31">
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
-        <v>111</v>
+      <c r="B39">
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H39" s="4">
         <v>3</v>
@@ -3828,36 +3855,45 @@
         <v>0</v>
       </c>
       <c r="M39" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N39">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O39" s="5">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="P39" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q39">
+        <v>6</v>
+      </c>
+      <c r="R39" s="5">
+        <v>8</v>
       </c>
       <c r="AE39" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:31">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40">
-        <v>144</v>
+      <c r="B40" t="s">
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H40" s="4">
         <v>3</v>
@@ -3872,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>3</v>
@@ -3890,7 +3926,7 @@
         <v>8</v>
       </c>
       <c r="AE40" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:31">
@@ -3898,52 +3934,52 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H41" s="4">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4">
+        <v>21</v>
+      </c>
+      <c r="N41">
+        <v>4</v>
+      </c>
+      <c r="O41" s="5">
+        <v>5</v>
+      </c>
+      <c r="P41" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q41">
         <v>3</v>
       </c>
-      <c r="I41" s="5">
-        <v>3</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4">
-        <v>7</v>
-      </c>
-      <c r="N41">
-        <v>3</v>
-      </c>
-      <c r="O41" s="5">
-        <v>4</v>
-      </c>
-      <c r="P41" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q41">
-        <v>6</v>
-      </c>
       <c r="R41" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:31">
@@ -3951,19 +3987,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
@@ -3978,25 +4014,25 @@
         <v>1</v>
       </c>
       <c r="M42" s="4">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O42" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P42" s="4">
         <v>2</v>
       </c>
       <c r="Q42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R42" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:31">
@@ -4004,25 +4040,25 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H43" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -4031,25 +4067,25 @@
         <v>1</v>
       </c>
       <c r="M43" s="4">
+        <v>7</v>
+      </c>
+      <c r="N43">
+        <v>4</v>
+      </c>
+      <c r="O43" s="5">
         <v>5</v>
       </c>
-      <c r="N43">
-        <v>1</v>
-      </c>
-      <c r="O43" s="5">
-        <v>2</v>
-      </c>
       <c r="P43" s="4">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="Q43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R43" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:31">
@@ -4057,52 +4093,52 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="4">
+        <v>2</v>
+      </c>
+      <c r="I44" s="5">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="4">
+        <v>6</v>
+      </c>
+      <c r="N44">
+        <v>3</v>
+      </c>
+      <c r="O44" s="5">
+        <v>3</v>
+      </c>
+      <c r="P44" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q44">
+        <v>2</v>
+      </c>
+      <c r="R44" s="5">
+        <v>3</v>
+      </c>
+      <c r="AE44" t="s">
         <v>33</v>
-      </c>
-      <c r="H44" s="4">
-        <v>4</v>
-      </c>
-      <c r="I44" s="5">
-        <v>3</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="M44" s="4">
-        <v>7</v>
-      </c>
-      <c r="N44">
-        <v>4</v>
-      </c>
-      <c r="O44" s="5">
-        <v>5</v>
-      </c>
-      <c r="P44" s="4">
-        <v>38</v>
-      </c>
-      <c r="Q44">
-        <v>4</v>
-      </c>
-      <c r="R44" s="5">
-        <v>5</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:31">
@@ -4110,52 +4146,52 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H45" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" s="5">
         <v>3</v>
       </c>
       <c r="P45" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:31">
@@ -4163,52 +4199,61 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="4">
+        <v>7</v>
+      </c>
+      <c r="I46" s="5">
+        <v>4</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4">
+        <v>6</v>
+      </c>
+      <c r="N46">
+        <v>5</v>
+      </c>
+      <c r="O46" s="5">
+        <v>5</v>
+      </c>
+      <c r="P46" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" s="5">
+        <v>1</v>
+      </c>
+      <c r="S46" s="4">
+        <v>18</v>
+      </c>
+      <c r="T46">
+        <v>0.9</v>
+      </c>
+      <c r="U46" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="AE46" t="s">
         <v>33</v>
-      </c>
-      <c r="H46" s="4">
-        <v>4</v>
-      </c>
-      <c r="I46" s="5">
-        <v>3</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46">
-        <v>1</v>
-      </c>
-      <c r="M46" s="4">
-        <v>7</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
-      </c>
-      <c r="O46" s="5">
-        <v>3</v>
-      </c>
-      <c r="P46" s="4">
-        <v>41</v>
-      </c>
-      <c r="Q46">
-        <v>1</v>
-      </c>
-      <c r="R46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:31">
@@ -4216,61 +4261,52 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H47" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I47" s="5">
         <v>4</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>1</v>
       </c>
       <c r="M47" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47" s="5">
+        <v>2</v>
+      </c>
+      <c r="P47" s="4">
+        <v>42</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
+      <c r="R47" s="5">
         <v>5</v>
       </c>
-      <c r="O47" s="5">
-        <v>5</v>
-      </c>
-      <c r="P47" s="4">
-        <v>14</v>
-      </c>
-      <c r="Q47">
-        <v>1</v>
-      </c>
-      <c r="R47" s="5">
-        <v>1</v>
-      </c>
-      <c r="S47" s="4">
-        <v>18</v>
-      </c>
-      <c r="T47">
-        <v>0.9</v>
-      </c>
-      <c r="U47" s="5">
-        <v>1.2</v>
-      </c>
       <c r="AE47" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:31">
@@ -4278,52 +4314,61 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H48" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" s="5">
         <v>4</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>1</v>
       </c>
       <c r="M48" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O48" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P48" s="4">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Q48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R48" s="5">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="S48" s="4">
+        <v>2</v>
+      </c>
+      <c r="T48">
+        <v>7</v>
+      </c>
+      <c r="U48" s="5">
+        <v>8</v>
       </c>
       <c r="AE48" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:31">
@@ -4331,61 +4376,61 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="4">
+        <v>10</v>
+      </c>
+      <c r="I49" s="5">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="M49" s="4">
+        <v>32</v>
+      </c>
+      <c r="N49">
+        <v>40</v>
+      </c>
+      <c r="O49" s="5">
+        <v>40</v>
+      </c>
+      <c r="P49" s="4">
         <v>33</v>
       </c>
-      <c r="H49" s="4">
-        <v>5</v>
-      </c>
-      <c r="I49" s="5">
-        <v>4</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="M49" s="4">
-        <v>7</v>
-      </c>
-      <c r="N49">
-        <v>7</v>
-      </c>
-      <c r="O49" s="5">
-        <v>9</v>
-      </c>
-      <c r="P49" s="4">
-        <v>26</v>
-      </c>
       <c r="Q49">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R49" s="5">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="S49" s="4">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="T49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U49" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AE49" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:31">
@@ -4393,87 +4438,66 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H50" s="4">
+        <v>2</v>
+      </c>
+      <c r="I50" s="5">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <v>11</v>
+      </c>
+      <c r="N50">
         <v>10</v>
       </c>
-      <c r="I50" s="5">
-        <v>6</v>
-      </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="M50" s="4">
-        <v>32</v>
-      </c>
-      <c r="N50">
-        <v>40</v>
-      </c>
       <c r="O50" s="5">
-        <v>40</v>
-      </c>
-      <c r="P50" s="4">
-        <v>33</v>
-      </c>
-      <c r="Q50">
-        <v>30</v>
-      </c>
-      <c r="R50" s="5">
-        <v>30</v>
-      </c>
-      <c r="S50" s="4">
-        <v>19</v>
-      </c>
-      <c r="T50">
-        <v>1</v>
-      </c>
-      <c r="U50" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AE50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:31">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
-        <v>134</v>
-      </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H51" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I51" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -4485,30 +4509,42 @@
         <v>11</v>
       </c>
       <c r="N51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O51" s="5">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="P51" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q51">
+        <v>3</v>
+      </c>
+      <c r="R51" s="5">
+        <v>3</v>
       </c>
       <c r="AE51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:31">
       <c r="A52">
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>138</v>
+      </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H52" s="4">
         <v>4</v>
@@ -4526,22 +4562,22 @@
         <v>11</v>
       </c>
       <c r="N52">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O52" s="5">
         <v>11</v>
       </c>
       <c r="P52" s="4">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R52" s="5">
         <v>3</v>
       </c>
       <c r="AE52" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:31">
@@ -4549,52 +4585,52 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="4">
+        <v>5</v>
+      </c>
+      <c r="I53" s="5">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="M53" s="4">
+        <v>6</v>
+      </c>
+      <c r="N53">
+        <v>5</v>
+      </c>
+      <c r="O53" s="5">
+        <v>7</v>
+      </c>
+      <c r="P53" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q53">
+        <v>1.1</v>
+      </c>
+      <c r="R53" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="AE53" t="s">
         <v>33</v>
-      </c>
-      <c r="H53" s="4">
-        <v>4</v>
-      </c>
-      <c r="I53" s="5">
-        <v>3</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="M53" s="4">
-        <v>11</v>
-      </c>
-      <c r="N53">
-        <v>7</v>
-      </c>
-      <c r="O53" s="5">
-        <v>11</v>
-      </c>
-      <c r="P53" s="4">
-        <v>45</v>
-      </c>
-      <c r="Q53">
-        <v>2</v>
-      </c>
-      <c r="R53" s="5">
-        <v>3</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:31">
@@ -4602,25 +4638,25 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H54" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I54" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -4632,75 +4668,72 @@
         <v>6</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O54" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P54" s="4">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="Q54">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="R54" s="5">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AE54" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H55" s="4">
+        <v>1</v>
+      </c>
+      <c r="I55" s="5">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="M55" s="4">
         <v>9</v>
       </c>
-      <c r="I55" s="5">
-        <v>6</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55">
-        <v>1</v>
-      </c>
-      <c r="M55" s="4">
-        <v>6</v>
-      </c>
       <c r="N55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P55" s="4">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55" s="5">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -4708,98 +4741,51 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H56" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I56" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56">
         <v>1</v>
       </c>
+      <c r="L56">
+        <v>6</v>
+      </c>
       <c r="M56" s="4">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="N56">
         <v>2</v>
       </c>
       <c r="O56" s="5">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P56" s="4">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R56" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>145</v>
-      </c>
-      <c r="C57" t="s">
-        <v>146</v>
-      </c>
-      <c r="D57" t="s">
-        <v>44</v>
-      </c>
-      <c r="E57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" t="s">
-        <v>33</v>
-      </c>
-      <c r="H57" s="4">
-        <v>5</v>
-      </c>
-      <c r="I57" s="5">
-        <v>5</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="M57" s="4">
-        <v>52</v>
-      </c>
-      <c r="N57">
-        <v>2</v>
-      </c>
-      <c r="O57" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="P57" s="4">
-        <v>53</v>
-      </c>
-      <c r="Q57">
-        <v>0.5</v>
-      </c>
-      <c r="R57" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -4816,7 +4802,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4844,19 +4830,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4864,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4882,19 +4868,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4905,16 +4891,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4925,16 +4911,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4945,13 +4931,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4962,16 +4948,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4982,13 +4968,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5002,13 +4988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" t="s">
         <v>173</v>
-      </c>
-      <c r="C9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" t="s">
-        <v>172</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5022,13 +5008,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5042,13 +5028,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5059,16 +5045,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5079,16 +5065,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5099,19 +5085,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5122,16 +5108,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5142,16 +5128,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5162,13 +5148,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5182,16 +5168,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5202,13 +5188,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5222,13 +5208,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5242,16 +5228,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5262,16 +5248,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5282,13 +5268,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5302,19 +5288,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5325,13 +5311,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5345,16 +5331,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5368,16 +5354,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5388,13 +5374,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5408,19 +5394,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5434,13 +5420,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5454,19 +5440,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5477,19 +5463,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5500,19 +5486,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5523,16 +5509,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5543,16 +5529,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5563,19 +5549,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" t="s">
         <v>216</v>
       </c>
-      <c r="C36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E36" t="s">
-        <v>215</v>
-      </c>
       <c r="F36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5589,13 +5575,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5609,16 +5595,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5629,13 +5615,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5652,16 +5638,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5672,13 +5658,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5695,19 +5681,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5721,13 +5707,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5741,13 +5727,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5761,19 +5747,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5784,16 +5770,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5804,13 +5790,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5824,19 +5810,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5847,13 +5833,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -5867,19 +5853,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -5890,13 +5876,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -5910,13 +5896,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -5930,76 +5916,19 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D53" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="I53">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:9">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" t="s">
-        <v>237</v>
-      </c>
-      <c r="C54" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" t="s">
-        <v>193</v>
-      </c>
-      <c r="E54">
-        <v>3</v>
-      </c>
-      <c r="G54">
-        <v>6</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:9">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55" t="s">
-        <v>238</v>
-      </c>
-      <c r="C55" t="s">
-        <v>238</v>
-      </c>
-      <c r="D55" t="s">
-        <v>231</v>
-      </c>
-      <c r="E55">
-        <v>3</v>
-      </c>
-      <c r="G55">
-        <v>6</v>
-      </c>
-      <c r="I55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>239</v>
-      </c>
-      <c r="C56" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -6035,31 +5964,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6067,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6096,10 +6025,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6119,10 +6048,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6142,10 +6071,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6165,10 +6094,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6188,10 +6117,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6211,10 +6140,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6234,10 +6163,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6257,10 +6186,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6280,10 +6209,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6309,10 +6238,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6338,10 +6267,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6361,10 +6290,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6384,10 +6313,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6407,10 +6336,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6430,10 +6359,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6453,10 +6382,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6476,10 +6405,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6493,10 +6422,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6538,16 +6467,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1" t="s">
         <v>256</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>257</v>
-      </c>
-      <c r="F1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6555,13 +6484,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" t="s">
         <v>260</v>
-      </c>
-      <c r="C2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D2" t="s">
-        <v>262</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6575,16 +6504,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" ht="13" customHeight="1" spans="1:6">
@@ -6592,16 +6521,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6609,13 +6538,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6629,13 +6558,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6649,13 +6578,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6669,13 +6598,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E8">
         <v>3</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3CB174-B493-41F6-87CB-55A3FEE172D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
+    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -842,167 +848,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1021,188 +877,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1228,319 +904,31 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1798,42 +1186,42 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="44.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="10.425" customWidth="1"/>
-    <col min="5" max="5" width="13.425" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14" style="5" customWidth="1"/>
-    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" customWidth="1"/>
-    <col min="13" max="13" width="9.70833333333333" style="4" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="16" max="16" width="11" style="4" customWidth="1"/>
-    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" style="5" customWidth="1"/>
-    <col min="19" max="19" width="9" style="4"/>
-    <col min="21" max="21" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="22" max="22" width="10.7083333333333" style="4" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9" style="2"/>
+    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" style="5" customWidth="1"/>
-    <col min="25" max="25" width="12.425" style="4" customWidth="1"/>
-    <col min="26" max="26" width="12.425" style="5" customWidth="1"/>
-    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
-    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -1858,10 +1246,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1873,46 +1261,46 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -1947,10 +1335,10 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="2">
         <v>4</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="3">
         <v>3</v>
       </c>
       <c r="J2">
@@ -1959,16 +1347,16 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="2">
         <v>11</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="3">
         <v>7</v>
       </c>
-      <c r="AC2" s="6"/>
+      <c r="AC2" s="4"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
@@ -1992,10 +1380,10 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
         <v>0</v>
       </c>
       <c r="J3">
@@ -2004,16 +1392,16 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="2">
         <v>2</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="3">
         <v>4</v>
       </c>
-      <c r="AC3" s="6"/>
+      <c r="AC3" s="4"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
@@ -2037,10 +1425,10 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <v>5</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>5</v>
       </c>
       <c r="J4">
@@ -2049,16 +1437,16 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="2">
         <v>11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="3">
         <v>15</v>
       </c>
-      <c r="AC4" s="6"/>
+      <c r="AC4" s="4"/>
       <c r="AE4" t="s">
         <v>35</v>
       </c>
@@ -2082,10 +1470,10 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="4">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3">
         <v>3</v>
       </c>
       <c r="J5">
@@ -2094,25 +1482,25 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="2">
         <v>11</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="3">
         <v>5</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="2">
         <v>2</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC5" s="6"/>
+      <c r="R5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="4"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
@@ -2139,10 +1527,10 @@
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2151,10 +1539,10 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6"/>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4"/>
       <c r="AE6" t="s">
         <v>35</v>
       </c>
@@ -2178,10 +1566,10 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="3">
         <v>5</v>
       </c>
       <c r="J7">
@@ -2190,10 +1578,10 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="2">
         <v>4</v>
       </c>
-      <c r="AC7" s="6"/>
+      <c r="AC7" s="4"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
@@ -2220,10 +1608,10 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2232,34 +1620,34 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="2">
         <v>2</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="3">
         <v>7</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
         <v>3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="5">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="R8" s="3">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
         <v>14</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="6"/>
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="4"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
@@ -2283,10 +1671,10 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>0</v>
       </c>
       <c r="J9">
@@ -2295,25 +1683,25 @@
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="2">
         <v>17</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2">
         <v>2</v>
       </c>
       <c r="Q9">
         <v>4</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="3">
         <v>6</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="4"/>
       <c r="AE9" t="s">
         <v>35</v>
       </c>
@@ -2337,10 +1725,10 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="4">
-        <v>2</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2349,25 +1737,25 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="2">
         <v>6</v>
       </c>
       <c r="N10">
         <v>3</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="3">
         <v>4</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="2">
         <v>2</v>
       </c>
       <c r="Q10">
         <v>3</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10" s="3">
         <v>4</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="4"/>
       <c r="AE10" t="s">
         <v>33</v>
       </c>
@@ -2391,10 +1779,10 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="4">
-        <v>2</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2403,25 +1791,25 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="2">
         <v>7</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="5">
-        <v>3</v>
-      </c>
-      <c r="P11" s="4">
+      <c r="O11" s="3">
+        <v>3</v>
+      </c>
+      <c r="P11" s="2">
         <v>2</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="6"/>
+      <c r="R11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="4"/>
       <c r="AE11" t="s">
         <v>52</v>
       </c>
@@ -2445,10 +1833,10 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="4">
-        <v>2</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3">
         <v>2</v>
       </c>
       <c r="J12">
@@ -2457,25 +1845,25 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="2">
         <v>15</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
-      <c r="O12" s="5">
-        <v>3</v>
-      </c>
-      <c r="P12" s="4">
+      <c r="O12" s="3">
+        <v>3</v>
+      </c>
+      <c r="P12" s="2">
         <v>2</v>
       </c>
       <c r="Q12">
         <v>2</v>
       </c>
-      <c r="R12" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC12" s="6"/>
+      <c r="R12" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="4"/>
       <c r="AE12" t="s">
         <v>61</v>
       </c>
@@ -2499,10 +1887,10 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <v>6</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="3">
         <v>6</v>
       </c>
       <c r="J13">
@@ -2511,25 +1899,25 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M13" s="2">
         <v>11</v>
       </c>
       <c r="N13">
         <v>9</v>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="3">
         <v>13</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="2">
         <v>11</v>
       </c>
       <c r="Q13">
         <v>9</v>
       </c>
-      <c r="R13" s="5">
+      <c r="R13" s="3">
         <v>13</v>
       </c>
-      <c r="AC13" s="6"/>
+      <c r="AC13" s="4"/>
       <c r="AD13" t="s">
         <v>64</v>
       </c>
@@ -2556,10 +1944,10 @@
       <c r="F14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="3">
         <v>5</v>
       </c>
       <c r="J14">
@@ -2568,25 +1956,25 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="2">
         <v>11</v>
       </c>
       <c r="N14">
         <v>11</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="3">
         <v>15</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P14" s="2">
         <v>2</v>
       </c>
       <c r="Q14">
         <v>7</v>
       </c>
-      <c r="R14" s="5">
+      <c r="R14" s="3">
         <v>9</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="4"/>
       <c r="AE14" t="s">
         <v>35</v>
       </c>
@@ -2610,10 +1998,10 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="3">
         <v>4</v>
       </c>
       <c r="J15">
@@ -2622,16 +2010,16 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="M15" s="4">
+      <c r="M15" s="2">
         <v>6</v>
       </c>
       <c r="N15">
         <v>6</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="3">
         <v>8</v>
       </c>
-      <c r="AC15" s="6"/>
+      <c r="AC15" s="4"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
@@ -2655,10 +2043,10 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="2">
         <v>4</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="3">
         <v>4</v>
       </c>
       <c r="J16">
@@ -2667,16 +2055,16 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M16" s="2">
         <v>18</v>
       </c>
       <c r="N16">
         <v>1.4</v>
       </c>
-      <c r="O16" s="5">
+      <c r="O16" s="3">
         <v>1.8</v>
       </c>
-      <c r="AC16" s="6"/>
+      <c r="AC16" s="4"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
@@ -2700,10 +2088,10 @@
       <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <v>6</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="3">
         <v>5</v>
       </c>
       <c r="J17">
@@ -2712,25 +2100,25 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="2">
         <v>6</v>
       </c>
       <c r="N17">
         <v>4</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="3">
         <v>5</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P17" s="2">
         <v>18</v>
       </c>
       <c r="Q17">
         <v>0.8</v>
       </c>
-      <c r="R17" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AC17" s="6"/>
+      <c r="R17" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AC17" s="4"/>
       <c r="AE17" t="s">
         <v>33</v>
       </c>
@@ -2754,10 +2142,10 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="4">
-        <v>3</v>
-      </c>
-      <c r="I18" s="5">
+      <c r="H18" s="2">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>3</v>
       </c>
       <c r="J18">
@@ -2766,34 +2154,34 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18" s="2">
         <v>19</v>
       </c>
       <c r="N18">
         <v>1</v>
       </c>
-      <c r="O18" s="5">
-        <v>1</v>
-      </c>
-      <c r="P18" s="4">
+      <c r="O18" s="3">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2">
         <v>2</v>
       </c>
       <c r="Q18">
         <v>4</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R18" s="3">
         <v>6</v>
       </c>
-      <c r="S18" s="4">
+      <c r="S18" s="2">
         <v>21</v>
       </c>
       <c r="T18">
         <v>2</v>
       </c>
-      <c r="U18" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="7"/>
+      <c r="U18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="5"/>
       <c r="AE18" t="s">
         <v>35</v>
       </c>
@@ -2817,10 +2205,10 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>6</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="3">
         <v>5</v>
       </c>
       <c r="J19">
@@ -2829,10 +2217,10 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="M19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="6"/>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4"/>
       <c r="AE19" t="s">
         <v>35</v>
       </c>
@@ -2856,10 +2244,10 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <v>4</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="3">
         <v>3</v>
       </c>
       <c r="J20">
@@ -2868,16 +2256,16 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="2">
         <v>15</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="3">
         <v>7</v>
       </c>
-      <c r="AC20" s="6"/>
+      <c r="AC20" s="4"/>
       <c r="AE20" t="s">
         <v>61</v>
       </c>
@@ -2901,10 +2289,10 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="3">
         <v>4</v>
       </c>
       <c r="J21">
@@ -2913,25 +2301,25 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="2">
         <v>23</v>
       </c>
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21" s="5">
-        <v>1</v>
-      </c>
-      <c r="P21" s="4">
+      <c r="O21" s="3">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
         <v>7</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="R21" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="6"/>
+      <c r="R21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="4"/>
       <c r="AE21" t="s">
         <v>52</v>
       </c>
@@ -2955,10 +2343,10 @@
       <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="3">
         <v>6</v>
       </c>
       <c r="J22">
@@ -2967,16 +2355,16 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="M22" s="4">
+      <c r="M22" s="2">
         <v>24</v>
       </c>
       <c r="N22">
         <v>24</v>
       </c>
-      <c r="O22" s="5">
+      <c r="O22" s="3">
         <v>30</v>
       </c>
-      <c r="AC22" s="7"/>
+      <c r="AC22" s="5"/>
       <c r="AE22" t="s">
         <v>61</v>
       </c>
@@ -3000,10 +2388,10 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <v>5</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <v>4</v>
       </c>
       <c r="J23">
@@ -3012,34 +2400,34 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="2">
         <v>26</v>
       </c>
       <c r="N23">
         <v>2</v>
       </c>
-      <c r="O23" s="5">
-        <v>2</v>
-      </c>
-      <c r="P23" s="4">
+      <c r="O23" s="3">
+        <v>2</v>
+      </c>
+      <c r="P23" s="2">
         <v>11</v>
       </c>
       <c r="Q23">
         <v>30</v>
       </c>
-      <c r="R23" s="5">
+      <c r="R23" s="3">
         <v>42</v>
       </c>
-      <c r="S23" s="4">
+      <c r="S23" s="2">
         <v>2</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
-      <c r="U23" s="5">
+      <c r="U23" s="3">
         <v>7</v>
       </c>
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="4"/>
       <c r="AE23" t="s">
         <v>61</v>
       </c>
@@ -3063,10 +2451,10 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="2">
         <v>4</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="3">
         <v>4</v>
       </c>
       <c r="J24">
@@ -3075,25 +2463,25 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="M24" s="4">
+      <c r="M24" s="2">
         <v>6</v>
       </c>
       <c r="N24">
         <v>2</v>
       </c>
-      <c r="O24" s="5">
+      <c r="O24" s="3">
         <v>4</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="2">
         <v>28</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="R24" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="6"/>
+      <c r="R24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="4"/>
       <c r="AE24" t="s">
         <v>33</v>
       </c>
@@ -3117,10 +2505,10 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="4">
-        <v>1</v>
-      </c>
-      <c r="I25" s="5">
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3129,25 +2517,25 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="4">
+      <c r="M25" s="2">
         <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
-      <c r="O25" s="5">
+      <c r="O25" s="3">
         <v>7</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="2">
         <v>2</v>
       </c>
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="R25" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="6"/>
+      <c r="R25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="4"/>
       <c r="AE25" t="s">
         <v>33</v>
       </c>
@@ -3171,10 +2559,10 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="2">
         <v>4</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="3">
         <v>4</v>
       </c>
       <c r="J26">
@@ -3183,25 +2571,25 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="2">
         <v>15</v>
       </c>
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="3">
         <v>4</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="2">
         <v>11</v>
       </c>
       <c r="Q26">
         <v>8</v>
       </c>
-      <c r="R26" s="5">
+      <c r="R26" s="3">
         <v>11</v>
       </c>
-      <c r="AC26" s="6"/>
+      <c r="AC26" s="4"/>
       <c r="AE26" t="s">
         <v>61</v>
       </c>
@@ -3225,10 +2613,10 @@
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="4">
-        <v>3</v>
-      </c>
-      <c r="I27" s="5">
+      <c r="H27" s="2">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>2</v>
       </c>
       <c r="J27">
@@ -3237,16 +2625,16 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="M27" s="4">
+      <c r="M27" s="2">
         <v>7</v>
       </c>
       <c r="N27">
         <v>3</v>
       </c>
-      <c r="O27" s="5">
+      <c r="O27" s="3">
         <v>5</v>
       </c>
-      <c r="AC27" s="6"/>
+      <c r="AC27" s="4"/>
       <c r="AE27" t="s">
         <v>52</v>
       </c>
@@ -3270,10 +2658,10 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="4">
-        <v>3</v>
-      </c>
-      <c r="I28" s="5">
+      <c r="H28" s="2">
+        <v>3</v>
+      </c>
+      <c r="I28" s="3">
         <v>2</v>
       </c>
       <c r="J28">
@@ -3282,25 +2670,25 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="M28" s="4">
+      <c r="M28" s="2">
         <v>7</v>
       </c>
       <c r="N28">
         <v>3</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="3">
         <v>4</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="2">
         <v>2</v>
       </c>
       <c r="Q28">
         <v>4</v>
       </c>
-      <c r="R28" s="5">
+      <c r="R28" s="3">
         <v>6</v>
       </c>
-      <c r="AC28" s="6"/>
+      <c r="AC28" s="4"/>
       <c r="AE28" t="s">
         <v>52</v>
       </c>
@@ -3324,10 +2712,10 @@
       <c r="F29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="2">
         <v>10</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="3">
         <v>8</v>
       </c>
       <c r="J29">
@@ -3336,34 +2724,34 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="2">
         <v>15</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
-      <c r="O29" s="5">
+      <c r="O29" s="3">
         <v>7</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="2">
         <v>30</v>
       </c>
       <c r="Q29">
         <v>1</v>
       </c>
-      <c r="R29" s="5">
-        <v>1</v>
-      </c>
-      <c r="S29" s="4">
+      <c r="R29" s="3">
+        <v>1</v>
+      </c>
+      <c r="S29" s="2">
         <v>31</v>
       </c>
       <c r="T29">
         <v>1</v>
       </c>
-      <c r="U29" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="7"/>
+      <c r="U29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="5"/>
       <c r="AE29" t="s">
         <v>61</v>
       </c>
@@ -3387,10 +2775,10 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="4">
-        <v>1</v>
-      </c>
-      <c r="I30" s="5">
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
         <v>0</v>
       </c>
       <c r="J30">
@@ -3399,16 +2787,16 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M30" s="2">
         <v>2</v>
       </c>
       <c r="N30">
         <v>6</v>
       </c>
-      <c r="O30" s="5">
+      <c r="O30" s="3">
         <v>8</v>
       </c>
-      <c r="AC30" s="6"/>
+      <c r="AC30" s="4"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
@@ -3432,10 +2820,10 @@
       <c r="F31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="2">
         <v>6</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="3">
         <v>5</v>
       </c>
       <c r="J31">
@@ -3444,34 +2832,34 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="M31" s="4">
+      <c r="M31" s="2">
         <v>19</v>
       </c>
       <c r="N31">
         <v>1</v>
       </c>
-      <c r="O31" s="5">
-        <v>1</v>
-      </c>
-      <c r="P31" s="4">
+      <c r="O31" s="3">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2">
         <v>11</v>
       </c>
       <c r="Q31">
         <v>4</v>
       </c>
-      <c r="R31" s="5">
+      <c r="R31" s="3">
         <v>7</v>
       </c>
-      <c r="S31" s="4">
+      <c r="S31" s="2">
         <v>14</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
-      <c r="U31" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="7"/>
+      <c r="U31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="5"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
@@ -3495,10 +2883,10 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="2">
         <v>5</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="3">
         <v>5</v>
       </c>
       <c r="J32">
@@ -3507,34 +2895,34 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="2">
         <v>32</v>
       </c>
       <c r="N32">
         <v>30</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O32" s="3">
         <v>30</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="2">
         <v>2</v>
       </c>
       <c r="Q32">
         <v>3</v>
       </c>
-      <c r="R32" s="5">
+      <c r="R32" s="3">
         <v>5</v>
       </c>
-      <c r="S32" s="4">
+      <c r="S32" s="2">
         <v>21</v>
       </c>
       <c r="T32">
         <v>2</v>
       </c>
-      <c r="U32" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="6"/>
+      <c r="U32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="4"/>
       <c r="AE32" t="s">
         <v>35</v>
       </c>
@@ -3558,10 +2946,10 @@
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="2">
         <v>4</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="3">
         <v>4</v>
       </c>
       <c r="J33">
@@ -3570,25 +2958,25 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" s="4">
+      <c r="M33" s="2">
         <v>33</v>
       </c>
       <c r="N33">
         <v>50</v>
       </c>
-      <c r="O33" s="5">
+      <c r="O33" s="3">
         <v>70</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="2">
         <v>2</v>
       </c>
       <c r="Q33">
         <v>2</v>
       </c>
-      <c r="R33" s="5">
+      <c r="R33" s="3">
         <v>4</v>
       </c>
-      <c r="AC33" s="7"/>
+      <c r="AC33" s="5"/>
       <c r="AE33" t="s">
         <v>35</v>
       </c>
@@ -3612,10 +3000,10 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="2">
         <v>4</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="3">
         <v>3</v>
       </c>
       <c r="J34">
@@ -3624,25 +3012,25 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="M34" s="4">
+      <c r="M34" s="2">
         <v>33</v>
       </c>
       <c r="N34">
         <v>20</v>
       </c>
-      <c r="O34" s="5">
+      <c r="O34" s="3">
         <v>30</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="2">
         <v>35</v>
       </c>
       <c r="Q34">
         <v>1</v>
       </c>
-      <c r="R34" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="7"/>
+      <c r="R34" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="5"/>
       <c r="AE34" t="s">
         <v>35</v>
       </c>
@@ -3666,10 +3054,10 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="2">
         <v>7</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="3">
         <v>6</v>
       </c>
       <c r="J35">
@@ -3701,10 +3089,10 @@
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="2">
         <v>8</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="3">
         <v>7</v>
       </c>
       <c r="J36">
@@ -3713,13 +3101,13 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="2">
         <v>11</v>
       </c>
       <c r="N36">
         <v>42</v>
       </c>
-      <c r="O36" s="5">
+      <c r="O36" s="3">
         <v>54</v>
       </c>
       <c r="AE36" t="s">
@@ -3745,10 +3133,10 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="4">
-        <v>3</v>
-      </c>
-      <c r="I37" s="5">
+      <c r="H37" s="2">
+        <v>3</v>
+      </c>
+      <c r="I37" s="3">
         <v>3</v>
       </c>
       <c r="J37">
@@ -3757,22 +3145,22 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="M37" s="4">
+      <c r="M37" s="2">
         <v>37</v>
       </c>
       <c r="N37">
         <v>1</v>
       </c>
-      <c r="O37" s="5">
-        <v>2</v>
-      </c>
-      <c r="P37" s="4">
+      <c r="O37" s="3">
+        <v>2</v>
+      </c>
+      <c r="P37" s="2">
         <v>15</v>
       </c>
       <c r="Q37">
         <v>3</v>
       </c>
-      <c r="R37" s="5">
+      <c r="R37" s="3">
         <v>4</v>
       </c>
       <c r="AE37" t="s">
@@ -3798,10 +3186,10 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="4">
-        <v>3</v>
-      </c>
-      <c r="I38" s="5">
+      <c r="H38" s="2">
+        <v>3</v>
+      </c>
+      <c r="I38" s="3">
         <v>3</v>
       </c>
       <c r="J38">
@@ -3810,13 +3198,13 @@
       <c r="K38">
         <v>0</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="2">
         <v>11</v>
       </c>
       <c r="N38">
         <v>18</v>
       </c>
-      <c r="O38" s="5">
+      <c r="O38" s="3">
         <v>22</v>
       </c>
       <c r="AE38" t="s">
@@ -3842,10 +3230,10 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="4">
-        <v>3</v>
-      </c>
-      <c r="I39" s="5">
+      <c r="H39" s="2">
+        <v>3</v>
+      </c>
+      <c r="I39" s="3">
         <v>3</v>
       </c>
       <c r="J39">
@@ -3854,22 +3242,22 @@
       <c r="K39">
         <v>0</v>
       </c>
-      <c r="M39" s="4">
+      <c r="M39" s="2">
         <v>15</v>
       </c>
       <c r="N39">
         <v>3</v>
       </c>
-      <c r="O39" s="5">
+      <c r="O39" s="3">
         <v>4</v>
       </c>
-      <c r="P39" s="4">
+      <c r="P39" s="2">
         <v>2</v>
       </c>
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="5">
+      <c r="R39" s="3">
         <v>8</v>
       </c>
       <c r="AE39" t="s">
@@ -3895,10 +3283,10 @@
       <c r="F40" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="4">
-        <v>3</v>
-      </c>
-      <c r="I40" s="5">
+      <c r="H40" s="2">
+        <v>3</v>
+      </c>
+      <c r="I40" s="3">
         <v>3</v>
       </c>
       <c r="J40">
@@ -3907,22 +3295,22 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="M40" s="4">
+      <c r="M40" s="2">
         <v>7</v>
       </c>
       <c r="N40">
         <v>3</v>
       </c>
-      <c r="O40" s="5">
+      <c r="O40" s="3">
         <v>4</v>
       </c>
-      <c r="P40" s="4">
+      <c r="P40" s="2">
         <v>2</v>
       </c>
       <c r="Q40">
         <v>6</v>
       </c>
-      <c r="R40" s="5">
+      <c r="R40" s="3">
         <v>8</v>
       </c>
       <c r="AE40" t="s">
@@ -3948,10 +3336,10 @@
       <c r="F41" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="4">
-        <v>1</v>
-      </c>
-      <c r="I41" s="5">
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
         <v>1</v>
       </c>
       <c r="J41">
@@ -3960,22 +3348,22 @@
       <c r="K41">
         <v>1</v>
       </c>
-      <c r="M41" s="4">
+      <c r="M41" s="2">
         <v>21</v>
       </c>
       <c r="N41">
         <v>4</v>
       </c>
-      <c r="O41" s="5">
+      <c r="O41" s="3">
         <v>5</v>
       </c>
-      <c r="P41" s="4">
+      <c r="P41" s="2">
         <v>2</v>
       </c>
       <c r="Q41">
         <v>3</v>
       </c>
-      <c r="R41" s="5">
+      <c r="R41" s="3">
         <v>5</v>
       </c>
       <c r="AE41" t="s">
@@ -4001,10 +3389,10 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="4">
-        <v>1</v>
-      </c>
-      <c r="I42" s="5">
+      <c r="H42" s="2">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4013,22 +3401,22 @@
       <c r="K42">
         <v>1</v>
       </c>
-      <c r="M42" s="4">
+      <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42" s="5">
-        <v>2</v>
-      </c>
-      <c r="P42" s="4">
+      <c r="O42" s="3">
+        <v>2</v>
+      </c>
+      <c r="P42" s="2">
         <v>2</v>
       </c>
       <c r="Q42">
         <v>6</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="3">
         <v>7</v>
       </c>
       <c r="AE42" t="s">
@@ -4054,10 +3442,10 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="2">
         <v>4</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="3">
         <v>3</v>
       </c>
       <c r="J43">
@@ -4066,22 +3454,22 @@
       <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="2">
         <v>7</v>
       </c>
       <c r="N43">
         <v>4</v>
       </c>
-      <c r="O43" s="5">
+      <c r="O43" s="3">
         <v>5</v>
       </c>
-      <c r="P43" s="4">
+      <c r="P43" s="2">
         <v>38</v>
       </c>
       <c r="Q43">
         <v>4</v>
       </c>
-      <c r="R43" s="5">
+      <c r="R43" s="3">
         <v>5</v>
       </c>
       <c r="AE43" t="s">
@@ -4107,10 +3495,10 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="4">
-        <v>2</v>
-      </c>
-      <c r="I44" s="5">
+      <c r="H44" s="2">
+        <v>2</v>
+      </c>
+      <c r="I44" s="3">
         <v>2</v>
       </c>
       <c r="J44">
@@ -4119,22 +3507,22 @@
       <c r="K44">
         <v>0</v>
       </c>
-      <c r="M44" s="4">
+      <c r="M44" s="2">
         <v>6</v>
       </c>
       <c r="N44">
         <v>3</v>
       </c>
-      <c r="O44" s="5">
-        <v>3</v>
-      </c>
-      <c r="P44" s="4">
+      <c r="O44" s="3">
+        <v>3</v>
+      </c>
+      <c r="P44" s="2">
         <v>39</v>
       </c>
       <c r="Q44">
         <v>2</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="3">
         <v>3</v>
       </c>
       <c r="AE44" t="s">
@@ -4160,10 +3548,10 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="2">
         <v>4</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="3">
         <v>3</v>
       </c>
       <c r="J45">
@@ -4172,22 +3560,22 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="M45" s="4">
+      <c r="M45" s="2">
         <v>7</v>
       </c>
       <c r="N45">
         <v>1</v>
       </c>
-      <c r="O45" s="5">
-        <v>3</v>
-      </c>
-      <c r="P45" s="4">
+      <c r="O45" s="3">
+        <v>3</v>
+      </c>
+      <c r="P45" s="2">
         <v>41</v>
       </c>
       <c r="Q45">
         <v>1</v>
       </c>
-      <c r="R45" s="5">
+      <c r="R45" s="3">
         <v>1</v>
       </c>
       <c r="AE45" t="s">
@@ -4213,10 +3601,10 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="2">
         <v>7</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="3">
         <v>4</v>
       </c>
       <c r="J46">
@@ -4225,31 +3613,31 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="M46" s="4">
+      <c r="M46" s="2">
         <v>6</v>
       </c>
       <c r="N46">
         <v>5</v>
       </c>
-      <c r="O46" s="5">
+      <c r="O46" s="3">
         <v>5</v>
       </c>
-      <c r="P46" s="4">
+      <c r="P46" s="2">
         <v>14</v>
       </c>
       <c r="Q46">
         <v>1</v>
       </c>
-      <c r="R46" s="5">
-        <v>1</v>
-      </c>
-      <c r="S46" s="4">
+      <c r="R46" s="3">
+        <v>1</v>
+      </c>
+      <c r="S46" s="2">
         <v>18</v>
       </c>
       <c r="T46">
         <v>0.9</v>
       </c>
-      <c r="U46" s="5">
+      <c r="U46" s="3">
         <v>1.2</v>
       </c>
       <c r="AE46" t="s">
@@ -4275,10 +3663,10 @@
       <c r="F47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H47" s="2">
         <v>6</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="3">
         <v>4</v>
       </c>
       <c r="J47">
@@ -4287,22 +3675,22 @@
       <c r="K47">
         <v>1</v>
       </c>
-      <c r="M47" s="4">
+      <c r="M47" s="2">
         <v>15</v>
       </c>
       <c r="N47">
         <v>2</v>
       </c>
-      <c r="O47" s="5">
-        <v>2</v>
-      </c>
-      <c r="P47" s="4">
+      <c r="O47" s="3">
+        <v>2</v>
+      </c>
+      <c r="P47" s="2">
         <v>42</v>
       </c>
       <c r="Q47">
         <v>3</v>
       </c>
-      <c r="R47" s="5">
+      <c r="R47" s="3">
         <v>5</v>
       </c>
       <c r="AE47" t="s">
@@ -4328,10 +3716,10 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48" s="2">
         <v>5</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="3">
         <v>4</v>
       </c>
       <c r="J48">
@@ -4340,31 +3728,31 @@
       <c r="K48">
         <v>1</v>
       </c>
-      <c r="M48" s="4">
+      <c r="M48" s="2">
         <v>7</v>
       </c>
       <c r="N48">
         <v>7</v>
       </c>
-      <c r="O48" s="5">
+      <c r="O48" s="3">
         <v>9</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P48" s="2">
         <v>26</v>
       </c>
       <c r="Q48">
         <v>2</v>
       </c>
-      <c r="R48" s="5">
-        <v>2</v>
-      </c>
-      <c r="S48" s="4">
+      <c r="R48" s="3">
+        <v>2</v>
+      </c>
+      <c r="S48" s="2">
         <v>2</v>
       </c>
       <c r="T48">
         <v>7</v>
       </c>
-      <c r="U48" s="5">
+      <c r="U48" s="3">
         <v>8</v>
       </c>
       <c r="AE48" t="s">
@@ -4390,10 +3778,10 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="2">
         <v>10</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="3">
         <v>6</v>
       </c>
       <c r="J49">
@@ -4402,31 +3790,31 @@
       <c r="K49">
         <v>1</v>
       </c>
-      <c r="M49" s="4">
+      <c r="M49" s="2">
         <v>32</v>
       </c>
       <c r="N49">
         <v>40</v>
       </c>
-      <c r="O49" s="5">
+      <c r="O49" s="3">
         <v>40</v>
       </c>
-      <c r="P49" s="4">
+      <c r="P49" s="2">
         <v>33</v>
       </c>
       <c r="Q49">
         <v>30</v>
       </c>
-      <c r="R49" s="5">
+      <c r="R49" s="3">
         <v>30</v>
       </c>
-      <c r="S49" s="4">
+      <c r="S49" s="2">
         <v>19</v>
       </c>
       <c r="T49">
         <v>1</v>
       </c>
-      <c r="U49" s="5">
+      <c r="U49" s="3">
         <v>1</v>
       </c>
       <c r="AE49" t="s">
@@ -4452,10 +3840,10 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="4">
-        <v>2</v>
-      </c>
-      <c r="I50" s="5">
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="I50" s="3">
         <v>1</v>
       </c>
       <c r="J50">
@@ -4464,13 +3852,13 @@
       <c r="K50">
         <v>0</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M50" s="2">
         <v>11</v>
       </c>
       <c r="N50">
         <v>10</v>
       </c>
-      <c r="O50" s="5">
+      <c r="O50" s="3">
         <v>14</v>
       </c>
       <c r="AE50" t="s">
@@ -4493,10 +3881,10 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="2">
         <v>4</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="3">
         <v>3</v>
       </c>
       <c r="J51">
@@ -4505,22 +3893,22 @@
       <c r="K51">
         <v>0</v>
       </c>
-      <c r="M51" s="4">
+      <c r="M51" s="2">
         <v>11</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
-      <c r="O51" s="5">
+      <c r="O51" s="3">
         <v>11</v>
       </c>
-      <c r="P51" s="4">
+      <c r="P51" s="2">
         <v>6</v>
       </c>
       <c r="Q51">
         <v>3</v>
       </c>
-      <c r="R51" s="5">
+      <c r="R51" s="3">
         <v>3</v>
       </c>
       <c r="AE51" t="s">
@@ -4546,10 +3934,10 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H52" s="2">
         <v>4</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="3">
         <v>3</v>
       </c>
       <c r="J52">
@@ -4558,22 +3946,22 @@
       <c r="K52">
         <v>0</v>
       </c>
-      <c r="M52" s="4">
+      <c r="M52" s="2">
         <v>11</v>
       </c>
       <c r="N52">
         <v>7</v>
       </c>
-      <c r="O52" s="5">
+      <c r="O52" s="3">
         <v>11</v>
       </c>
-      <c r="P52" s="4">
+      <c r="P52" s="2">
         <v>45</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="3">
         <v>3</v>
       </c>
       <c r="AE52" t="s">
@@ -4599,10 +3987,10 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53" s="2">
         <v>5</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="3">
         <v>4</v>
       </c>
       <c r="J53">
@@ -4611,22 +3999,22 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="M53" s="4">
+      <c r="M53" s="2">
         <v>6</v>
       </c>
       <c r="N53">
         <v>5</v>
       </c>
-      <c r="O53" s="5">
+      <c r="O53" s="3">
         <v>7</v>
       </c>
-      <c r="P53" s="4">
+      <c r="P53" s="2">
         <v>18</v>
       </c>
       <c r="Q53">
-        <v>1.1</v>
-      </c>
-      <c r="R53" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R53" s="3">
         <v>1.7</v>
       </c>
       <c r="AE53" t="s">
@@ -4652,10 +4040,10 @@
       <c r="F54" t="s">
         <v>34</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54" s="2">
         <v>9</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="3">
         <v>6</v>
       </c>
       <c r="J54">
@@ -4664,29 +4052,29 @@
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="M54" s="4">
+      <c r="M54" s="2">
         <v>6</v>
       </c>
       <c r="N54">
         <v>1</v>
       </c>
-      <c r="O54" s="5">
-        <v>3</v>
-      </c>
-      <c r="P54" s="4">
+      <c r="O54" s="3">
+        <v>3</v>
+      </c>
+      <c r="P54" s="2">
         <v>49</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="5">
+      <c r="R54" s="3">
         <v>1</v>
       </c>
       <c r="AE54" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4705,10 +4093,10 @@
       <c r="F55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="4">
-        <v>1</v>
-      </c>
-      <c r="I55" s="5">
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
         <v>0</v>
       </c>
       <c r="J55">
@@ -4717,26 +4105,26 @@
       <c r="K55">
         <v>1</v>
       </c>
-      <c r="M55" s="4">
+      <c r="M55" s="2">
         <v>9</v>
       </c>
       <c r="N55">
         <v>2</v>
       </c>
-      <c r="O55" s="5">
-        <v>2</v>
-      </c>
-      <c r="P55" s="4">
+      <c r="O55" s="3">
+        <v>2</v>
+      </c>
+      <c r="P55" s="2">
         <v>21</v>
       </c>
       <c r="Q55">
         <v>2</v>
       </c>
-      <c r="R55" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="R55" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4755,10 +4143,10 @@
       <c r="F56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" s="4">
+      <c r="H56" s="2">
         <v>5</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="3">
         <v>5</v>
       </c>
       <c r="J56">
@@ -4770,49 +4158,45 @@
       <c r="L56">
         <v>6</v>
       </c>
-      <c r="M56" s="4">
+      <c r="M56" s="2">
         <v>50</v>
       </c>
       <c r="N56">
         <v>2</v>
       </c>
-      <c r="O56" s="5">
+      <c r="O56" s="3">
         <v>2.5</v>
       </c>
-      <c r="P56" s="4">
+      <c r="P56" s="2">
         <v>51</v>
       </c>
       <c r="Q56">
         <v>0.5</v>
       </c>
-      <c r="R56" s="5">
+      <c r="R56" s="3">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4845,7 +4229,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4861,7 +4245,6 @@
       <c r="I2">
         <v>-1</v>
       </c>
-      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
@@ -5544,7 +4927,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:9">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>34</v>
       </c>
@@ -5570,7 +4953,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:9">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>35</v>
       </c>
@@ -5742,7 +5125,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:9">
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>43</v>
       </c>
@@ -5933,26 +5316,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5991,7 +5372,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6020,7 +5401,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6043,7 +5424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6066,7 +5447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6089,7 +5470,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6112,7 +5493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6135,7 +5516,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6158,7 +5539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
@@ -6181,7 +5562,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:7">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
@@ -6204,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
@@ -6233,7 +5614,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>10</v>
       </c>
@@ -6262,7 +5643,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:7">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>11</v>
       </c>
@@ -6285,7 +5666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>12</v>
       </c>
@@ -6308,7 +5689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>13</v>
       </c>
@@ -6331,7 +5712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>14</v>
       </c>
@@ -6373,7 +5754,7 @@
       <c r="F17">
         <v>46</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>0.1</v>
       </c>
     </row>
@@ -6400,7 +5781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -6417,7 +5798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -6436,24 +5817,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6479,7 +5858,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6499,7 +5878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6516,7 +5895,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" ht="13" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6533,7 +5912,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6553,7 +5932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6573,7 +5952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6593,7 +5972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -6615,7 +5994,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="269">
   <si>
     <t>ID</t>
   </si>
@@ -767,7 +767,7 @@
     <t>专注</t>
   </si>
   <si>
-    <t>积极</t>
+    <t>盐</t>
   </si>
   <si>
     <t>Persistent</t>
@@ -794,7 +794,10 @@
     <t>营业</t>
   </si>
   <si>
-    <t>盐</t>
+    <t>盐应对</t>
+  </si>
+  <si>
+    <t>好娇娇</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -5941,7 +5944,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -6043,7 +6046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6058,12 +6061,6 @@
       </c>
       <c r="E4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -6425,12 +6422,29 @@
         <v>253</v>
       </c>
       <c r="C20" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C21" t="s">
         <v>242</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
         <v>0</v>
       </c>
     </row>
@@ -6467,16 +6481,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6484,13 +6498,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6504,13 +6518,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" t="s">
         <v>261</v>
-      </c>
-      <c r="C3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D3" t="s">
-        <v>260</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -6521,13 +6535,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" t="s">
         <v>263</v>
       </c>
-      <c r="C4" t="s">
-        <v>262</v>
-      </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -6538,13 +6552,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6558,13 +6572,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6578,13 +6592,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6598,13 +6612,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E8">
         <v>3</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="279">
   <si>
     <t>ID</t>
   </si>
@@ -281,495 +281,519 @@
     <t>在有红温的状态下可使用，参数+24</t>
   </si>
   <si>
+    <t>激怒</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
+  </si>
+  <si>
+    <t>美丽动人</t>
+  </si>
+  <si>
+    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
+  </si>
+  <si>
+    <t>小巧思</t>
+  </si>
+  <si>
+    <t>亲和力+5，神采+1</t>
+  </si>
+  <si>
+    <t>冲刺！</t>
+  </si>
+  <si>
+    <t>红温+3，参数+8</t>
+  </si>
+  <si>
+    <t>闭眼</t>
+  </si>
+  <si>
+    <t>专注+3</t>
+  </si>
+  <si>
+    <t>小憩</t>
+  </si>
+  <si>
+    <t>专注+3，神采+4</t>
+  </si>
+  <si>
+    <t>状态火热</t>
+  </si>
+  <si>
+    <t>红温+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
+  </si>
+  <si>
+    <t>躺</t>
+  </si>
+  <si>
+    <t>神采+6</t>
+  </si>
+  <si>
+    <t>惊喜</t>
+  </si>
+  <si>
+    <t>舰长+1，参数+4，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>祝福</t>
+  </si>
+  <si>
+    <t>流水+30，神采+3，体力消耗减少50%+2回合</t>
+  </si>
+  <si>
+    <t>宣传</t>
+  </si>
+  <si>
+    <t>同接+50，神采+2</t>
+  </si>
+  <si>
+    <t>直播通知</t>
+  </si>
+  <si>
+    <t>同接+20，以后，每当打出A卡时，同接+10,</t>
+  </si>
+  <si>
+    <t>爆米</t>
+  </si>
+  <si>
+    <t>获得同接数20%的流水</t>
+  </si>
+  <si>
+    <t>爆！</t>
+  </si>
+  <si>
+    <t>参数+42</t>
+  </si>
+  <si>
+    <t>越想越气</t>
+  </si>
+  <si>
+    <t>有红温的状态下，红温+3</t>
+  </si>
+  <si>
+    <t>欢呼</t>
+  </si>
+  <si>
+    <t>参数+18</t>
+  </si>
+  <si>
+    <t>红温+3，神采+6</t>
+  </si>
+  <si>
+    <t>观察</t>
+  </si>
+  <si>
+    <t>专注+3，神采+6</t>
+  </si>
+  <si>
+    <t>首页推送</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+4回合，神采+3</t>
+  </si>
+  <si>
+    <t>预知梦</t>
+  </si>
+  <si>
+    <t>体力消耗减少1点，神采+5</t>
+  </si>
+  <si>
+    <t>距离感</t>
+  </si>
+  <si>
+    <t>专注+4，体力回复4</t>
+  </si>
+  <si>
+    <t>亲切</t>
+  </si>
+  <si>
+    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
+  </si>
+  <si>
+    <t>最初的神降临</t>
+  </si>
+  <si>
+    <t>专注+1，以后每当打出A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>迷人</t>
+  </si>
+  <si>
+    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
+  </si>
+  <si>
+    <t>申请对线</t>
+  </si>
+  <si>
+    <t>红温+2，之后4回合内，回合结束时，参数+4</t>
+  </si>
+  <si>
+    <t>子弹时间</t>
+  </si>
+  <si>
+    <t>专注+7，体力消耗增加+2回合，神采+7</t>
+  </si>
+  <si>
+    <t>哭唧唧</t>
+  </si>
+  <si>
+    <t>流水+40，同接+30，舰长+1</t>
+  </si>
+  <si>
+    <t>耶！</t>
+  </si>
+  <si>
+    <t>参数+10</t>
+  </si>
+  <si>
+    <t>参数+8，亲和力+3</t>
+  </si>
+  <si>
+    <t>玩梗</t>
+  </si>
+  <si>
+    <t>参数+7，幽默+2</t>
+  </si>
+  <si>
+    <t>盯~</t>
+  </si>
+  <si>
+    <t>亲和力+5，获得亲和力110%的参数</t>
+  </si>
+  <si>
+    <t>氛围感</t>
+  </si>
+  <si>
+    <t>亲和力+1，以后，回合结束时，亲和力+3</t>
+  </si>
+  <si>
+    <t>摘花</t>
+  </si>
+  <si>
+    <t>抽两张牌，体力消耗减少+2回合</t>
+  </si>
+  <si>
+    <t>点炮仗</t>
+  </si>
+  <si>
+    <t>红温&gt;10层时可使用获得红温200%的参数红温减少50%</t>
+  </si>
+  <si>
+    <t>逼逼赖赖</t>
+  </si>
+  <si>
+    <t>红温+3，卡牌使用次数+1，如果红温大于10层，红温+3</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>WhenToApply</t>
+  </si>
+  <si>
+    <t>Condition1</t>
+  </si>
+  <si>
+    <t>Condition2</t>
+  </si>
+  <si>
+    <t>MultiplyByLayer</t>
+  </si>
+  <si>
+    <t>下一张牌使用两次</t>
+  </si>
+  <si>
+    <t>VDoublePlayEffect</t>
+  </si>
+  <si>
+    <t>回合结束时，参数+X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回合结束时，参数+ {AttributeDelta} </t>
+  </si>
+  <si>
+    <t>VAddEffect</t>
+  </si>
+  <si>
+    <t>BAParameter</t>
+  </si>
+  <si>
+    <t>OnTurnEndBuffApply</t>
+  </si>
+  <si>
+    <t>神采+X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神采+ {AttributeDelta} </t>
+  </si>
+  <si>
+    <t>BAShield</t>
+  </si>
+  <si>
+    <t>回合+X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回合+ {AttributeDelta} </t>
+  </si>
+  <si>
+    <t>BATurn</t>
+  </si>
+  <si>
+    <t>重抽手牌</t>
+  </si>
+  <si>
+    <t>重新抽取剩余手牌</t>
+  </si>
+  <si>
+    <t>VRedrawEffect</t>
+  </si>
+  <si>
+    <t>体力消耗削减X点</t>
+  </si>
+  <si>
+    <t>VShieldStaminaModifierEffect</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>亲和力+X</t>
+  </si>
+  <si>
+    <t>VBuffModifyEffect</t>
+  </si>
+  <si>
+    <t>专注+X</t>
+  </si>
+  <si>
+    <t>积极+X</t>
+  </si>
+  <si>
+    <t>抽X张卡牌</t>
+  </si>
+  <si>
+    <t>VDrawCardEffect</t>
+  </si>
+  <si>
+    <t>从抽牌堆选择卡牌</t>
+  </si>
+  <si>
+    <t>VPickCardFromPileEffect</t>
+  </si>
+  <si>
+    <t>DrawPile</t>
+  </si>
+  <si>
+    <t>参数+X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参数+ {AttributeDelta} </t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力-X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回合结束时，亲和力-{AttributeDelta} </t>
+  </si>
+  <si>
+    <t>参数获得量增加X%</t>
+  </si>
+  <si>
+    <t>VAttributeGainRateModifierEffect</t>
+  </si>
+  <si>
+    <t>手牌使用次数+X</t>
+  </si>
+  <si>
+    <t>BAPlayLeft</t>
+  </si>
+  <si>
+    <t>红温+X</t>
+  </si>
+  <si>
+    <t>参数获得量+X</t>
+  </si>
+  <si>
+    <t>VAttributeGainPointsModifierEffect</t>
+  </si>
+  <si>
+    <t>沉浸+X</t>
+  </si>
+  <si>
+    <t>亲和力X%的参数获得</t>
+  </si>
+  <si>
+    <t>VAddParamsBuffPercentageEffect</t>
+  </si>
+  <si>
+    <t>舰长+X</t>
+  </si>
+  <si>
+    <t>BAMembershipCount</t>
+  </si>
+  <si>
+    <t>体力消耗减少X%</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%+X回合</t>
+  </si>
+  <si>
+    <t>回合结束时，专注+X</t>
+  </si>
+  <si>
+    <t>以后回合结束时专注+X</t>
+  </si>
+  <si>
+    <t>在有红温时，参数+X</t>
+  </si>
+  <si>
+    <t>体力消耗增加X%</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%+X回合</t>
+  </si>
+  <si>
+    <t>每当使用M卡时，亲和力+X</t>
+  </si>
+  <si>
+    <t>OnCardPlayed</t>
+  </si>
+  <si>
+    <t>每当使用M卡亲和力+1</t>
+  </si>
+  <si>
+    <t>每当使用M卡时，亲和力+1</t>
+  </si>
+  <si>
+    <t>回合开始时，参数+X</t>
+  </si>
+  <si>
+    <t>OnTurnBeginBuffApply</t>
+  </si>
+  <si>
+    <t>下一回合开始时，参数+18</t>
+  </si>
+  <si>
+    <t>下下回合开始时，参数+24</t>
+  </si>
+  <si>
+    <t>流水+X</t>
+  </si>
+  <si>
+    <t>BARevenue</t>
+  </si>
+  <si>
+    <t>同接+X</t>
+  </si>
+  <si>
+    <t>BAViewerCount</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，同接+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡同接+10</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，同接+10</t>
+  </si>
+  <si>
+    <t>获得同接数X%的流水</t>
+  </si>
+  <si>
+    <t>有红温时，专注+X</t>
+  </si>
+  <si>
+    <t>体力回复X点</t>
+  </si>
+  <si>
+    <t>BAStamina</t>
+  </si>
+  <si>
+    <t>亲和力大于3层时，亲和力+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，专注+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，专注+1</t>
+  </si>
+  <si>
+    <t>之后X回合内，回合结束时，参数+X</t>
+  </si>
+  <si>
+    <t>获得X回合，回合结束时，参数+4</t>
+  </si>
+  <si>
+    <t>神采获得量增加X</t>
+  </si>
+  <si>
+    <t>幽默+X</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力变为X倍</t>
+  </si>
+  <si>
+    <t>VBuffAddPercentageEffect</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力变为1.1倍</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力+X</t>
+  </si>
+  <si>
+    <t>回合结束时，亲和力+3</t>
+  </si>
+  <si>
+    <t>获得红温X%的参数</t>
+  </si>
+  <si>
+    <t>减少X%的红温</t>
+  </si>
+  <si>
+    <t>红温大于10层时，红温+X</t>
+  </si>
+  <si>
+    <t>红温大于10层时，参数获得量+X%</t>
+  </si>
+  <si>
+    <t>红温大于30层时，参数获得量+X%</t>
+  </si>
+  <si>
+    <t>红温大于50层时，参数获得量+X%</t>
+  </si>
+  <si>
+    <t>红温大于50层时，大于50层的部分每层红温会使参数获得量+5%</t>
+  </si>
+  <si>
+    <t>BuffType</t>
+  </si>
+  <si>
+    <t>Stackable</t>
+  </si>
+  <si>
+    <t>Latency</t>
+  </si>
+  <si>
+    <t>亲和力</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
     <t>红温</t>
   </si>
   <si>
-    <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
-  </si>
-  <si>
-    <t>美丽动人</t>
-  </si>
-  <si>
-    <t>亲和力+2，以后，每当使用M卡时，亲和力+1</t>
-  </si>
-  <si>
-    <t>小巧思</t>
-  </si>
-  <si>
-    <t>亲和力+5，神采+1</t>
-  </si>
-  <si>
-    <t>冲刺！</t>
-  </si>
-  <si>
-    <t>红温+3，参数+8</t>
-  </si>
-  <si>
-    <t>闭眼</t>
-  </si>
-  <si>
-    <t>专注+3</t>
-  </si>
-  <si>
-    <t>小憩</t>
-  </si>
-  <si>
-    <t>专注+3，神采+4</t>
-  </si>
-  <si>
-    <t>状态火热</t>
-  </si>
-  <si>
-    <t>红温+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
-  </si>
-  <si>
-    <t>躺</t>
-  </si>
-  <si>
-    <t>神采+6</t>
-  </si>
-  <si>
-    <t>惊喜</t>
-  </si>
-  <si>
-    <t>舰长+1，参数+4，卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>祝福</t>
-  </si>
-  <si>
-    <t>流水+30，神采+3，体力消耗减少50%+2回合</t>
-  </si>
-  <si>
-    <t>宣传</t>
-  </si>
-  <si>
-    <t>同接+50，神采+2</t>
-  </si>
-  <si>
-    <t>直播通知</t>
-  </si>
-  <si>
-    <t>同接+20，以后，每当打出A卡时，同接+10,</t>
-  </si>
-  <si>
-    <t>爆米</t>
-  </si>
-  <si>
-    <t>获得同接数20%的流水</t>
-  </si>
-  <si>
-    <t>爆！</t>
-  </si>
-  <si>
-    <t>参数+42</t>
-  </si>
-  <si>
-    <t>越想越气</t>
-  </si>
-  <si>
-    <t>有红温的状态下，专注+1，红温+3</t>
-  </si>
-  <si>
-    <t>欢呼</t>
-  </si>
-  <si>
-    <t>参数+18</t>
-  </si>
-  <si>
-    <t>红温+3，神采+6</t>
-  </si>
-  <si>
-    <t>观察</t>
-  </si>
-  <si>
-    <t>专注+3，神采+6</t>
-  </si>
-  <si>
-    <t>首页推送</t>
-  </si>
-  <si>
-    <t>体力消耗减少50%+4回合，神采+3</t>
-  </si>
-  <si>
-    <t>预知梦</t>
-  </si>
-  <si>
-    <t>体力消耗减少1点，神采+5</t>
-  </si>
-  <si>
-    <t>距离感</t>
-  </si>
-  <si>
-    <t>专注+4，体力回复4</t>
-  </si>
-  <si>
-    <t>亲切</t>
-  </si>
-  <si>
-    <t>亲和力+3，亲和力大于三层时，亲和力+2</t>
-  </si>
-  <si>
-    <t>最初的神降临</t>
-  </si>
-  <si>
-    <t>专注+1，以后每当打出A卡时，专注+1</t>
-  </si>
-  <si>
-    <t>迷人</t>
-  </si>
-  <si>
-    <t>亲和力+5，卡牌使用次数+1，获得亲和力90%的参数</t>
-  </si>
-  <si>
-    <t>申请对线</t>
-  </si>
-  <si>
-    <t>红温+2，之后4回合内，回合结束时，参数+4</t>
-  </si>
-  <si>
-    <t>子弹时间</t>
-  </si>
-  <si>
-    <t>专注+7，体力消耗增加+2回合，神采+7</t>
-  </si>
-  <si>
-    <t>哭唧唧</t>
-  </si>
-  <si>
-    <t>流水+40，同接+30，舰长+1</t>
-  </si>
-  <si>
-    <t>耶！</t>
-  </si>
-  <si>
-    <t>参数+10</t>
-  </si>
-  <si>
-    <t>参数+8，亲和力+3</t>
-  </si>
-  <si>
-    <t>应援</t>
-  </si>
-  <si>
-    <t>参数+7，幽默+2</t>
-  </si>
-  <si>
-    <t>盯~</t>
-  </si>
-  <si>
-    <t>亲和力+5，获得亲和力110%的参数</t>
-  </si>
-  <si>
-    <t>氛围感</t>
-  </si>
-  <si>
-    <t>亲和力+1，以后，回合结束时，亲和力+3</t>
-  </si>
-  <si>
-    <t>摘花</t>
-  </si>
-  <si>
-    <t>抽两张牌，体力消耗减少+2回合</t>
-  </si>
-  <si>
-    <t>点炮仗</t>
-  </si>
-  <si>
-    <t>红温&gt;10层时可使用，获得红温200%的参数，红温减少50%</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>WhenToApply</t>
-  </si>
-  <si>
-    <t>Condition1</t>
-  </si>
-  <si>
-    <t>Condition2</t>
-  </si>
-  <si>
-    <t>MultiplyByLayer</t>
-  </si>
-  <si>
-    <t>下一张牌使用两次</t>
-  </si>
-  <si>
-    <t>VDoublePlayEffect</t>
-  </si>
-  <si>
-    <t>回合结束时，参数+X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回合结束时，参数+ {AttributeDelta} </t>
-  </si>
-  <si>
-    <t>VAddEffect</t>
-  </si>
-  <si>
-    <t>BAParameter</t>
-  </si>
-  <si>
-    <t>OnTurnEndBuffApply</t>
-  </si>
-  <si>
-    <t>神采+X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神采+ {AttributeDelta} </t>
-  </si>
-  <si>
-    <t>BAShield</t>
-  </si>
-  <si>
-    <t>回合+X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回合+ {AttributeDelta} </t>
-  </si>
-  <si>
-    <t>BATurn</t>
-  </si>
-  <si>
-    <t>重抽手牌</t>
-  </si>
-  <si>
-    <t>重新抽取剩余手牌</t>
-  </si>
-  <si>
-    <t>VRedrawEffect</t>
-  </si>
-  <si>
-    <t>体力消耗削减X点</t>
-  </si>
-  <si>
-    <t>VShieldStaminaModifierEffect</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>亲和力+X</t>
-  </si>
-  <si>
-    <t>VBuffModifyEffect</t>
-  </si>
-  <si>
-    <t>专注+X</t>
-  </si>
-  <si>
-    <t>积极+X</t>
-  </si>
-  <si>
-    <t>抽X张卡牌</t>
-  </si>
-  <si>
-    <t>VDrawCardEffect</t>
-  </si>
-  <si>
-    <t>从抽牌堆选择卡牌</t>
-  </si>
-  <si>
-    <t>VPickCardFromPileEffect</t>
-  </si>
-  <si>
-    <t>DrawPile</t>
-  </si>
-  <si>
-    <t>参数+X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参数+ {AttributeDelta} </t>
-  </si>
-  <si>
-    <t>回合结束时，亲和力-X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回合结束时，亲和力-{AttributeDelta} </t>
-  </si>
-  <si>
-    <t>参数获得量增加X%</t>
-  </si>
-  <si>
-    <t>VAttributeGainRateModifierEffect</t>
-  </si>
-  <si>
-    <t>手牌使用次数+X</t>
-  </si>
-  <si>
-    <t>BAPlayLeft</t>
-  </si>
-  <si>
-    <t>红温+X</t>
-  </si>
-  <si>
-    <t>参数获得量+X</t>
-  </si>
-  <si>
-    <t>VAttributeGainPointsModifierEffect</t>
-  </si>
-  <si>
-    <t>沉浸+X</t>
-  </si>
-  <si>
-    <t>亲和力X%的参数获得</t>
-  </si>
-  <si>
-    <t>VAddParamsBuffPercentageEffect</t>
-  </si>
-  <si>
-    <t>舰长+X</t>
-  </si>
-  <si>
-    <t>BAMembershipCount</t>
-  </si>
-  <si>
-    <t>体力消耗减少X%</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>体力消耗减少50%+X回合</t>
-  </si>
-  <si>
-    <t>回合结束时，专注+X</t>
-  </si>
-  <si>
-    <t>以后回合结束时专注+X</t>
-  </si>
-  <si>
-    <t>在有红温时，参数+X</t>
-  </si>
-  <si>
-    <t>体力消耗增加X%</t>
-  </si>
-  <si>
-    <t>体力消耗增加50%+X回合</t>
-  </si>
-  <si>
-    <t>每当使用M卡时，亲和力+X</t>
-  </si>
-  <si>
-    <t>OnCardPlayed</t>
-  </si>
-  <si>
-    <t>每当使用M卡亲和力+1</t>
-  </si>
-  <si>
-    <t>每当使用M卡时，亲和力+1</t>
-  </si>
-  <si>
-    <t>回合开始时，参数+X</t>
-  </si>
-  <si>
-    <t>OnTurnBeginBuffApply</t>
-  </si>
-  <si>
-    <t>下一回合开始时，参数+18</t>
-  </si>
-  <si>
-    <t>下下回合开始时，参数+24</t>
-  </si>
-  <si>
-    <t>流水+X</t>
-  </si>
-  <si>
-    <t>BARevenue</t>
-  </si>
-  <si>
-    <t>同接+X</t>
-  </si>
-  <si>
-    <t>BAViewerCount</t>
-  </si>
-  <si>
-    <t>每当使用A卡时，同接+X</t>
-  </si>
-  <si>
-    <t>每当使用A卡同接+10</t>
-  </si>
-  <si>
-    <t>每当使用A卡时，同接+10</t>
-  </si>
-  <si>
-    <t>获得同接数X%的流水</t>
-  </si>
-  <si>
-    <t>有红温时，专注+X</t>
-  </si>
-  <si>
-    <t>体力回复X点</t>
-  </si>
-  <si>
-    <t>BAStamina</t>
-  </si>
-  <si>
-    <t>亲和力大于3层时，亲和力+X</t>
-  </si>
-  <si>
-    <t>每当使用A卡时，专注+X</t>
-  </si>
-  <si>
-    <t>每当使用A卡时，专注+1</t>
-  </si>
-  <si>
-    <t>之后X回合内，回合结束时，参数+X</t>
-  </si>
-  <si>
-    <t>获得X回合，回合结束时，参数+4</t>
-  </si>
-  <si>
-    <t>神采获得量增加X</t>
-  </si>
-  <si>
-    <t>幽默+X</t>
-  </si>
-  <si>
-    <t>回合结束时，亲和力变为X倍</t>
-  </si>
-  <si>
-    <t>VBuffAddPercentageEffect</t>
-  </si>
-  <si>
-    <t>回合结束时，亲和力变为1.1倍</t>
-  </si>
-  <si>
-    <t>回合结束时，亲和力+X</t>
-  </si>
-  <si>
-    <t>回合结束时，亲和力+3</t>
-  </si>
-  <si>
-    <t>获得红温X%的参数</t>
-  </si>
-  <si>
-    <t>减少X%的红温</t>
-  </si>
-  <si>
-    <t>BuffType</t>
-  </si>
-  <si>
-    <t>Stackable</t>
-  </si>
-  <si>
-    <t>Latency</t>
-  </si>
-  <si>
-    <t>亲和力</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>专注</t>
-  </si>
-  <si>
-    <t>盐</t>
-  </si>
-  <si>
     <t>Persistent</t>
   </si>
   <si>
@@ -840,6 +864,12 @@
   </si>
   <si>
     <t>当红温大于10层时</t>
+  </si>
+  <si>
+    <t>当红温大于30层时</t>
+  </si>
+  <si>
+    <t>当红温大于50层时</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1507,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1486,6 +1516,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1806,8 +1839,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AE56"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -1931,7 +1964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" hidden="1" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1971,12 +2004,12 @@
       <c r="O2" s="5">
         <v>7</v>
       </c>
-      <c r="AC2" s="6"/>
+      <c r="AC2" s="7"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" hidden="1" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2016,12 +2049,12 @@
       <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="AC3" s="6"/>
+      <c r="AC3" s="7"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" hidden="1" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2061,12 +2094,12 @@
       <c r="O4" s="5">
         <v>15</v>
       </c>
-      <c r="AC4" s="6"/>
+      <c r="AC4" s="7"/>
       <c r="AE4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" hidden="1" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2115,12 +2148,12 @@
       <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="AC5" s="6"/>
+      <c r="AC5" s="7"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" hidden="1" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2157,12 +2190,12 @@
       <c r="M6" s="4">
         <v>0</v>
       </c>
-      <c r="AC6" s="6"/>
+      <c r="AC6" s="7"/>
       <c r="AE6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" hidden="1" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2196,12 +2229,12 @@
       <c r="M7" s="4">
         <v>4</v>
       </c>
-      <c r="AC7" s="6"/>
+      <c r="AC7" s="7"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" hidden="1" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2262,12 +2295,12 @@
       <c r="U8" s="5">
         <v>1</v>
       </c>
-      <c r="AC8" s="6"/>
+      <c r="AC8" s="7"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" hidden="1" spans="1:31">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2316,12 +2349,12 @@
       <c r="R9" s="5">
         <v>6</v>
       </c>
-      <c r="AC9" s="6"/>
+      <c r="AC9" s="7"/>
       <c r="AE9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" hidden="1" spans="1:31">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2370,12 +2403,12 @@
       <c r="R10" s="5">
         <v>4</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="7"/>
       <c r="AE10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" hidden="1" spans="1:31">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2424,7 +2457,7 @@
       <c r="R11" s="5">
         <v>3</v>
       </c>
-      <c r="AC11" s="6"/>
+      <c r="AC11" s="7"/>
       <c r="AE11" t="s">
         <v>52</v>
       </c>
@@ -2478,12 +2511,12 @@
       <c r="R12" s="5">
         <v>3</v>
       </c>
-      <c r="AC12" s="6"/>
+      <c r="AC12" s="7"/>
       <c r="AE12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" hidden="1" spans="1:31">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2532,7 +2565,7 @@
       <c r="R13" s="5">
         <v>13</v>
       </c>
-      <c r="AC13" s="6"/>
+      <c r="AC13" s="7"/>
       <c r="AD13" t="s">
         <v>64</v>
       </c>
@@ -2540,7 +2573,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" hidden="1" spans="1:31">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2589,12 +2622,12 @@
       <c r="R14" s="5">
         <v>9</v>
       </c>
-      <c r="AC14" s="6"/>
+      <c r="AC14" s="7"/>
       <c r="AE14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" hidden="1" spans="1:31">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2634,12 +2667,12 @@
       <c r="O15" s="5">
         <v>8</v>
       </c>
-      <c r="AC15" s="6"/>
+      <c r="AC15" s="7"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" hidden="1" spans="1:31">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2679,12 +2712,12 @@
       <c r="O16" s="5">
         <v>1.8</v>
       </c>
-      <c r="AC16" s="6"/>
+      <c r="AC16" s="7"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" hidden="1" spans="1:31">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2733,12 +2766,12 @@
       <c r="R17" s="5">
         <v>1.1</v>
       </c>
-      <c r="AC17" s="6"/>
+      <c r="AC17" s="7"/>
       <c r="AE17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" hidden="1" spans="1:31">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2796,12 +2829,12 @@
       <c r="U18" s="5">
         <v>3</v>
       </c>
-      <c r="AC18" s="7"/>
+      <c r="AC18" s="8"/>
       <c r="AE18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" hidden="1" spans="1:31">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2835,7 +2868,7 @@
       <c r="M19" s="4">
         <v>0</v>
       </c>
-      <c r="AC19" s="6"/>
+      <c r="AC19" s="7"/>
       <c r="AE19" t="s">
         <v>35</v>
       </c>
@@ -2880,12 +2913,12 @@
       <c r="O20" s="5">
         <v>7</v>
       </c>
-      <c r="AC20" s="6"/>
+      <c r="AC20" s="7"/>
       <c r="AE20" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" hidden="1" spans="1:31">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2934,7 +2967,7 @@
       <c r="R21" s="5">
         <v>2</v>
       </c>
-      <c r="AC21" s="6"/>
+      <c r="AC21" s="7"/>
       <c r="AE21" t="s">
         <v>52</v>
       </c>
@@ -2970,8 +3003,11 @@
       <c r="K22">
         <v>0</v>
       </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
       <c r="M22" s="4">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N22">
         <v>24</v>
@@ -2979,7 +3015,7 @@
       <c r="O22" s="5">
         <v>30</v>
       </c>
-      <c r="AC22" s="7"/>
+      <c r="AC22" s="8"/>
       <c r="AE22" t="s">
         <v>61</v>
       </c>
@@ -3042,12 +3078,12 @@
       <c r="U23" s="5">
         <v>7</v>
       </c>
-      <c r="AC23" s="6"/>
+      <c r="AC23" s="7"/>
       <c r="AE23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" hidden="1" spans="1:31">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3096,12 +3132,12 @@
       <c r="R24" s="5">
         <v>1</v>
       </c>
-      <c r="AC24" s="6"/>
+      <c r="AC24" s="7"/>
       <c r="AE24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" hidden="1" spans="1:31">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3150,7 +3186,7 @@
       <c r="R25" s="5">
         <v>1</v>
       </c>
-      <c r="AC25" s="6"/>
+      <c r="AC25" s="7"/>
       <c r="AE25" t="s">
         <v>33</v>
       </c>
@@ -3204,12 +3240,12 @@
       <c r="R26" s="5">
         <v>11</v>
       </c>
-      <c r="AC26" s="6"/>
+      <c r="AC26" s="7"/>
       <c r="AE26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" hidden="1" spans="1:31">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3249,12 +3285,12 @@
       <c r="O27" s="5">
         <v>5</v>
       </c>
-      <c r="AC27" s="6"/>
+      <c r="AC27" s="7"/>
       <c r="AE27" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" hidden="1" spans="1:31">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3303,7 +3339,7 @@
       <c r="R28" s="5">
         <v>6</v>
       </c>
-      <c r="AC28" s="6"/>
+      <c r="AC28" s="7"/>
       <c r="AE28" t="s">
         <v>52</v>
       </c>
@@ -3366,12 +3402,12 @@
       <c r="U29" s="5">
         <v>1</v>
       </c>
-      <c r="AC29" s="7"/>
+      <c r="AC29" s="8"/>
       <c r="AE29" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" hidden="1" spans="1:31">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3411,12 +3447,12 @@
       <c r="O30" s="5">
         <v>8</v>
       </c>
-      <c r="AC30" s="6"/>
+      <c r="AC30" s="7"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" hidden="1" spans="1:31">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3474,12 +3510,12 @@
       <c r="U31" s="5">
         <v>1</v>
       </c>
-      <c r="AC31" s="7"/>
+      <c r="AC31" s="8"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" hidden="1" spans="1:31">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3537,12 +3573,12 @@
       <c r="U32" s="5">
         <v>3</v>
       </c>
-      <c r="AC32" s="6"/>
+      <c r="AC32" s="7"/>
       <c r="AE32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" hidden="1" spans="1:31">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3591,12 +3627,12 @@
       <c r="R33" s="5">
         <v>4</v>
       </c>
-      <c r="AC33" s="7"/>
+      <c r="AC33" s="8"/>
       <c r="AE33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" hidden="1" spans="1:31">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3645,12 +3681,12 @@
       <c r="R34" s="5">
         <v>1</v>
       </c>
-      <c r="AC34" s="7"/>
+      <c r="AC34" s="8"/>
       <c r="AE34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" hidden="1" spans="1:31">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3760,29 +3796,23 @@
       <c r="K37">
         <v>0</v>
       </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
       <c r="M37" s="4">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" s="5">
-        <v>2</v>
-      </c>
-      <c r="P37" s="4">
-        <v>15</v>
-      </c>
-      <c r="Q37">
-        <v>3</v>
-      </c>
-      <c r="R37" s="5">
         <v>4</v>
       </c>
       <c r="AE37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="1:31">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3830,7 +3860,7 @@
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="6">
         <v>144</v>
       </c>
       <c r="C39" t="s">
@@ -3879,7 +3909,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" hidden="1" spans="1:31">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3932,7 +3962,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" hidden="1" spans="1:31">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3985,7 +4015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" hidden="1" spans="1:31">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4038,7 +4068,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" hidden="1" spans="1:31">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4091,7 +4121,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" hidden="1" spans="1:31">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4144,7 +4174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" hidden="1" spans="1:31">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4197,7 +4227,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" hidden="1" spans="1:31">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4312,7 +4342,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" hidden="1" spans="1:31">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4374,7 +4404,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" hidden="1" spans="1:31">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4436,7 +4466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" hidden="1" spans="1:31">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4480,7 +4510,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" hidden="1" spans="1:31">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4583,7 +4613,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" hidden="1" spans="1:31">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4636,7 +4666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" hidden="1" spans="1:31">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4689,7 +4719,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4738,8 +4768,11 @@
       <c r="R55" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="AE55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4786,14 +4819,84 @@
         <v>51</v>
       </c>
       <c r="Q56">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R56" s="5">
-        <v>0.5</v>
+        <v>-0.5</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="2:31">
+      <c r="B57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" t="s">
+        <v>49</v>
+      </c>
+      <c r="E57" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57" s="4">
+        <v>2</v>
+      </c>
+      <c r="I57" s="5">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="M57" s="4">
+        <v>15</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57" s="5">
+        <v>4</v>
+      </c>
+      <c r="P57" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="R57" s="5">
+        <v>1</v>
+      </c>
+      <c r="S57" s="4">
+        <v>52</v>
+      </c>
+      <c r="T57">
+        <v>3</v>
+      </c>
+      <c r="U57" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="30">
+      <filters blank="1">
+        <filter val="C"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4805,7 +4908,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4833,19 +4936,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4853,13 +4956,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4871,19 +4974,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4894,16 +4997,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4914,16 +5017,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4934,13 +5037,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4951,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4971,13 +5074,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4991,13 +5094,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5011,13 +5114,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" t="s">
         <v>175</v>
-      </c>
-      <c r="C10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" t="s">
-        <v>173</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5031,13 +5134,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5048,16 +5151,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5068,16 +5171,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5088,19 +5191,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5111,16 +5214,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5131,16 +5234,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5151,13 +5254,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5171,16 +5274,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5191,13 +5294,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5211,13 +5314,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5231,16 +5334,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5251,16 +5354,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5271,13 +5374,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5291,19 +5394,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5314,13 +5417,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5334,16 +5437,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5357,16 +5460,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5377,13 +5480,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5397,19 +5500,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5423,13 +5526,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5443,19 +5546,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5466,19 +5569,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5489,19 +5592,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5512,16 +5615,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5532,16 +5635,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5552,19 +5655,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5578,13 +5681,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5598,16 +5701,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5618,13 +5721,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5641,16 +5744,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E40" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5661,13 +5764,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5684,19 +5787,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5710,13 +5813,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5730,13 +5833,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5750,19 +5853,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5773,16 +5876,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5793,13 +5896,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5813,19 +5916,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5836,13 +5939,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -5856,19 +5959,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -5879,13 +5982,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -5899,13 +6002,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D52" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -5919,18 +6022,110 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="I53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D55" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" t="s">
+        <v>160</v>
+      </c>
+      <c r="G55">
+        <v>6</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" t="s">
+        <v>242</v>
+      </c>
+      <c r="D56" t="s">
+        <v>188</v>
+      </c>
+      <c r="E56" t="s">
+        <v>160</v>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="I56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" t="s">
+        <v>244</v>
+      </c>
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="I57">
         <v>-1</v>
       </c>
     </row>
@@ -5967,13 +6162,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -5999,10 +6194,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6028,10 +6223,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6051,10 +6246,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6063,15 +6258,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6083,6 +6278,18 @@
         <v>13</v>
       </c>
       <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>53</v>
+      </c>
+      <c r="I5">
+        <v>0.5</v>
+      </c>
+      <c r="J5">
+        <v>54</v>
+      </c>
+      <c r="K5">
         <v>0.5</v>
       </c>
     </row>
@@ -6091,10 +6298,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6114,10 +6321,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6137,10 +6344,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6160,10 +6367,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6183,10 +6390,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6206,10 +6413,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6235,10 +6442,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6264,10 +6471,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6287,10 +6494,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6310,10 +6517,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6333,10 +6540,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C16" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6356,10 +6563,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6379,10 +6586,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6402,10 +6609,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6419,10 +6626,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" t="s">
         <v>253</v>
-      </c>
-      <c r="C20" t="s">
-        <v>245</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6436,10 +6643,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6458,8 +6665,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
     <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
@@ -6481,16 +6688,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="G1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6498,13 +6705,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6518,13 +6725,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -6535,13 +6742,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -6552,13 +6759,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6572,13 +6779,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6592,13 +6799,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6612,19 +6819,59 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" t="s">
         <v>268</v>
       </c>
-      <c r="C8" t="s">
-        <v>260</v>
-      </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
         <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3CB174-B493-41F6-87CB-55A3FEE172D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74C98BE-B780-4652-BCFB-6A55DE563D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="270">
   <si>
     <t>ID</t>
   </si>
@@ -843,6 +841,12 @@
   </si>
   <si>
     <t>当红温大于10层时</t>
+  </si>
+  <si>
+    <t>Effect5</t>
+  </si>
+  <si>
+    <t>E5Param</t>
   </si>
 </sst>
 </file>
@@ -1193,35 +1197,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="44.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="44.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.1796875" customWidth="1"/>
+    <col min="15" max="15" width="17.7265625" style="3" customWidth="1"/>
     <col min="16" max="16" width="11" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.26953125" customWidth="1"/>
+    <col min="18" max="18" width="17.1796875" style="3" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7265625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7265625" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.28515625" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" customWidth="1"/>
+    <col min="24" max="24" width="17.7265625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.453125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.453125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.26953125" customWidth="1"/>
+    <col min="29" max="29" width="4.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -4187,16 +4191,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5322,22 +5326,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5371,8 +5375,20 @@
       <c r="K1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5401,7 +5417,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5424,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5447,7 +5463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5470,7 +5486,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5493,7 +5509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5516,7 +5532,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5539,7 +5555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5562,7 +5578,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5585,7 +5601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5614,7 +5630,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5643,7 +5659,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5666,7 +5682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5689,7 +5705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5712,7 +5728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5817,22 +5833,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5878,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.95" customHeight="1">
+    <row r="3" spans="1:7" ht="13" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5895,7 +5911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.95" customHeight="1">
+    <row r="4" spans="1:7" ht="13" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74C98BE-B780-4652-BCFB-6A55DE563D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8EAD07-B57A-4215-A3E3-99C55092F7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
     <sheet name="Effects" sheetId="2" r:id="rId2"/>
     <sheet name="Buffs" sheetId="3" r:id="rId3"/>
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
+    <sheet name="RaisingEffects" sheetId="5" r:id="rId5"/>
+    <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="272">
   <si>
     <t>ID</t>
   </si>
@@ -847,6 +849,12 @@
   </si>
   <si>
     <t>E5Param</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
   </si>
 </sst>
 </file>
@@ -1197,35 +1205,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="3" max="3" width="44.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="7.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" customWidth="1"/>
-    <col min="11" max="11" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.1796875" customWidth="1"/>
-    <col min="15" max="15" width="17.7265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
     <col min="16" max="16" width="11" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.26953125" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="21" max="21" width="17.7265625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.7265625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7265625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12.453125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.453125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.26953125" customWidth="1"/>
-    <col min="29" max="29" width="4.26953125" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -4191,16 +4199,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="8" width="10.26953125" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5320,24 +5328,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.453125" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5840,15 +5848,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5894,7 +5902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13" customHeight="1">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5911,7 +5919,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13" customHeight="1">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6012,4 +6020,50 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B963FD-B399-4A5F-A7EE-C698A9110DBE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8EAD07-B57A-4215-A3E3-99C55092F7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3389E295-0CD1-4980-8DBC-C1F272A18743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="275">
   <si>
     <t>ID</t>
   </si>
@@ -851,10 +851,19 @@
     <t>E5Param</t>
   </si>
   <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>Param2</t>
+    <t>Param</t>
+  </si>
+  <si>
+    <t>asfkldsajfklsd</t>
+  </si>
+  <si>
+    <t>safdsafsadfasdf</t>
+  </si>
+  <si>
+    <t>VRaisingAddAbilityEffect</t>
+  </si>
+  <si>
+    <t>CASingingAbility</t>
   </si>
 </sst>
 </file>
@@ -6024,38 +6033,60 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>270</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>271</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3389E295-0CD1-4980-8DBC-C1F272A18743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D7ED88-B76F-4F31-8975-5EBD0106BDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
     <sheet name="RaisingEffects" sheetId="5" r:id="rId5"/>
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
+    <sheet name="DialogueEvents" sheetId="7" r:id="rId7"/>
+    <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="305">
   <si>
     <t>ID</t>
   </si>
@@ -854,9 +856,6 @@
     <t>Param</t>
   </si>
   <si>
-    <t>asfkldsajfklsd</t>
-  </si>
-  <si>
     <t>safdsafsadfasdf</t>
   </si>
   <si>
@@ -864,13 +863,106 @@
   </si>
   <si>
     <t>CASingingAbility</t>
+  </si>
+  <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>AddSinging</t>
+  </si>
+  <si>
+    <t>AddGaming</t>
+  </si>
+  <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>AddStamina</t>
+  </si>
+  <si>
+    <t>CAGamingAbility</t>
+  </si>
+  <si>
+    <t>CAChattingAbility</t>
+  </si>
+  <si>
+    <t>VRaisingAddAttributeEffect</t>
+  </si>
+  <si>
+    <t>CAStamina</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Stream1</t>
+  </si>
+  <si>
+    <t>Stream2</t>
+  </si>
+  <si>
+    <t>Stream3</t>
+  </si>
+  <si>
+    <t>DayOff!</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>Recover 10 Stamina</t>
+  </si>
+  <si>
+    <t>Recover 20 Stamina</t>
+  </si>
+  <si>
+    <t>Recover 30 Stamina</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>BackGroundColor</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>#AB0580</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>TurnCount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -878,8 +970,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -895,6 +1000,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF2160"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4B58FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB200"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB0580"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -929,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -938,12 +1073,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1214,35 +1365,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="44.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="44.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.1796875" customWidth="1"/>
+    <col min="15" max="15" width="17.7265625" style="3" customWidth="1"/>
     <col min="16" max="16" width="11" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.26953125" customWidth="1"/>
+    <col min="18" max="18" width="17.1796875" style="3" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7265625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7265625" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.28515625" customWidth="1"/>
-    <col min="29" max="29" width="4.28515625" customWidth="1"/>
+    <col min="24" max="24" width="17.7265625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.453125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.453125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.26953125" customWidth="1"/>
+    <col min="29" max="29" width="4.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -4201,23 +4352,23 @@
   </sheetData>
   <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" customWidth="1"/>
+    <col min="7" max="8" width="10.26953125" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5344,17 +5495,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5857,15 +6008,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5911,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.95" customHeight="1">
+    <row r="3" spans="1:7" ht="13" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5928,7 +6079,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.95" customHeight="1">
+    <row r="4" spans="1:7" ht="13" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6033,15 +6184,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6069,19 +6220,76 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" t="s">
         <v>271</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>272</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>273</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>274</v>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -6093,8 +6301,407 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B963FD-B399-4A5F-A7EE-C698A9110DBE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F843A941-2090-4EA2-92B0-02A8CDB751AA}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" customWidth="1"/>
+    <col min="6" max="6" width="8.36328125" customWidth="1"/>
+    <col min="7" max="7" width="5.7265625" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="16.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="J2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="J4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>284</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AA25C0-E9A0-4DAC-9454-4255D17FAEDC}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="22.26953125" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="6.7265625" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D7ED88-B76F-4F31-8975-5EBD0106BDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DCB856-4F87-438E-9FD0-8798FB7101B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9285" yWindow="2265" windowWidth="25575" windowHeight="13665" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="326">
   <si>
     <t>ID</t>
   </si>
@@ -956,18 +956,95 @@
   </si>
   <si>
     <t>TurnCount</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>SuccessEvent</t>
+  </si>
+  <si>
+    <t>FailEvent</t>
+  </si>
+  <si>
+    <t>InitialViewers</t>
+  </si>
+  <si>
+    <t>AddPressure</t>
+  </si>
+  <si>
+    <t>Add Pressure</t>
+  </si>
+  <si>
+    <t>CAPressure</t>
+  </si>
+  <si>
+    <t>Add Money</t>
+  </si>
+  <si>
+    <t>CAMoney</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
+    <t>AddMoney</t>
+  </si>
+  <si>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>NoStamina</t>
+  </si>
+  <si>
+    <t>SkipEvent</t>
+  </si>
+  <si>
+    <t>VRaisingSkipEventEffect</t>
+  </si>
+  <si>
+    <t>VRaisingModifyScheduleEffect</t>
+  </si>
+  <si>
+    <t>ModifySchedule</t>
+  </si>
+  <si>
+    <t>OuttaStamina</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1064,7 +1141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1073,12 +1150,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1087,9 +1167,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFFF"/>
       <color rgb="FFAB0580"/>
       <color rgb="FF00B050"/>
-      <color rgb="FFFFFFFF"/>
       <color rgb="FFFFB200"/>
       <color rgb="FF4B58FF"/>
       <color rgb="FFFF2160"/>
@@ -1365,35 +1445,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="3" max="3" width="44.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="7.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" customWidth="1"/>
-    <col min="11" max="11" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.1796875" customWidth="1"/>
-    <col min="15" max="15" width="17.7265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
     <col min="16" max="16" width="11" style="2" customWidth="1"/>
-    <col min="17" max="17" width="12.26953125" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
     <col min="19" max="19" width="9" style="2"/>
-    <col min="21" max="21" width="17.7265625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.7265625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7265625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="12.453125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.453125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12.26953125" customWidth="1"/>
-    <col min="29" max="29" width="4.26953125" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -4359,16 +4439,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="8" width="10.26953125" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5495,17 +5575,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.453125" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6008,15 +6088,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6062,7 +6142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13" customHeight="1">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6079,7 +6159,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13" customHeight="1">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6184,15 +6264,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.453125" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
-    <col min="4" max="4" width="25.1796875" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
-    <col min="6" max="6" width="17.26953125" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6290,6 +6370,68 @@
       </c>
       <c r="F5" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D9" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6301,7 +6443,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B963FD-B399-4A5F-A7EE-C698A9110DBE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6309,19 +6451,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F843A941-2090-4EA2-92B0-02A8CDB751AA}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
-    <col min="2" max="2" width="23.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" customWidth="1"/>
-    <col min="6" max="6" width="8.36328125" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" customWidth="1"/>
-    <col min="10" max="10" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6376,7 +6518,7 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>283</v>
@@ -6402,7 +6544,7 @@
         <v>283</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -6506,7 +6648,7 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="14" t="s">
         <v>284</v>
       </c>
       <c r="I6" s="10" t="s">
@@ -6548,7 +6690,98 @@
         <v>292</v>
       </c>
     </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>284</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="J8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>320</v>
+      </c>
+      <c r="D10" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="J10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="I11" s="13"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6556,22 +6789,25 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AA25C0-E9A0-4DAC-9454-4255D17FAEDC}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.6328125" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="6" width="11.36328125" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.90625" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6599,11 +6835,23 @@
       <c r="I1" t="s">
         <v>297</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="12" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M1" t="s">
+        <v>306</v>
+      </c>
+      <c r="N1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6634,8 +6882,20 @@
       <c r="J2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6666,8 +6926,20 @@
       <c r="J3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>500</v>
+      </c>
+      <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6698,9 +6970,21 @@
       <c r="J4">
         <v>10</v>
       </c>
+      <c r="K4">
+        <v>30</v>
+      </c>
+      <c r="L4">
+        <v>10000</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\Resources\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DCB856-4F87-438E-9FD0-8798FB7101B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D400E5-2427-453D-BE35-A0B85247F1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9285" yWindow="2265" windowWidth="25575" windowHeight="13665" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1820" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="330">
   <si>
     <t>ID</t>
   </si>
@@ -1019,18 +1019,37 @@
   </si>
   <si>
     <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>sadf</t>
+  </si>
+  <si>
+    <t>Type_M</t>
+  </si>
+  <si>
+    <t>AddRandomM</t>
+  </si>
+  <si>
+    <t>VRaisingAddRandomCardEffect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1150,15 +1169,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6264,12 +6283,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
@@ -6432,6 +6451,23 @@
       </c>
       <c r="D9" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6442,10 +6478,53 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B963FD-B399-4A5F-A7EE-C698A9110DBE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6520,7 +6599,7 @@
       <c r="G2">
         <v>90</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="13" t="s">
         <v>283</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -6587,7 +6666,7 @@
       <c r="H4" t="s">
         <v>283</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="14" t="s">
         <v>298</v>
       </c>
       <c r="J4" t="s">
@@ -6616,10 +6695,10 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>301</v>
       </c>
       <c r="J5" t="s">
@@ -6648,10 +6727,10 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>301</v>
       </c>
       <c r="J6" t="s">
@@ -6683,7 +6762,7 @@
       <c r="H7" t="s">
         <v>284</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="9" t="s">
         <v>301</v>
       </c>
       <c r="J7" t="s">
@@ -6712,7 +6791,7 @@
       <c r="H8" t="s">
         <v>284</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>316</v>
       </c>
       <c r="J8" t="s">
@@ -6741,7 +6820,7 @@
       <c r="H9" t="s">
         <v>284</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>317</v>
       </c>
       <c r="J9" t="s">
@@ -6770,7 +6849,7 @@
       <c r="H10" t="s">
         <v>284</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="11" t="s">
         <v>319</v>
       </c>
       <c r="J10" t="s">
@@ -6778,10 +6857,10 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="I11" s="13"/>
+      <c r="I11" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6792,7 +6871,7 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
@@ -6835,7 +6914,7 @@
       <c r="I1" t="s">
         <v>297</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>304</v>
       </c>
       <c r="K1" t="s">
@@ -6876,7 +6955,7 @@
       <c r="H2" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>302</v>
       </c>
       <c r="J2">
@@ -6920,7 +6999,7 @@
       <c r="H3" t="s">
         <v>303</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>302</v>
       </c>
       <c r="J3">
@@ -6964,7 +7043,7 @@
       <c r="H4" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>302</v>
       </c>
       <c r="J4">
@@ -6984,7 +7063,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$AE$1:$AE$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="294">
   <si>
     <t>ID</t>
   </si>
@@ -158,6 +158,9 @@
     <t>参数+15</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>战术喝水</t>
   </si>
   <si>
@@ -179,63 +182,54 @@
     <t>刷新</t>
   </si>
   <si>
-    <t>重抽其他手牌，抽牌次数+1</t>
+    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
+  </si>
+  <si>
+    <t>才八点</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+7，出牌次数+1</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>wink</t>
+  </si>
+  <si>
+    <t>亲和力+3，神采+2</t>
+  </si>
+  <si>
+    <t>集中</t>
+  </si>
+  <si>
+    <t>专注+2，神采+2</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
+  </si>
+  <si>
+    <t>二次推流</t>
+  </si>
+  <si>
+    <t>参数+9/2次</t>
+  </si>
+  <si>
+    <t>加分动画显示需改进</t>
+  </si>
+  <si>
+    <t>计划</t>
+  </si>
+  <si>
+    <t>参数+11，神采+7</t>
   </si>
   <si>
     <t>Rare</t>
   </si>
   <si>
-    <t>才八点</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+7，出牌次数+1</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>渐入佳境</t>
-  </si>
-  <si>
-    <t>体力消耗减少1点，神采+4</t>
-  </si>
-  <si>
-    <t>wink</t>
-  </si>
-  <si>
-    <t>亲和力+3，神采+2</t>
-  </si>
-  <si>
-    <t>集中</t>
-  </si>
-  <si>
-    <t>专注+2，神采+2</t>
-  </si>
-  <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>红温+2，神采+2</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>二次推流</t>
-  </si>
-  <si>
-    <t>参数+9/2次</t>
-  </si>
-  <si>
-    <t>加分动画显示需改进</t>
-  </si>
-  <si>
-    <t>计划</t>
-  </si>
-  <si>
-    <t>参数+11，神采+7</t>
-  </si>
-  <si>
     <t>小花花</t>
   </si>
   <si>
@@ -260,9 +254,6 @@
     <t>舰长+1，神采+4，体力消耗减少+2回合</t>
   </si>
   <si>
-    <t>再一次</t>
-  </si>
-  <si>
     <t>攻击弹幕</t>
   </si>
   <si>
@@ -317,10 +308,10 @@
     <t>专注+3，神采+4</t>
   </si>
   <si>
-    <t>状态火热</t>
-  </si>
-  <si>
-    <t>红温+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
+    <t>警告！</t>
+  </si>
+  <si>
+    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
   </si>
   <si>
     <t>躺</t>
@@ -329,16 +320,10 @@
     <t>神采+6</t>
   </si>
   <si>
-    <t>惊喜</t>
-  </si>
-  <si>
-    <t>舰长+1，参数+4，卡牌使用次数+1</t>
-  </si>
-  <si>
     <t>祝福</t>
   </si>
   <si>
-    <t>流水+30，神采+3，体力消耗减少50%+2回合</t>
+    <t>流水+30，神采+3，体力消耗减少+2回合</t>
   </si>
   <si>
     <t>宣传</t>
@@ -350,7 +335,7 @@
     <t>直播通知</t>
   </si>
   <si>
-    <t>同接+20，以后，每当打出A卡时，同接+10,</t>
+    <t>同接+20，以后，每当打出A卡时，同接+10</t>
   </si>
   <si>
     <t>爆米</t>
@@ -362,13 +347,13 @@
     <t>爆！</t>
   </si>
   <si>
-    <t>参数+42</t>
+    <t>参数+38</t>
   </si>
   <si>
     <t>越想越气</t>
   </si>
   <si>
-    <t>有红温的状态下，红温+3</t>
+    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
   </si>
   <si>
     <t>欢呼</t>
@@ -425,7 +410,7 @@
     <t>申请对线</t>
   </si>
   <si>
-    <t>红温+2，之后4回合内，回合结束时，参数+4</t>
+    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
   </si>
   <si>
     <t>子弹时间</t>
@@ -476,7 +461,7 @@
     <t>点炮仗</t>
   </si>
   <si>
-    <t>红温&gt;10层时可使用获得红温200%的参数红温减少50%</t>
+    <t>红温&gt;10层时可使用，获得红温300%的参数，红温减少50%</t>
   </si>
   <si>
     <t>逼逼赖赖</t>
@@ -485,6 +470,39 @@
     <t>红温+3，卡牌使用次数+1，如果红温大于10层，红温+3</t>
   </si>
   <si>
+    <t>雷区</t>
+  </si>
+  <si>
+    <t>红温+1，以后每当使用A卡的时候，红温+1</t>
+  </si>
+  <si>
+    <t>红温+2，幽默+1</t>
+  </si>
+  <si>
+    <t>自洽</t>
+  </si>
+  <si>
+    <t>幽默+3，参数+12，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>早上好！</t>
+  </si>
+  <si>
+    <t>开局加入手牌，幽默+2，神采+2</t>
+  </si>
+  <si>
+    <t>拜拜！！！</t>
+  </si>
+  <si>
+    <t>最后一回合加入手牌，</t>
+  </si>
+  <si>
+    <t>封禁</t>
+  </si>
+  <si>
+    <t>神采+5两次，获得神采70%的参数</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -770,6 +788,24 @@
     <t>红温大于50层时，大于50层的部分每层红温会使参数获得量+5%</t>
   </si>
   <si>
+    <t>红温大于10层时，参数+X</t>
+  </si>
+  <si>
+    <t>参数+ {AttributeDelta}</t>
+  </si>
+  <si>
+    <t>红温大于30层时，参数+X</t>
+  </si>
+  <si>
+    <t>红温大于50层时，参数+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡，红温+X</t>
+  </si>
+  <si>
+    <t>每当使用A卡，红温+1</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -779,6 +815,12 @@
     <t>Latency</t>
   </si>
   <si>
+    <t>Effect5</t>
+  </si>
+  <si>
+    <t>E5Param</t>
+  </si>
+  <si>
     <t>亲和力</t>
   </si>
   <si>
@@ -822,6 +864,9 @@
   </si>
   <si>
     <t>好娇娇</t>
+  </si>
+  <si>
+    <t>每当使用A卡时，红温+1</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1840,12 +1885,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AE60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="44.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="38.2166666666667" customWidth="1"/>
     <col min="4" max="4" width="10.425" customWidth="1"/>
     <col min="5" max="5" width="13.425" customWidth="1"/>
     <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
@@ -2054,7 +2099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:31">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2096,7 +2141,7 @@
       </c>
       <c r="AC4" s="7"/>
       <c r="AE4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="1:31">
@@ -2104,10 +2149,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -2153,24 +2198,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:31">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2192,7 +2237,7 @@
       </c>
       <c r="AC6" s="7"/>
       <c r="AE6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="1:31">
@@ -2200,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -2218,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2228,6 +2273,24 @@
       </c>
       <c r="M7" s="4">
         <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>21</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="4">
+        <v>14</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1</v>
       </c>
       <c r="AC7" s="7"/>
       <c r="AE7" t="s">
@@ -2245,13 +2308,13 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2302,7 +2365,7 @@
     </row>
     <row r="9" hidden="1" spans="1:31">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
@@ -2320,43 +2383,43 @@
         <v>34</v>
       </c>
       <c r="H9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P9" s="4">
         <v>2</v>
       </c>
       <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9" s="5">
         <v>4</v>
-      </c>
-      <c r="R9" s="5">
-        <v>6</v>
       </c>
       <c r="AC9" s="7"/>
       <c r="AE9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" hidden="1" spans="1:31">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -2386,31 +2449,31 @@
         <v>0</v>
       </c>
       <c r="M10" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" s="4">
         <v>2</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC10" s="7"/>
       <c r="AE10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
@@ -2440,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N11">
         <v>2</v>
@@ -2459,12 +2522,12 @@
       </c>
       <c r="AC11" s="7"/>
       <c r="AE11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" spans="1:31">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
@@ -2476,49 +2539,52 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O12" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P12" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R12" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC12" s="7"/>
+      <c r="AD12" t="s">
+        <v>61</v>
+      </c>
       <c r="AE12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="1:31">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
@@ -2527,7 +2593,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -2536,13 +2602,13 @@
         <v>34</v>
       </c>
       <c r="H13" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2551,31 +2617,28 @@
         <v>11</v>
       </c>
       <c r="N13">
+        <v>11</v>
+      </c>
+      <c r="O13" s="5">
+        <v>15</v>
+      </c>
+      <c r="P13" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13" s="5">
         <v>9</v>
       </c>
-      <c r="O13" s="5">
-        <v>13</v>
-      </c>
-      <c r="P13" s="4">
-        <v>11</v>
-      </c>
-      <c r="Q13">
-        <v>9</v>
-      </c>
-      <c r="R13" s="5">
-        <v>13</v>
-      </c>
       <c r="AC13" s="7"/>
-      <c r="AD13" t="s">
-        <v>64</v>
-      </c>
       <c r="AE13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:31">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>65</v>
@@ -2584,10 +2647,10 @@
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -2596,7 +2659,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2605,31 +2668,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O14" s="5">
-        <v>15</v>
-      </c>
-      <c r="P14" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q14">
-        <v>7</v>
-      </c>
-      <c r="R14" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14" s="7"/>
       <c r="AE14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="1:31">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>67</v>
@@ -2638,34 +2692,34 @@
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
       </c>
       <c r="H15" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="5">
         <v>4</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="M15" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="O15" s="5">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" s="7"/>
       <c r="AE15" t="s">
@@ -2674,7 +2728,7 @@
     </row>
     <row r="16" hidden="1" spans="1:31">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>69</v>
@@ -2683,7 +2737,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -2692,25 +2746,34 @@
         <v>34</v>
       </c>
       <c r="H16" s="4">
+        <v>6</v>
+      </c>
+      <c r="I16" s="5">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>6</v>
+      </c>
+      <c r="N16">
         <v>4</v>
       </c>
-      <c r="I16" s="5">
-        <v>4</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
+      <c r="O16" s="5">
+        <v>5</v>
+      </c>
+      <c r="P16" s="4">
         <v>18</v>
       </c>
-      <c r="N16">
-        <v>1.4</v>
-      </c>
-      <c r="O16" s="5">
-        <v>1.8</v>
+      <c r="Q16">
+        <v>0.8</v>
+      </c>
+      <c r="R16" s="5">
+        <v>1.1</v>
       </c>
       <c r="AC16" s="7"/>
       <c r="AE16" t="s">
@@ -2719,7 +2782,7 @@
     </row>
     <row r="17" hidden="1" spans="1:31">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
@@ -2728,52 +2791,61 @@
         <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="4">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>19</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5">
+        <v>1</v>
+      </c>
+      <c r="P17" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q17">
+        <v>4</v>
+      </c>
+      <c r="R17" s="5">
         <v>6</v>
       </c>
-      <c r="I17" s="5">
-        <v>5</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4">
-        <v>6</v>
-      </c>
-      <c r="N17">
-        <v>4</v>
-      </c>
-      <c r="O17" s="5">
-        <v>5</v>
-      </c>
-      <c r="P17" s="4">
+      <c r="S17" s="4">
+        <v>21</v>
+      </c>
+      <c r="T17">
+        <v>2</v>
+      </c>
+      <c r="U17" s="5">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="8"/>
+      <c r="AE17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
+      <c r="A18">
         <v>18</v>
-      </c>
-      <c r="Q17">
-        <v>0.8</v>
-      </c>
-      <c r="R17" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="AC17" s="7"/>
-      <c r="AE17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" hidden="1" spans="1:31">
-      <c r="A18">
-        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
@@ -2782,7 +2854,7 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
@@ -2791,61 +2863,43 @@
         <v>34</v>
       </c>
       <c r="H18" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="5">
         <v>3</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O18" s="5">
-        <v>1</v>
-      </c>
-      <c r="P18" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q18">
-        <v>4</v>
-      </c>
-      <c r="R18" s="5">
-        <v>6</v>
-      </c>
-      <c r="S18" s="4">
-        <v>21</v>
-      </c>
-      <c r="T18">
-        <v>2</v>
-      </c>
-      <c r="U18" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="AC18" s="7"/>
       <c r="AE18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" hidden="1" spans="1:31">
       <c r="A19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -2854,10 +2908,10 @@
         <v>34</v>
       </c>
       <c r="H19" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2866,37 +2920,52 @@
         <v>1</v>
       </c>
       <c r="M19" s="4">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19" s="5">
+        <v>2</v>
       </c>
       <c r="AC19" s="7"/>
       <c r="AE19" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:31">
       <c r="A20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I20" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2904,35 +2973,38 @@
       <c r="K20">
         <v>0</v>
       </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
       <c r="M20" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="O20" s="5">
-        <v>7</v>
-      </c>
-      <c r="AC20" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="AC20" s="8"/>
       <c r="AE20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" hidden="1" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -2944,160 +3016,166 @@
         <v>4</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="M21" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q21">
+        <v>30</v>
+      </c>
+      <c r="R21" s="5">
+        <v>42</v>
+      </c>
+      <c r="S21" s="4">
+        <v>2</v>
+      </c>
+      <c r="T21">
+        <v>5</v>
+      </c>
+      <c r="U21" s="5">
         <v>7</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21" s="5">
-        <v>2</v>
       </c>
       <c r="AC21" s="7"/>
       <c r="AE21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" hidden="1" spans="1:31">
       <c r="A22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
       </c>
       <c r="H22" s="4">
+        <v>4</v>
+      </c>
+      <c r="I22" s="5">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4">
         <v>6</v>
       </c>
-      <c r="I22" s="5">
-        <v>6</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4">
-        <v>11</v>
-      </c>
       <c r="N22">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O22" s="5">
-        <v>30</v>
-      </c>
-      <c r="AC22" s="8"/>
+        <v>4</v>
+      </c>
+      <c r="P22" s="4">
+        <v>28</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="7"/>
       <c r="AE22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" hidden="1" spans="1:31">
       <c r="A23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="4">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4">
+        <v>6</v>
+      </c>
+      <c r="N23">
         <v>5</v>
       </c>
-      <c r="I23" s="5">
-        <v>4</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="M23" s="4">
-        <v>26</v>
-      </c>
-      <c r="N23">
-        <v>2</v>
-      </c>
       <c r="O23" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P23" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R23" s="5">
-        <v>42</v>
-      </c>
-      <c r="S23" s="4">
-        <v>2</v>
-      </c>
-      <c r="T23">
-        <v>5</v>
-      </c>
-      <c r="U23" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AC23" s="7"/>
       <c r="AE23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
@@ -3109,46 +3187,46 @@
         <v>4</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="5">
         <v>4</v>
       </c>
       <c r="P24" s="4">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R24" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AC24" s="7"/>
       <c r="AE24" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:31">
       <c r="A25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
         <v>38</v>
@@ -3157,64 +3235,55 @@
         <v>34</v>
       </c>
       <c r="H25" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="M25" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25" s="5">
         <v>5</v>
-      </c>
-      <c r="O25" s="5">
-        <v>7</v>
-      </c>
-      <c r="P25" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25" s="5">
-        <v>1</v>
       </c>
       <c r="AC25" s="7"/>
       <c r="AE25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" spans="1:31">
       <c r="A26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
       </c>
       <c r="H26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3223,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>3</v>
@@ -3232,73 +3301,97 @@
         <v>4</v>
       </c>
       <c r="P26" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R26" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AC26" s="7"/>
       <c r="AE26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
       </c>
       <c r="H27" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I27" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O27" s="5">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="P27" s="4">
+        <v>56</v>
+      </c>
+      <c r="Q27">
+        <v>24</v>
+      </c>
+      <c r="R27" s="5">
+        <v>30</v>
+      </c>
+      <c r="S27" s="4">
+        <v>57</v>
+      </c>
+      <c r="T27">
+        <v>36</v>
+      </c>
+      <c r="U27" s="5">
+        <v>44</v>
+      </c>
+      <c r="V27" s="4"/>
+      <c r="W27"/>
+      <c r="X27" s="5"/>
+      <c r="AC27" s="8"/>
       <c r="AE27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" hidden="1" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31">
       <c r="A28">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3310,64 +3403,55 @@
         <v>34</v>
       </c>
       <c r="H28" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="M28" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O28" s="5">
-        <v>4</v>
-      </c>
-      <c r="P28" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q28">
-        <v>4</v>
-      </c>
-      <c r="R28" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC28" s="7"/>
       <c r="AE28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" spans="1:31">
       <c r="A29">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
       </c>
       <c r="H29" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -3376,49 +3460,49 @@
         <v>1</v>
       </c>
       <c r="M29" s="4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="N29">
+        <v>30</v>
+      </c>
+      <c r="O29" s="5">
+        <v>30</v>
+      </c>
+      <c r="P29" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>3</v>
+      </c>
+      <c r="R29" s="5">
         <v>5</v>
       </c>
-      <c r="O29" s="5">
-        <v>7</v>
-      </c>
-      <c r="P29" s="4">
-        <v>30</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-      <c r="R29" s="5">
-        <v>1</v>
-      </c>
       <c r="S29" s="4">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="AC29" s="7"/>
       <c r="AE29" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" hidden="1" spans="1:31">
       <c r="A30">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -3427,55 +3511,64 @@
         <v>34</v>
       </c>
       <c r="H30" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O30" s="5">
-        <v>8</v>
-      </c>
-      <c r="AC30" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="P30" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q30">
+        <v>2</v>
+      </c>
+      <c r="R30" s="5">
+        <v>4</v>
+      </c>
+      <c r="AC30" s="8"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" hidden="1" spans="1:31">
       <c r="A31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
       </c>
       <c r="H31" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3484,30 +3577,21 @@
         <v>1</v>
       </c>
       <c r="M31" s="4">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O31" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="P31" s="4">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R31" s="5">
-        <v>7</v>
-      </c>
-      <c r="S31" s="4">
-        <v>14</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31" s="5">
         <v>1</v>
       </c>
       <c r="AC31" s="8"/>
@@ -3517,16 +3601,16 @@
     </row>
     <row r="32" hidden="1" spans="1:31">
       <c r="A32">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
@@ -3535,10 +3619,10 @@
         <v>34</v>
       </c>
       <c r="H32" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I32" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3546,62 +3630,34 @@
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="M32" s="4">
-        <v>32</v>
-      </c>
-      <c r="N32">
-        <v>30</v>
-      </c>
-      <c r="O32" s="5">
-        <v>30</v>
-      </c>
-      <c r="P32" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q32">
-        <v>3</v>
-      </c>
-      <c r="R32" s="5">
-        <v>5</v>
-      </c>
-      <c r="S32" s="4">
-        <v>21</v>
-      </c>
-      <c r="T32">
-        <v>2</v>
-      </c>
-      <c r="U32" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="7"/>
       <c r="AE32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:31">
+    <row r="33" spans="1:31">
       <c r="A33">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
       </c>
       <c r="H33" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I33" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -3610,40 +3666,30 @@
         <v>1</v>
       </c>
       <c r="M33" s="4">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="N33">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="O33" s="5">
-        <v>70</v>
-      </c>
-      <c r="P33" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q33">
-        <v>2</v>
-      </c>
-      <c r="R33" s="5">
-        <v>4</v>
-      </c>
-      <c r="AC33" s="8"/>
+        <v>52</v>
+      </c>
       <c r="AE33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31">
+      <c r="A34">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" hidden="1" spans="1:31">
-      <c r="A34">
-        <v>32</v>
-      </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
@@ -3652,122 +3698,133 @@
         <v>34</v>
       </c>
       <c r="H34" s="4">
+        <v>3</v>
+      </c>
+      <c r="I34" s="5">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="4">
+        <v>15</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" s="5">
         <v>4</v>
       </c>
-      <c r="I34" s="5">
-        <v>3</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4">
+      <c r="AE34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31">
+      <c r="A35">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" t="s">
         <v>33</v>
-      </c>
-      <c r="N34">
-        <v>20</v>
-      </c>
-      <c r="O34" s="5">
-        <v>30</v>
-      </c>
-      <c r="P34" s="4">
-        <v>35</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="8"/>
-      <c r="AE34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" hidden="1" spans="1:31">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" t="s">
-        <v>38</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
       </c>
       <c r="H35" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I35" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M35" s="4">
+        <v>11</v>
+      </c>
+      <c r="N35">
+        <v>18</v>
+      </c>
+      <c r="O35" s="5">
+        <v>22</v>
       </c>
       <c r="AE35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:31">
       <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
+        <v>37</v>
+      </c>
+      <c r="B36" s="6">
+        <v>144</v>
       </c>
       <c r="C36" t="s">
         <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
       </c>
       <c r="H36" s="4">
+        <v>3</v>
+      </c>
+      <c r="I36" s="5">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="4">
+        <v>15</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" s="5">
+        <v>4</v>
+      </c>
+      <c r="P36" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q36">
+        <v>6</v>
+      </c>
+      <c r="R36" s="5">
         <v>8</v>
       </c>
-      <c r="I36" s="5">
-        <v>7</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="M36" s="4">
-        <v>11</v>
-      </c>
-      <c r="N36">
-        <v>42</v>
-      </c>
-      <c r="O36" s="5">
-        <v>54</v>
-      </c>
       <c r="AE36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" hidden="1" spans="1:31">
       <c r="A37">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
         <v>110</v>
@@ -3776,7 +3833,7 @@
         <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -3791,16 +3848,13 @@
         <v>3</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
       <c r="M37" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>3</v>
@@ -3808,13 +3862,22 @@
       <c r="O37" s="5">
         <v>4</v>
       </c>
+      <c r="P37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q37">
+        <v>6</v>
+      </c>
+      <c r="R37" s="5">
+        <v>8</v>
+      </c>
       <c r="AE37" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" hidden="1" spans="1:31">
       <c r="A38">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
         <v>112</v>
@@ -3823,51 +3886,60 @@
         <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
       </c>
       <c r="H38" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N38">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O38" s="5">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="P38" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q38">
+        <v>3</v>
+      </c>
+      <c r="R38" s="5">
+        <v>5</v>
       </c>
       <c r="AE38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" hidden="1" spans="1:31">
       <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6">
-        <v>144</v>
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -3876,25 +3948,25 @@
         <v>34</v>
       </c>
       <c r="H39" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P39" s="4">
         <v>2</v>
@@ -3903,24 +3975,24 @@
         <v>6</v>
       </c>
       <c r="R39" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE39" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" hidden="1" spans="1:31">
       <c r="A40">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -3929,7 +4001,7 @@
         <v>34</v>
       </c>
       <c r="H40" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="5">
         <v>3</v>
@@ -3938,25 +4010,25 @@
         <v>1</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="4">
         <v>7</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O40" s="5">
+        <v>5</v>
+      </c>
+      <c r="P40" s="4">
+        <v>38</v>
+      </c>
+      <c r="Q40">
         <v>4</v>
       </c>
-      <c r="P40" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q40">
-        <v>6</v>
-      </c>
       <c r="R40" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="s">
         <v>52</v>
@@ -3964,16 +4036,16 @@
     </row>
     <row r="41" hidden="1" spans="1:31">
       <c r="A41">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
@@ -3982,51 +4054,51 @@
         <v>34</v>
       </c>
       <c r="H41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="4">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O41" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P41" s="4">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="Q41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R41" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE41" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" hidden="1" spans="1:31">
       <c r="A42">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -4035,10 +4107,10 @@
         <v>34</v>
       </c>
       <c r="H42" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -4047,145 +4119,154 @@
         <v>1</v>
       </c>
       <c r="M42" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
       <c r="O42" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" s="4">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="Q42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R42" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" hidden="1" spans="1:31">
       <c r="A43">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="4">
+        <v>7</v>
+      </c>
+      <c r="I43" s="5">
         <v>4</v>
       </c>
-      <c r="I43" s="5">
-        <v>3</v>
-      </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>1</v>
       </c>
       <c r="M43" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43" s="5">
         <v>5</v>
       </c>
       <c r="P43" s="4">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="Q43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R43" s="5">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="S43" s="4">
+        <v>18</v>
+      </c>
+      <c r="T43">
+        <v>0.9</v>
+      </c>
+      <c r="U43" s="5">
+        <v>1.2</v>
       </c>
       <c r="AE43" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
       <c r="A44">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O44" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P44" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R44" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE44" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" hidden="1" spans="1:31">
       <c r="A45">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D45" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -4194,13 +4275,13 @@
         <v>34</v>
       </c>
       <c r="H45" s="4">
+        <v>5</v>
+      </c>
+      <c r="I45" s="5">
         <v>4</v>
       </c>
-      <c r="I45" s="5">
-        <v>3</v>
-      </c>
       <c r="J45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -4209,19 +4290,28 @@
         <v>7</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O45" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P45" s="4">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45" s="5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="S45" s="4">
+        <v>2</v>
+      </c>
+      <c r="T45">
+        <v>7</v>
+      </c>
+      <c r="U45" s="5">
+        <v>8</v>
       </c>
       <c r="AE45" t="s">
         <v>52</v>
@@ -4229,78 +4319,78 @@
     </row>
     <row r="46" hidden="1" spans="1:31">
       <c r="A46">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I46" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
         <v>1</v>
       </c>
       <c r="M46" s="4">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="O46" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="P46" s="4">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R46" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S46" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T46">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U46" s="5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AE46" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="1:31">
       <c r="A47">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -4309,104 +4399,83 @@
         <v>34</v>
       </c>
       <c r="H47" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I47" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O47" s="5">
-        <v>2</v>
-      </c>
-      <c r="P47" s="4">
-        <v>42</v>
-      </c>
-      <c r="Q47">
-        <v>3</v>
-      </c>
-      <c r="R47" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE47" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" hidden="1" spans="1:31">
       <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
         <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O48" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P48" s="4">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R48" s="5">
-        <v>2</v>
-      </c>
-      <c r="S48" s="4">
-        <v>2</v>
-      </c>
-      <c r="T48">
-        <v>7</v>
-      </c>
-      <c r="U48" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31">
       <c r="A49">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
         <v>133</v>
@@ -4415,60 +4484,51 @@
         <v>134</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I49" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="4">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="N49">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="O49" s="5">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="P49" s="4">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q49">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R49" s="5">
-        <v>30</v>
-      </c>
-      <c r="S49" s="4">
-        <v>19</v>
-      </c>
-      <c r="T49">
-        <v>1</v>
-      </c>
-      <c r="U49" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE49" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" hidden="1" spans="1:31">
       <c r="A50">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
         <v>135</v>
@@ -4477,7 +4537,7 @@
         <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -4486,145 +4546,157 @@
         <v>34</v>
       </c>
       <c r="H50" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I50" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O50" s="5">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="P50" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q50">
+        <v>1.1</v>
+      </c>
+      <c r="R50" s="5">
+        <v>1.7</v>
       </c>
       <c r="AE50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" hidden="1" spans="1:31">
       <c r="A51">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I51" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O51" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P51" s="4">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="Q51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R51" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE51" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" hidden="1" spans="1:31">
       <c r="A52">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O52" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P52" s="4">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31">
       <c r="A53">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -4636,78 +4708,84 @@
         <v>5</v>
       </c>
       <c r="I53" s="5">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>6</v>
+      </c>
+      <c r="M53" s="4">
+        <v>50</v>
+      </c>
+      <c r="N53">
+        <v>3</v>
+      </c>
+      <c r="O53" s="5">
         <v>4</v>
       </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="M53" s="4">
-        <v>6</v>
-      </c>
-      <c r="N53">
-        <v>5</v>
-      </c>
-      <c r="O53" s="5">
-        <v>7</v>
-      </c>
       <c r="P53" s="4">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="Q53">
-        <v>1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="R53" s="5">
-        <v>1.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AE53" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54" hidden="1" spans="1:31">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
       <c r="A54">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
       </c>
       <c r="H54" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I54" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <v>1</v>
       </c>
       <c r="M54" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P54" s="4">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="Q54">
         <v>1</v>
@@ -4715,22 +4793,31 @@
       <c r="R54" s="5">
         <v>1</v>
       </c>
+      <c r="S54" s="4">
+        <v>52</v>
+      </c>
+      <c r="T54">
+        <v>3</v>
+      </c>
+      <c r="U54" s="5">
+        <v>5</v>
+      </c>
       <c r="AE54" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:31">
       <c r="A55">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
@@ -4739,10 +4826,10 @@
         <v>34</v>
       </c>
       <c r="H55" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4750,82 +4837,77 @@
       <c r="K55">
         <v>1</v>
       </c>
-      <c r="M55" s="4">
-        <v>9</v>
+      <c r="M55">
+        <v>15</v>
       </c>
       <c r="N55">
-        <v>2</v>
-      </c>
-      <c r="O55" s="5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>3</v>
       </c>
       <c r="P55" s="4">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="Q55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" s="5">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z55"/>
+      <c r="AA55" s="5"/>
       <c r="AE55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>146</v>
-      </c>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="3:31">
       <c r="C56" t="s">
         <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I56" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56">
-        <v>6</v>
-      </c>
-      <c r="M56" s="4">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>15</v>
       </c>
       <c r="N56">
         <v>2</v>
       </c>
-      <c r="O56" s="5">
-        <v>2.5</v>
+      <c r="O56">
+        <v>2</v>
       </c>
       <c r="P56" s="4">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Q56">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="R56" s="5">
-        <v>-0.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Z56"/>
+      <c r="AA56" s="5"/>
       <c r="AE56" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="2:31">
@@ -4836,64 +4918,204 @@
         <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E57" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" t="s">
+        <v>47</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4">
+        <v>2</v>
+      </c>
+      <c r="I57" s="5">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>45</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="O57">
+        <v>4</v>
+      </c>
+      <c r="P57" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q57">
+        <v>12</v>
+      </c>
+      <c r="R57" s="5">
+        <v>18</v>
+      </c>
+      <c r="S57" s="4">
+        <v>14</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z57"/>
+      <c r="AA57" s="5"/>
+      <c r="AE57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="2:31">
+      <c r="B58" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" t="s">
         <v>38</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F58" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="4">
+        <v>3</v>
+      </c>
+      <c r="I58" s="5">
+        <v>3</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="M58" s="4">
+        <v>45</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58" s="5">
+        <v>3</v>
+      </c>
+      <c r="P58" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q58">
+        <v>2</v>
+      </c>
+      <c r="R58" s="5">
+        <v>3</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:31">
+      <c r="B59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="4">
+        <v>3</v>
+      </c>
+      <c r="I59" s="5">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="2:31">
+      <c r="B60" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" t="s">
+        <v>155</v>
+      </c>
+      <c r="D60" t="s">
         <v>46</v>
       </c>
-      <c r="G57">
-        <v>14</v>
-      </c>
-      <c r="H57" s="4">
-        <v>2</v>
-      </c>
-      <c r="I57" s="5">
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="M57" s="4">
-        <v>15</v>
-      </c>
-      <c r="N57">
-        <v>3</v>
-      </c>
-      <c r="O57" s="5">
-        <v>4</v>
-      </c>
-      <c r="P57" s="4">
-        <v>14</v>
-      </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
-      <c r="R57" s="5">
-        <v>1</v>
-      </c>
-      <c r="S57" s="4">
-        <v>52</v>
-      </c>
-      <c r="T57">
-        <v>3</v>
-      </c>
-      <c r="U57" s="5">
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" t="s">
+        <v>47</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+      <c r="H60" s="4">
+        <v>2</v>
+      </c>
+      <c r="I60" s="5">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="M60" s="4">
+        <v>2</v>
+      </c>
+      <c r="N60">
         <v>5</v>
       </c>
-      <c r="AE57" t="s">
-        <v>61</v>
+      <c r="O60" s="5">
+        <v>6</v>
+      </c>
+      <c r="P60" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q60">
+        <v>5</v>
+      </c>
+      <c r="R60" s="5">
+        <v>6</v>
+      </c>
+      <c r="S60" s="4"/>
+      <c r="T60"/>
+      <c r="U60" s="5"/>
+      <c r="AE60" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="30">
-      <filters blank="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="AE1:AE60" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
         <filter val="C"/>
       </filters>
     </filterColumn>
@@ -4908,7 +5130,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -4936,19 +5158,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4956,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4974,19 +5196,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4997,16 +5219,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5017,16 +5239,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" t="s">
         <v>165</v>
       </c>
-      <c r="C5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" t="s">
-        <v>159</v>
-      </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5037,13 +5259,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5054,16 +5276,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5074,13 +5296,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5094,13 +5316,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5114,13 +5336,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5134,13 +5356,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5151,16 +5373,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5171,16 +5393,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5191,19 +5413,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5214,16 +5436,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5234,16 +5456,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5254,13 +5476,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5274,16 +5496,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5294,13 +5516,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5314,13 +5536,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D20" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5334,16 +5556,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5354,16 +5576,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5374,13 +5596,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C23" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5394,19 +5616,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5417,13 +5639,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5437,16 +5659,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5460,16 +5682,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E27" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5480,13 +5702,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C28" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5500,19 +5722,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5526,13 +5748,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C30" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D30" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5546,19 +5768,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C31" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F31" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5569,19 +5791,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5592,19 +5814,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C33" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5615,16 +5837,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5635,16 +5857,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E35" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5655,19 +5877,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5681,13 +5903,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5701,16 +5923,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" t="s">
         <v>222</v>
-      </c>
-      <c r="C38" t="s">
-        <v>222</v>
-      </c>
-      <c r="D38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" t="s">
-        <v>216</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5721,13 +5943,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5744,16 +5966,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5764,13 +5986,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D41" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5787,19 +6009,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D42" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5813,13 +6035,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D43" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5833,13 +6055,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D44" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5853,19 +6075,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C45" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F45" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5876,16 +6098,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D46" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5896,13 +6118,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D47" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5916,19 +6138,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5939,13 +6161,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C49" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -5959,19 +6181,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -5982,13 +6204,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6002,13 +6224,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D52" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6022,13 +6244,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C53" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D53" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6042,13 +6264,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D54" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6065,16 +6287,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D55" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6088,16 +6310,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C56" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D56" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6111,21 +6333,133 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C57" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D57" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E57" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G57">
         <v>8</v>
       </c>
       <c r="I57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:9">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>251</v>
+      </c>
+      <c r="C58" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" t="s">
+        <v>166</v>
+      </c>
+      <c r="G58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>253</v>
+      </c>
+      <c r="C59" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" t="s">
+        <v>166</v>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>254</v>
+      </c>
+      <c r="C60" t="s">
+        <v>252</v>
+      </c>
+      <c r="D60" t="s">
+        <v>165</v>
+      </c>
+      <c r="E60" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>255</v>
+      </c>
+      <c r="C61" t="s">
+        <v>255</v>
+      </c>
+      <c r="D61" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>214</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>256</v>
+      </c>
+      <c r="C62" t="s">
+        <v>256</v>
+      </c>
+      <c r="D62" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62">
+        <v>20</v>
+      </c>
+      <c r="I62">
         <v>-1</v>
       </c>
     </row>
@@ -6139,7 +6473,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -6154,7 +6488,7 @@
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6162,13 +6496,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D1" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -6188,16 +6522,28 @@
       <c r="K1" t="s">
         <v>19</v>
       </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6223,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6246,10 +6592,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6263,10 +6609,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6298,10 +6644,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6321,10 +6667,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6344,10 +6690,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6367,10 +6713,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6390,10 +6736,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6413,10 +6759,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6442,10 +6788,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6471,10 +6817,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6494,10 +6840,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6517,10 +6863,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6540,10 +6886,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6563,10 +6909,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6586,10 +6932,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6609,10 +6955,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6626,10 +6972,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6643,16 +6989,39 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>59</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6688,16 +7057,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E1" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F1" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="G1" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6705,13 +7074,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6725,13 +7094,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D3" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -6742,13 +7111,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -6759,13 +7128,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6779,13 +7148,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6799,13 +7168,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6819,13 +7188,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -6839,13 +7208,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -6859,13 +7228,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E10">
         <v>3</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -17,7 +17,7 @@
     <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="365">
   <si>
     <t>ID</t>
   </si>
@@ -159,7 +159,7 @@
     <t>闪耀</t>
   </si>
   <si>
-    <t>参数+15</t>
+    <t>参数+15，红温大于10层时，参数+9</t>
   </si>
   <si>
     <t>C</t>
@@ -171,10 +171,10 @@
     <t>参数+5，神采+4</t>
   </si>
   <si>
-    <t>网络波动</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次</t>
+    <t>kale</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
   </si>
   <si>
     <t>Epic</t>
@@ -351,7 +351,7 @@
     <t>爆！</t>
   </si>
   <si>
-    <t>参数+38</t>
+    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
   </si>
   <si>
     <t>越想越气</t>
@@ -360,10 +360,10 @@
     <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
   </si>
   <si>
-    <t>欢呼</t>
-  </si>
-  <si>
-    <t>参数+18</t>
+    <t>为我欢呼</t>
+  </si>
+  <si>
+    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
   </si>
   <si>
     <t>红温+3，神采+6</t>
@@ -480,33 +480,42 @@
     <t>红温+1，以后每当使用A卡的时候，红温+1</t>
   </si>
   <si>
-    <t>红温+2，幽默+1</t>
-  </si>
-  <si>
     <t>自洽</t>
   </si>
   <si>
     <t>幽默+3，参数+12，卡牌使用次数+1</t>
   </si>
   <si>
-    <t>早上好！</t>
-  </si>
-  <si>
-    <t>开局加入手牌，幽默+2，神采+2</t>
-  </si>
-  <si>
-    <t>拜拜！！！</t>
-  </si>
-  <si>
-    <t>最后一回合加入手牌，</t>
-  </si>
-  <si>
     <t>封禁</t>
   </si>
   <si>
     <t>神采+5两次，获得神采70%的参数</t>
   </si>
   <si>
+    <t>节目效果</t>
+  </si>
+  <si>
+    <t>获得神采120%的参数</t>
+  </si>
+  <si>
+    <t>LLBC</t>
+  </si>
+  <si>
+    <t>神采+7，获得神采90%的参数</t>
+  </si>
+  <si>
+    <t>大爆特爆</t>
+  </si>
+  <si>
+    <t>消耗所有神采，获得消耗神采300%的参数</t>
+  </si>
+  <si>
+    <t>冷笑话</t>
+  </si>
+  <si>
+    <t>获得神采100%的参数，下一回合抽一张卡牌</t>
+  </si>
+  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -810,6 +819,27 @@
     <t>每当使用A卡，红温+1</t>
   </si>
   <si>
+    <t>红温大于30层时，获得红温X%的参数</t>
+  </si>
+  <si>
+    <t>红温大于10层时，神采+X</t>
+  </si>
+  <si>
+    <t>红温大于10层时，幽默+X</t>
+  </si>
+  <si>
+    <t>红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>每当使用M卡幽默+X</t>
+  </si>
+  <si>
+    <t>每当使用M卡时，幽默+X</t>
+  </si>
+  <si>
+    <t>每当使用M卡幽默+1</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -871,6 +901,9 @@
   </si>
   <si>
     <t>每当使用A卡时，红温+1</t>
+  </si>
+  <si>
+    <t>每当使用M卡时，幽默+1</t>
   </si>
   <si>
     <t>OperatorType</t>
@@ -1503,19 +1536,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color rgb="FFFF0000"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FFFF0000"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1766,7 +1799,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1780,10 +1813,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -2120,28 +2155,30 @@
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="38.2166666666667" customWidth="1"/>
+    <col min="3" max="3" width="76.5083333333333" customWidth="1"/>
     <col min="4" max="4" width="10.425" customWidth="1"/>
     <col min="5" max="5" width="13.425" customWidth="1"/>
     <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
+    <col min="7" max="7" width="9.70833333333333" style="10" customWidth="1"/>
     <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" style="10" customWidth="1"/>
     <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
     <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" customWidth="1"/>
+    <col min="12" max="12" width="9.70833333333333" style="10" customWidth="1"/>
     <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
     <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" customWidth="1"/>
+    <col min="15" max="15" width="17.7083333333333" style="10" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
     <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" customWidth="1"/>
+    <col min="18" max="18" width="17.1416666666667" style="10" customWidth="1"/>
+    <col min="21" max="21" width="17.7083333333333" style="10" customWidth="1"/>
     <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" customWidth="1"/>
-    <col min="25" max="26" width="12.425" customWidth="1"/>
+    <col min="24" max="24" width="17.7083333333333" style="10" customWidth="1"/>
+    <col min="25" max="25" width="12.425" customWidth="1"/>
+    <col min="26" max="26" width="12.425" style="10" customWidth="1"/>
     <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
+    <col min="28" max="28" width="9" style="10"/>
     <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2164,13 +2201,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2179,55 +2216,55 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="12" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="14" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -2237,7 +2274,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:31">
+    <row r="2" customFormat="1" hidden="1" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2256,10 +2293,10 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="12">
         <v>4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="14">
         <v>3</v>
       </c>
       <c r="J2">
@@ -2268,22 +2305,22 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="12">
         <v>11</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="14">
         <v>7</v>
       </c>
       <c r="P2"/>
-      <c r="AC2" s="13"/>
+      <c r="AC2" s="15"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:31">
+    <row r="3" customFormat="1" hidden="1" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2302,10 +2339,10 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
         <v>0</v>
       </c>
       <c r="J3">
@@ -2314,22 +2351,22 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="12">
         <v>2</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="14">
         <v>4</v>
       </c>
       <c r="P3"/>
-      <c r="AC3" s="13"/>
+      <c r="AC3" s="15"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" customFormat="1" hidden="1" spans="1:31">
+    <row r="4" customFormat="1" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2348,11 +2385,12 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="10">
+      <c r="G4" s="10"/>
+      <c r="H4" s="11">
         <v>5</v>
       </c>
-      <c r="I4" s="12">
-        <v>5</v>
+      <c r="I4" s="14">
+        <v>4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2360,22 +2398,35 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="10">
+      <c r="L4" s="10"/>
+      <c r="M4" s="12">
         <v>11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="12">
-        <v>15</v>
-      </c>
-      <c r="P4"/>
-      <c r="AC4" s="13"/>
+      <c r="O4" s="14">
+        <v>18</v>
+      </c>
+      <c r="P4">
+        <v>56</v>
+      </c>
+      <c r="Q4">
+        <v>9</v>
+      </c>
+      <c r="R4" s="10">
+        <v>12</v>
+      </c>
+      <c r="U4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="15"/>
       <c r="AE4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:31">
+    <row r="5" customFormat="1" hidden="1" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2394,10 +2445,10 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="12">
         <v>3</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="14">
         <v>3</v>
       </c>
       <c r="J5">
@@ -2406,31 +2457,31 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="12">
         <v>11</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="14">
         <v>5</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="12">
         <v>2</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="14">
         <v>2</v>
       </c>
       <c r="S5"/>
-      <c r="AC5" s="13"/>
+      <c r="AC5" s="15"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="1" hidden="1" spans="1:31">
+    <row r="6" customFormat="1" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2449,13 +2500,13 @@
       <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="10">
         <v>3</v>
       </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="11">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2464,15 +2515,38 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10"/>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6" s="10">
+        <v>7</v>
+      </c>
+      <c r="S6">
+        <v>9</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="10">
+        <v>1</v>
+      </c>
+      <c r="X6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="15"/>
       <c r="AE6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:31">
+    <row r="7" customFormat="1" hidden="1" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2491,10 +2565,10 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="12">
         <v>5</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="14">
         <v>4</v>
       </c>
       <c r="J7">
@@ -2503,29 +2577,29 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="12">
         <v>4</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="12">
         <v>21</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
-      <c r="R7" s="12">
-        <v>2</v>
-      </c>
-      <c r="S7" s="10">
+      <c r="R7" s="14">
+        <v>2</v>
+      </c>
+      <c r="S7" s="12">
         <v>14</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="14">
         <v>1</v>
       </c>
       <c r="V7"/>
-      <c r="AC7" s="13"/>
+      <c r="AC7" s="15"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
@@ -2552,10 +2626,10 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2564,35 +2638,35 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="12">
         <v>2</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="14">
         <v>7</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="12">
         <v>3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="12">
-        <v>1</v>
-      </c>
-      <c r="S8" s="10">
+      <c r="R8" s="14">
+        <v>1</v>
+      </c>
+      <c r="S8" s="12">
         <v>14</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="14">
         <v>1</v>
       </c>
       <c r="V8"/>
-      <c r="AC8" s="13"/>
+      <c r="AC8" s="15"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
@@ -2616,10 +2690,10 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="10">
-        <v>2</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="H9" s="12">
+        <v>2</v>
+      </c>
+      <c r="I9" s="14">
         <v>2</v>
       </c>
       <c r="J9">
@@ -2628,26 +2702,26 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="12">
         <v>6</v>
       </c>
       <c r="N9">
         <v>3</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="14">
         <v>4</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="12">
         <v>2</v>
       </c>
       <c r="Q9">
         <v>3</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="14">
         <v>4</v>
       </c>
       <c r="S9"/>
-      <c r="AC9" s="13"/>
+      <c r="AC9" s="15"/>
       <c r="AE9" t="s">
         <v>33</v>
       </c>
@@ -2671,10 +2745,10 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="10">
-        <v>2</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="12">
+        <v>2</v>
+      </c>
+      <c r="I10" s="14">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2683,31 +2757,31 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="12">
         <v>7</v>
       </c>
       <c r="N10">
         <v>2</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="14">
         <v>3</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="12">
         <v>2</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="14">
         <v>3</v>
       </c>
       <c r="S10"/>
-      <c r="AC10" s="13"/>
+      <c r="AC10" s="15"/>
       <c r="AE10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" customFormat="1" hidden="1" spans="1:31">
+    <row r="11" customFormat="1" spans="1:31">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2726,10 +2800,11 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="10">
-        <v>2</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="G11" s="10"/>
+      <c r="H11" s="11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="14">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2738,26 +2813,31 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
+      <c r="L11" s="10"/>
+      <c r="M11" s="12">
         <v>15</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="14">
         <v>3</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="12">
         <v>2</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="14">
         <v>3</v>
       </c>
       <c r="S11"/>
-      <c r="AC11" s="13"/>
+      <c r="U11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="15"/>
       <c r="AE11" t="s">
         <v>41</v>
       </c>
@@ -2781,10 +2861,10 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="12">
         <v>6</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="14">
         <v>6</v>
       </c>
       <c r="J12">
@@ -2793,26 +2873,26 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="12">
         <v>11</v>
       </c>
       <c r="N12">
         <v>9</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="14">
         <v>13</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="12">
         <v>11</v>
       </c>
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="14">
         <v>13</v>
       </c>
       <c r="S12"/>
-      <c r="AC12" s="13"/>
+      <c r="AC12" s="15"/>
       <c r="AD12" t="s">
         <v>61</v>
       </c>
@@ -2820,7 +2900,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:31">
+    <row r="13" customFormat="1" hidden="1" spans="1:31">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2839,10 +2919,10 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="12">
         <v>5</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="14">
         <v>5</v>
       </c>
       <c r="J13">
@@ -2851,26 +2931,26 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="12">
         <v>11</v>
       </c>
       <c r="N13">
         <v>11</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="14">
         <v>15</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="12">
         <v>2</v>
       </c>
       <c r="Q13">
         <v>7</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="14">
         <v>9</v>
       </c>
       <c r="S13"/>
-      <c r="AC13" s="13"/>
+      <c r="AC13" s="15"/>
       <c r="AD13"/>
       <c r="AE13" t="s">
         <v>35</v>
@@ -2895,10 +2975,10 @@
       <c r="F14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="12">
         <v>5</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="14">
         <v>4</v>
       </c>
       <c r="J14">
@@ -2907,20 +2987,20 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="12">
         <v>6</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="14">
         <v>8</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
-      <c r="AC14" s="13"/>
+      <c r="AC14" s="15"/>
       <c r="AE14" t="s">
         <v>33</v>
       </c>
@@ -2944,10 +3024,10 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="12">
         <v>4</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15">
@@ -2956,17 +3036,17 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="12">
         <v>18</v>
       </c>
       <c r="N15">
         <v>1.4</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="14">
         <v>1.8</v>
       </c>
       <c r="P15"/>
-      <c r="AC15" s="13"/>
+      <c r="AC15" s="15"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
@@ -2990,10 +3070,10 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="12">
         <v>6</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="14">
         <v>5</v>
       </c>
       <c r="J16">
@@ -3002,31 +3082,31 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="12">
         <v>6</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="14">
         <v>5</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="12">
         <v>18</v>
       </c>
       <c r="Q16">
         <v>0.8</v>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="14">
         <v>1.1</v>
       </c>
       <c r="S16"/>
-      <c r="AC16" s="13"/>
+      <c r="AC16" s="15"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:31">
+    <row r="17" customFormat="1" hidden="1" spans="1:31">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3045,10 +3125,10 @@
       <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="12">
         <v>3</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="14">
         <v>3</v>
       </c>
       <c r="J17">
@@ -3057,40 +3137,40 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="12">
         <v>19</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17" s="12">
-        <v>1</v>
-      </c>
-      <c r="P17" s="10">
+      <c r="O17" s="14">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12">
         <v>2</v>
       </c>
       <c r="Q17">
         <v>4</v>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="14">
         <v>6</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="12">
         <v>21</v>
       </c>
       <c r="T17">
         <v>2</v>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="14">
         <v>3</v>
       </c>
       <c r="V17"/>
-      <c r="AC17" s="14"/>
+      <c r="AC17" s="16"/>
       <c r="AE17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" customFormat="1" hidden="1" spans="1:31">
+    <row r="18" customFormat="1" spans="1:31">
       <c r="A18">
         <v>18</v>
       </c>
@@ -3109,10 +3189,11 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="10">
+      <c r="G18" s="10"/>
+      <c r="H18" s="11">
         <v>4</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="14">
         <v>3</v>
       </c>
       <c r="J18">
@@ -3121,23 +3202,32 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="10">
+      <c r="L18" s="10"/>
+      <c r="M18" s="12">
         <v>15</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="14">
         <v>7</v>
       </c>
       <c r="P18"/>
       <c r="Q18"/>
-      <c r="R18"/>
+      <c r="R18" s="10"/>
       <c r="S18"/>
       <c r="T18"/>
-      <c r="U18"/>
+      <c r="U18" s="10"/>
       <c r="V18"/>
-      <c r="AC18" s="13"/>
+      <c r="X18" s="10"/>
+      <c r="Y18">
+        <v>61</v>
+      </c>
+      <c r="Z18" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="15"/>
       <c r="AE18" t="s">
         <v>41</v>
       </c>
@@ -3161,10 +3251,10 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="12">
         <v>5</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="14">
         <v>4</v>
       </c>
       <c r="J19">
@@ -3173,31 +3263,31 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="12">
         <v>23</v>
       </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19" s="12">
-        <v>1</v>
-      </c>
-      <c r="P19" s="10">
+      <c r="O19" s="14">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12">
         <v>7</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="14">
         <v>2</v>
       </c>
       <c r="S19"/>
-      <c r="AC19" s="13"/>
+      <c r="AC19" s="15"/>
       <c r="AE19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="1" hidden="1" spans="1:31">
+    <row r="20" customFormat="1" spans="1:31">
       <c r="A20">
         <v>20</v>
       </c>
@@ -3216,10 +3306,11 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="10">
+      <c r="G20" s="10"/>
+      <c r="H20" s="11">
         <v>6</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="14">
         <v>6</v>
       </c>
       <c r="J20">
@@ -3228,25 +3319,35 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="10">
+      <c r="L20" s="10">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
         <v>11</v>
       </c>
       <c r="N20">
         <v>24</v>
       </c>
-      <c r="O20" s="12">
+      <c r="O20" s="14">
         <v>30</v>
       </c>
       <c r="P20"/>
-      <c r="AC20" s="14"/>
+      <c r="R20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20">
+        <v>62</v>
+      </c>
+      <c r="Z20" s="10">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="16"/>
       <c r="AE20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="1" hidden="1" spans="1:31">
+    <row r="21" customFormat="1" spans="1:31">
       <c r="A21">
         <v>21</v>
       </c>
@@ -3265,10 +3366,11 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="10">
+      <c r="G21" s="10"/>
+      <c r="H21" s="11">
         <v>5</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="14">
         <v>4</v>
       </c>
       <c r="J21">
@@ -3277,35 +3379,39 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" s="10">
+      <c r="L21" s="10"/>
+      <c r="M21" s="12">
         <v>26</v>
       </c>
       <c r="N21">
         <v>2</v>
       </c>
-      <c r="O21" s="12">
-        <v>2</v>
-      </c>
-      <c r="P21" s="10">
+      <c r="O21" s="14">
+        <v>2</v>
+      </c>
+      <c r="P21" s="12">
         <v>11</v>
       </c>
       <c r="Q21">
         <v>30</v>
       </c>
-      <c r="R21" s="12">
+      <c r="R21" s="14">
         <v>42</v>
       </c>
-      <c r="S21" s="10">
+      <c r="S21" s="11">
         <v>2</v>
       </c>
       <c r="T21">
         <v>5</v>
       </c>
-      <c r="U21" s="12">
+      <c r="U21" s="14">
         <v>7</v>
       </c>
       <c r="V21"/>
-      <c r="AC21" s="13"/>
+      <c r="X21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="15"/>
       <c r="AE21" t="s">
         <v>41</v>
       </c>
@@ -3329,10 +3435,10 @@
       <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <v>4</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="14">
         <v>4</v>
       </c>
       <c r="J22">
@@ -3341,26 +3447,26 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="12">
         <v>6</v>
       </c>
       <c r="N22">
         <v>2</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="14">
         <v>4</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="12">
         <v>28</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="R22" s="12">
+      <c r="R22" s="14">
         <v>1</v>
       </c>
       <c r="S22"/>
-      <c r="AC22" s="13"/>
+      <c r="AC22" s="15"/>
       <c r="AE22" t="s">
         <v>33</v>
       </c>
@@ -3384,10 +3490,10 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="10">
-        <v>1</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="H23" s="12">
+        <v>1</v>
+      </c>
+      <c r="I23" s="14">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3396,34 +3502,34 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="12">
         <v>6</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
-      <c r="O23" s="12">
+      <c r="O23" s="14">
         <v>7</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="12">
         <v>2</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="R23" s="12">
+      <c r="R23" s="14">
         <v>1</v>
       </c>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
-      <c r="AC23" s="13"/>
+      <c r="AC23" s="15"/>
       <c r="AE23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" customFormat="1" hidden="1" spans="1:31">
+    <row r="24" customFormat="1" spans="1:31">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3442,10 +3548,11 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="10">
+      <c r="G24" s="10"/>
+      <c r="H24" s="11">
         <v>4</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="14">
         <v>4</v>
       </c>
       <c r="J24">
@@ -3454,26 +3561,36 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="M24" s="10">
+      <c r="L24" s="10"/>
+      <c r="M24" s="12">
         <v>15</v>
       </c>
       <c r="N24">
         <v>3</v>
       </c>
-      <c r="O24" s="12">
+      <c r="O24" s="14">
         <v>4</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="12">
         <v>11</v>
       </c>
       <c r="Q24">
         <v>8</v>
       </c>
-      <c r="R24" s="12">
+      <c r="R24" s="14">
         <v>11</v>
       </c>
       <c r="S24"/>
-      <c r="AC24" s="13"/>
+      <c r="U24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24">
+        <v>63</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="15"/>
       <c r="AE24" t="s">
         <v>41</v>
       </c>
@@ -3497,10 +3614,10 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="12">
         <v>3</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="14">
         <v>2</v>
       </c>
       <c r="J25">
@@ -3509,20 +3626,20 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="12">
         <v>7</v>
       </c>
       <c r="N25">
         <v>3</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="14">
         <v>5</v>
       </c>
       <c r="P25"/>
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25"/>
-      <c r="AC25" s="13"/>
+      <c r="AC25" s="15"/>
       <c r="AE25" t="s">
         <v>52</v>
       </c>
@@ -3546,10 +3663,10 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="12">
         <v>3</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="14">
         <v>2</v>
       </c>
       <c r="J26">
@@ -3558,31 +3675,31 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="12">
         <v>7</v>
       </c>
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="12">
+      <c r="O26" s="14">
         <v>4</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="12">
         <v>2</v>
       </c>
       <c r="Q26">
         <v>4</v>
       </c>
-      <c r="R26" s="12">
+      <c r="R26" s="14">
         <v>6</v>
       </c>
       <c r="S26"/>
-      <c r="AC26" s="13"/>
+      <c r="AC26" s="15"/>
       <c r="AE26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" customFormat="1" hidden="1" spans="1:31">
+    <row r="27" customFormat="1" spans="1:31">
       <c r="A27">
         <v>27</v>
       </c>
@@ -3601,10 +3718,11 @@
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="10">
+      <c r="G27" s="10"/>
+      <c r="H27" s="11">
         <v>8</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27">
@@ -3613,43 +3731,46 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" s="10">
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
         <v>11</v>
       </c>
       <c r="N27">
         <v>12</v>
       </c>
-      <c r="O27" s="12">
+      <c r="O27" s="14">
         <v>18</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="12">
         <v>56</v>
       </c>
       <c r="Q27">
         <v>24</v>
       </c>
-      <c r="R27" s="12">
+      <c r="R27" s="14">
         <v>30</v>
       </c>
-      <c r="S27" s="10">
+      <c r="S27" s="11">
         <v>57</v>
       </c>
       <c r="T27">
         <v>36</v>
       </c>
-      <c r="U27" s="12">
+      <c r="U27" s="14">
         <v>44</v>
       </c>
       <c r="V27"/>
-      <c r="AC27" s="14"/>
+      <c r="X27" s="10"/>
+      <c r="Z27" s="10"/>
+      <c r="AB27" s="10"/>
+      <c r="AC27" s="16"/>
       <c r="AE27" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" customFormat="1" hidden="1" spans="1:31">
+    <row r="28" customFormat="1" spans="1:31">
       <c r="A28">
         <v>28</v>
       </c>
@@ -3668,10 +3789,11 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="12">
+      <c r="G28" s="10"/>
+      <c r="H28" s="11">
+        <v>1</v>
+      </c>
+      <c r="I28" s="14">
         <v>0</v>
       </c>
       <c r="J28">
@@ -3680,25 +3802,35 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="M28" s="10">
+      <c r="L28" s="10"/>
+      <c r="M28" s="12">
         <v>2</v>
       </c>
       <c r="N28">
         <v>6</v>
       </c>
-      <c r="O28" s="12">
+      <c r="O28" s="14">
         <v>8</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
-      <c r="R28"/>
+      <c r="R28" s="10"/>
       <c r="S28"/>
-      <c r="AC28" s="13"/>
+      <c r="U28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28">
+        <v>21</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="15"/>
       <c r="AE28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:31">
+    <row r="29" customFormat="1" hidden="1" spans="1:31">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3717,10 +3849,10 @@
       <c r="F29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="12">
         <v>5</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29">
@@ -3729,40 +3861,40 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="12">
         <v>32</v>
       </c>
       <c r="N29">
         <v>30</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="14">
         <v>30</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="12">
         <v>2</v>
       </c>
       <c r="Q29">
         <v>3</v>
       </c>
-      <c r="R29" s="12">
+      <c r="R29" s="14">
         <v>5</v>
       </c>
-      <c r="S29" s="10">
+      <c r="S29" s="12">
         <v>21</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
-      <c r="U29" s="12">
+      <c r="U29" s="14">
         <v>3</v>
       </c>
       <c r="V29"/>
-      <c r="AC29" s="13"/>
+      <c r="AC29" s="15"/>
       <c r="AE29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:31">
+    <row r="30" customFormat="1" hidden="1" spans="1:31">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3781,10 +3913,10 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="12">
         <v>4</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30">
@@ -3793,31 +3925,31 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="12">
         <v>33</v>
       </c>
       <c r="N30">
         <v>50</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="14">
         <v>70</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="12">
         <v>2</v>
       </c>
       <c r="Q30">
         <v>2</v>
       </c>
-      <c r="R30" s="12">
+      <c r="R30" s="14">
         <v>4</v>
       </c>
       <c r="S30"/>
-      <c r="AC30" s="14"/>
+      <c r="AC30" s="16"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:31">
+    <row r="31" customFormat="1" hidden="1" spans="1:31">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3836,10 +3968,10 @@
       <c r="F31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="12">
         <v>4</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31">
@@ -3848,34 +3980,34 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="12">
         <v>33</v>
       </c>
       <c r="N31">
         <v>20</v>
       </c>
-      <c r="O31" s="12">
+      <c r="O31" s="14">
         <v>30</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="12">
         <v>35</v>
       </c>
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="R31" s="12">
+      <c r="R31" s="14">
         <v>1</v>
       </c>
       <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31"/>
-      <c r="AC31" s="14"/>
+      <c r="AC31" s="16"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:31">
+    <row r="32" customFormat="1" hidden="1" spans="1:31">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3894,10 +4026,10 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="12">
         <v>7</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="14">
         <v>6</v>
       </c>
       <c r="J32">
@@ -3910,7 +4042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" customFormat="1" hidden="1" spans="1:31">
+    <row r="33" customFormat="1" spans="1:31">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3929,10 +4061,11 @@
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="10">
+      <c r="G33" s="10"/>
+      <c r="H33" s="11">
         <v>8</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="14">
         <v>7</v>
       </c>
       <c r="J33">
@@ -3941,24 +4074,34 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" s="10">
+      <c r="L33" s="10"/>
+      <c r="M33" s="12">
         <v>11</v>
       </c>
       <c r="N33">
         <v>38</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="14">
         <v>52</v>
       </c>
       <c r="P33"/>
       <c r="Q33"/>
-      <c r="R33"/>
+      <c r="R33" s="10"/>
       <c r="S33"/>
+      <c r="U33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33">
+        <v>64</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="10"/>
       <c r="AE33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" customFormat="1" hidden="1" spans="1:31">
+    <row r="34" customFormat="1" spans="1:31">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3977,10 +4120,11 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="10">
+      <c r="G34" s="10"/>
+      <c r="H34" s="11">
         <v>3</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="14">
         <v>3</v>
       </c>
       <c r="J34">
@@ -3989,27 +4133,31 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="10">
+      <c r="L34" s="10">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12">
         <v>15</v>
       </c>
       <c r="N34">
         <v>3</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="14">
         <v>4</v>
       </c>
       <c r="P34"/>
       <c r="Q34"/>
-      <c r="R34"/>
+      <c r="R34" s="10"/>
       <c r="S34"/>
+      <c r="U34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Z34" s="10"/>
+      <c r="AB34" s="10"/>
       <c r="AE34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" customFormat="1" hidden="1" spans="1:31">
+    <row r="35" customFormat="1" spans="1:31">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4028,10 +4176,11 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="10">
+      <c r="G35" s="10"/>
+      <c r="H35" s="11">
         <v>3</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="14">
         <v>3</v>
       </c>
       <c r="J35">
@@ -4040,25 +4189,31 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="M35" s="10">
+      <c r="L35" s="10"/>
+      <c r="M35" s="12">
         <v>11</v>
       </c>
       <c r="N35">
         <v>18</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="14">
         <v>22</v>
       </c>
       <c r="P35"/>
+      <c r="R35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Z35" s="10"/>
+      <c r="AB35" s="10"/>
       <c r="AE35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" customFormat="1" hidden="1" spans="1:31">
+    <row r="36" customFormat="1" spans="1:31">
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="13">
         <v>144</v>
       </c>
       <c r="C36" t="s">
@@ -4073,10 +4228,11 @@
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="10">
+      <c r="G36" s="10"/>
+      <c r="H36" s="11">
         <v>3</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="14">
         <v>3</v>
       </c>
       <c r="J36">
@@ -4085,25 +4241,30 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="M36" s="10">
+      <c r="L36" s="10"/>
+      <c r="M36" s="12">
         <v>15</v>
       </c>
       <c r="N36">
         <v>3</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="14">
         <v>4</v>
       </c>
-      <c r="P36" s="10">
+      <c r="P36" s="12">
         <v>2</v>
       </c>
       <c r="Q36">
         <v>6</v>
       </c>
-      <c r="R36" s="12">
+      <c r="R36" s="14">
         <v>8</v>
       </c>
       <c r="S36"/>
+      <c r="U36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Z36" s="10"/>
+      <c r="AB36" s="10"/>
       <c r="AE36" t="s">
         <v>41</v>
       </c>
@@ -4127,10 +4288,10 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="12">
         <v>3</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="14">
         <v>3</v>
       </c>
       <c r="J37">
@@ -4139,22 +4300,22 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="M37" s="10">
+      <c r="M37" s="12">
         <v>7</v>
       </c>
       <c r="N37">
         <v>3</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="14">
         <v>4</v>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="12">
         <v>2</v>
       </c>
       <c r="Q37">
         <v>6</v>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="14">
         <v>8</v>
       </c>
       <c r="S37"/>
@@ -4162,7 +4323,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:31">
+    <row r="38" customFormat="1" hidden="1" spans="1:31">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4181,10 +4342,10 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="10">
-        <v>1</v>
-      </c>
-      <c r="I38" s="12">
+      <c r="H38" s="12">
+        <v>1</v>
+      </c>
+      <c r="I38" s="14">
         <v>1</v>
       </c>
       <c r="J38">
@@ -4193,22 +4354,22 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="M38" s="10">
+      <c r="M38" s="12">
         <v>21</v>
       </c>
       <c r="N38">
         <v>4</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="14">
         <v>5</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="12">
         <v>2</v>
       </c>
       <c r="Q38">
         <v>3</v>
       </c>
-      <c r="R38" s="12">
+      <c r="R38" s="14">
         <v>5</v>
       </c>
       <c r="S38"/>
@@ -4216,7 +4377,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:31">
+    <row r="39" customFormat="1" hidden="1" spans="1:31">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4235,10 +4396,10 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="10">
-        <v>1</v>
-      </c>
-      <c r="I39" s="12">
+      <c r="H39" s="12">
+        <v>1</v>
+      </c>
+      <c r="I39" s="14">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4247,22 +4408,22 @@
       <c r="K39">
         <v>1</v>
       </c>
-      <c r="M39" s="10">
+      <c r="M39" s="12">
         <v>5</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39" s="12">
-        <v>2</v>
-      </c>
-      <c r="P39" s="10">
+      <c r="O39" s="14">
+        <v>2</v>
+      </c>
+      <c r="P39" s="12">
         <v>2</v>
       </c>
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="12">
+      <c r="R39" s="14">
         <v>7</v>
       </c>
       <c r="S39"/>
@@ -4289,10 +4450,10 @@
       <c r="F40" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="12">
         <v>4</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="14">
         <v>3</v>
       </c>
       <c r="J40">
@@ -4301,22 +4462,22 @@
       <c r="K40">
         <v>1</v>
       </c>
-      <c r="M40" s="10">
+      <c r="M40" s="12">
         <v>7</v>
       </c>
       <c r="N40">
         <v>4</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O40" s="14">
         <v>5</v>
       </c>
-      <c r="P40" s="10">
+      <c r="P40" s="12">
         <v>38</v>
       </c>
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="12">
+      <c r="R40" s="14">
         <v>5</v>
       </c>
       <c r="S40"/>
@@ -4343,10 +4504,10 @@
       <c r="F41" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="10">
-        <v>2</v>
-      </c>
-      <c r="I41" s="12">
+      <c r="H41" s="12">
+        <v>2</v>
+      </c>
+      <c r="I41" s="14">
         <v>2</v>
       </c>
       <c r="J41">
@@ -4355,22 +4516,22 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="M41" s="10">
+      <c r="M41" s="12">
         <v>6</v>
       </c>
       <c r="N41">
         <v>3</v>
       </c>
-      <c r="O41" s="12">
+      <c r="O41" s="14">
         <v>3</v>
       </c>
-      <c r="P41" s="10">
+      <c r="P41" s="12">
         <v>39</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
-      <c r="R41" s="12">
+      <c r="R41" s="14">
         <v>3</v>
       </c>
       <c r="S41"/>
@@ -4397,10 +4558,10 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="12">
         <v>4</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="14">
         <v>3</v>
       </c>
       <c r="J42">
@@ -4409,22 +4570,22 @@
       <c r="K42">
         <v>1</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="12">
         <v>7</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42" s="12">
+      <c r="O42" s="14">
         <v>3</v>
       </c>
-      <c r="P42" s="10">
+      <c r="P42" s="12">
         <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
-      <c r="R42" s="12">
+      <c r="R42" s="14">
         <v>1</v>
       </c>
       <c r="S42"/>
@@ -4451,10 +4612,10 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="12">
         <v>7</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="14">
         <v>4</v>
       </c>
       <c r="J43">
@@ -4463,31 +4624,31 @@
       <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" s="10">
+      <c r="M43" s="12">
         <v>6</v>
       </c>
       <c r="N43">
         <v>5</v>
       </c>
-      <c r="O43" s="12">
+      <c r="O43" s="14">
         <v>5</v>
       </c>
-      <c r="P43" s="10">
+      <c r="P43" s="12">
         <v>14</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
-      <c r="R43" s="12">
-        <v>1</v>
-      </c>
-      <c r="S43" s="10">
+      <c r="R43" s="14">
+        <v>1</v>
+      </c>
+      <c r="S43" s="12">
         <v>18</v>
       </c>
       <c r="T43">
         <v>0.9</v>
       </c>
-      <c r="U43" s="12">
+      <c r="U43" s="14">
         <v>1.2</v>
       </c>
       <c r="V43"/>
@@ -4495,7 +4656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" customFormat="1" hidden="1" spans="1:31">
+    <row r="44" customFormat="1" spans="1:31">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4514,10 +4675,11 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="10">
+      <c r="G44" s="10"/>
+      <c r="H44" s="11">
         <v>6</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="14">
         <v>4</v>
       </c>
       <c r="J44">
@@ -4526,25 +4688,30 @@
       <c r="K44">
         <v>1</v>
       </c>
-      <c r="M44" s="10">
+      <c r="L44" s="10"/>
+      <c r="M44" s="12">
         <v>15</v>
       </c>
       <c r="N44">
         <v>2</v>
       </c>
-      <c r="O44" s="12">
-        <v>2</v>
-      </c>
-      <c r="P44" s="10">
+      <c r="O44" s="14">
+        <v>2</v>
+      </c>
+      <c r="P44" s="12">
         <v>42</v>
       </c>
       <c r="Q44">
         <v>8</v>
       </c>
-      <c r="R44" s="12">
+      <c r="R44" s="14">
         <v>12</v>
       </c>
       <c r="S44"/>
+      <c r="U44" s="10"/>
+      <c r="X44" s="10"/>
+      <c r="Z44" s="10"/>
+      <c r="AB44" s="10"/>
       <c r="AE44" t="s">
         <v>41</v>
       </c>
@@ -4568,10 +4735,10 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="12">
         <v>5</v>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="14">
         <v>4</v>
       </c>
       <c r="J45">
@@ -4580,31 +4747,31 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="12">
         <v>7</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
-      <c r="O45" s="12">
+      <c r="O45" s="14">
         <v>9</v>
       </c>
-      <c r="P45" s="10">
+      <c r="P45" s="12">
         <v>26</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
-      <c r="R45" s="12">
-        <v>2</v>
-      </c>
-      <c r="S45" s="10">
+      <c r="R45" s="14">
+        <v>2</v>
+      </c>
+      <c r="S45" s="12">
         <v>2</v>
       </c>
       <c r="T45">
         <v>7</v>
       </c>
-      <c r="U45" s="12">
+      <c r="U45" s="14">
         <v>8</v>
       </c>
       <c r="V45"/>
@@ -4612,7 +4779,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:31">
+    <row r="46" customFormat="1" hidden="1" spans="1:31">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4631,10 +4798,10 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="12">
         <v>10</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="14">
         <v>6</v>
       </c>
       <c r="J46">
@@ -4643,31 +4810,31 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="M46" s="10">
+      <c r="M46" s="12">
         <v>32</v>
       </c>
       <c r="N46">
         <v>40</v>
       </c>
-      <c r="O46" s="12">
+      <c r="O46" s="14">
         <v>40</v>
       </c>
-      <c r="P46" s="10">
+      <c r="P46" s="12">
         <v>33</v>
       </c>
       <c r="Q46">
         <v>30</v>
       </c>
-      <c r="R46" s="12">
+      <c r="R46" s="14">
         <v>30</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46" s="12">
         <v>19</v>
       </c>
       <c r="T46">
         <v>1</v>
       </c>
-      <c r="U46" s="12">
+      <c r="U46" s="14">
         <v>1</v>
       </c>
       <c r="V46"/>
@@ -4694,10 +4861,10 @@
       <c r="F47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="10">
-        <v>2</v>
-      </c>
-      <c r="I47" s="12">
+      <c r="H47" s="12">
+        <v>2</v>
+      </c>
+      <c r="I47" s="14">
         <v>1</v>
       </c>
       <c r="J47">
@@ -4706,13 +4873,13 @@
       <c r="K47">
         <v>0</v>
       </c>
-      <c r="M47" s="10">
+      <c r="M47" s="12">
         <v>11</v>
       </c>
       <c r="N47">
         <v>10</v>
       </c>
-      <c r="O47" s="12">
+      <c r="O47" s="14">
         <v>14</v>
       </c>
       <c r="P47"/>
@@ -4740,10 +4907,10 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="12">
         <v>4</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="14">
         <v>3</v>
       </c>
       <c r="J48">
@@ -4752,22 +4919,22 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="M48" s="10">
+      <c r="M48" s="12">
         <v>11</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
-      <c r="O48" s="12">
+      <c r="O48" s="14">
         <v>11</v>
       </c>
-      <c r="P48" s="10">
+      <c r="P48" s="12">
         <v>6</v>
       </c>
       <c r="Q48">
         <v>3</v>
       </c>
-      <c r="R48" s="12">
+      <c r="R48" s="14">
         <v>3</v>
       </c>
       <c r="S48"/>
@@ -4778,7 +4945,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" customFormat="1" hidden="1" spans="1:31">
+    <row r="49" customFormat="1" spans="1:31">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4797,10 +4964,11 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="10">
+      <c r="G49" s="10"/>
+      <c r="H49" s="11">
         <v>4</v>
       </c>
-      <c r="I49" s="12">
+      <c r="I49" s="14">
         <v>3</v>
       </c>
       <c r="J49">
@@ -4809,28 +4977,32 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="M49" s="10">
+      <c r="L49" s="10"/>
+      <c r="M49" s="12">
         <v>11</v>
       </c>
       <c r="N49">
         <v>7</v>
       </c>
-      <c r="O49" s="12">
+      <c r="O49" s="14">
         <v>11</v>
       </c>
-      <c r="P49" s="10">
+      <c r="P49" s="12">
         <v>45</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
-      <c r="R49" s="12">
+      <c r="R49" s="14">
         <v>3</v>
       </c>
       <c r="S49"/>
       <c r="T49"/>
-      <c r="U49"/>
+      <c r="U49" s="10"/>
       <c r="V49"/>
+      <c r="X49" s="10"/>
+      <c r="Z49" s="10"/>
+      <c r="AB49" s="10"/>
       <c r="AE49" t="s">
         <v>41</v>
       </c>
@@ -4854,10 +5026,10 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="12">
         <v>5</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="14">
         <v>4</v>
       </c>
       <c r="J50">
@@ -4866,22 +5038,22 @@
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="M50" s="10">
+      <c r="M50" s="12">
         <v>6</v>
       </c>
       <c r="N50">
         <v>5</v>
       </c>
-      <c r="O50" s="12">
+      <c r="O50" s="14">
         <v>7</v>
       </c>
-      <c r="P50" s="10">
+      <c r="P50" s="12">
         <v>18</v>
       </c>
       <c r="Q50">
         <v>1.1</v>
       </c>
-      <c r="R50" s="12">
+      <c r="R50" s="14">
         <v>1.7</v>
       </c>
       <c r="S50"/>
@@ -4908,10 +5080,10 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="12">
         <v>9</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="14">
         <v>6</v>
       </c>
       <c r="J51">
@@ -4920,22 +5092,22 @@
       <c r="K51">
         <v>1</v>
       </c>
-      <c r="M51" s="10">
+      <c r="M51" s="12">
         <v>6</v>
       </c>
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51" s="12">
+      <c r="O51" s="14">
         <v>3</v>
       </c>
-      <c r="P51" s="10">
+      <c r="P51" s="12">
         <v>49</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
-      <c r="R51" s="12">
+      <c r="R51" s="14">
         <v>1</v>
       </c>
       <c r="S51"/>
@@ -4943,7 +5115,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:31">
+    <row r="52" customFormat="1" hidden="1" spans="1:31">
       <c r="A52">
         <v>53</v>
       </c>
@@ -4962,10 +5134,10 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="10">
-        <v>1</v>
-      </c>
-      <c r="I52" s="12">
+      <c r="H52" s="12">
+        <v>1</v>
+      </c>
+      <c r="I52" s="14">
         <v>0</v>
       </c>
       <c r="J52">
@@ -4974,22 +5146,22 @@
       <c r="K52">
         <v>1</v>
       </c>
-      <c r="M52" s="10">
+      <c r="M52" s="12">
         <v>9</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
-      <c r="O52" s="12">
-        <v>2</v>
-      </c>
-      <c r="P52" s="10">
+      <c r="O52" s="14">
+        <v>2</v>
+      </c>
+      <c r="P52" s="12">
         <v>21</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="12">
+      <c r="R52" s="14">
         <v>2</v>
       </c>
       <c r="S52"/>
@@ -4997,7 +5169,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" customFormat="1" hidden="1" spans="1:31">
+    <row r="53" customFormat="1" spans="1:31">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5016,10 +5188,11 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="10">
+      <c r="G53" s="10"/>
+      <c r="H53" s="11">
         <v>5</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="14">
         <v>5</v>
       </c>
       <c r="J53">
@@ -5028,33 +5201,37 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="10">
         <v>6</v>
       </c>
-      <c r="M53" s="10">
+      <c r="M53" s="11">
         <v>50</v>
       </c>
       <c r="N53">
         <v>3</v>
       </c>
-      <c r="O53" s="12">
+      <c r="O53" s="14">
         <v>4</v>
       </c>
-      <c r="P53" s="10">
+      <c r="P53" s="11">
         <v>51</v>
       </c>
       <c r="Q53">
         <v>-0.5</v>
       </c>
-      <c r="R53" s="12">
+      <c r="R53" s="14">
         <v>-0.5</v>
       </c>
       <c r="S53"/>
+      <c r="U53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Z53" s="10"/>
+      <c r="AB53" s="10"/>
       <c r="AE53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" customFormat="1" hidden="1" spans="1:31">
+    <row r="54" customFormat="1" spans="1:31">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5073,13 +5250,13 @@
       <c r="F54" t="s">
         <v>47</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="10">
         <v>14</v>
       </c>
-      <c r="H54" s="10">
-        <v>2</v>
-      </c>
-      <c r="I54" s="12">
+      <c r="H54" s="11">
+        <v>2</v>
+      </c>
+      <c r="I54" s="14">
         <v>1</v>
       </c>
       <c r="J54">
@@ -5088,39 +5265,43 @@
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="M54" s="10">
+      <c r="L54" s="10"/>
+      <c r="M54" s="11">
         <v>15</v>
       </c>
       <c r="N54">
         <v>3</v>
       </c>
-      <c r="O54" s="12">
+      <c r="O54" s="14">
         <v>4</v>
       </c>
-      <c r="P54" s="10">
+      <c r="P54" s="11">
         <v>14</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="12">
-        <v>1</v>
-      </c>
-      <c r="S54" s="10">
+      <c r="R54" s="14">
+        <v>1</v>
+      </c>
+      <c r="S54" s="11">
         <v>52</v>
       </c>
       <c r="T54">
         <v>3</v>
       </c>
-      <c r="U54" s="12">
+      <c r="U54" s="14">
         <v>5</v>
       </c>
       <c r="V54"/>
+      <c r="X54" s="10"/>
+      <c r="Z54" s="10"/>
+      <c r="AB54" s="10"/>
       <c r="AE54" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="55" customFormat="1" hidden="1" spans="1:31">
+    <row r="55" customFormat="1" spans="1:31">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5139,10 +5320,11 @@
       <c r="F55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="10">
+      <c r="G55" s="10"/>
+      <c r="H55" s="11">
         <v>4</v>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="14">
         <v>3</v>
       </c>
       <c r="J55">
@@ -5151,89 +5333,117 @@
       <c r="K55">
         <v>1</v>
       </c>
+      <c r="L55" s="10"/>
       <c r="M55">
         <v>15</v>
       </c>
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="10">
         <v>3</v>
       </c>
-      <c r="P55" s="10">
+      <c r="P55" s="11">
         <v>60</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
-      <c r="R55" s="12">
+      <c r="R55" s="14">
         <v>1</v>
       </c>
       <c r="S55"/>
-      <c r="AA55" s="12"/>
+      <c r="U55" s="10"/>
+      <c r="X55" s="10"/>
+      <c r="Z55" s="10"/>
+      <c r="AA55" s="14"/>
+      <c r="AB55" s="10"/>
       <c r="AE55" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" customFormat="1" hidden="1" spans="3:31">
+    <row r="56" customFormat="1" spans="1:31">
+      <c r="A56">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>147</v>
+      </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>34</v>
-      </c>
-      <c r="H56" s="10">
+        <v>47</v>
+      </c>
+      <c r="G56" s="10">
         <v>3</v>
       </c>
-      <c r="I56" s="12">
-        <v>2</v>
+      <c r="H56" s="11">
+        <v>2</v>
+      </c>
+      <c r="I56" s="14">
+        <v>1</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56"/>
+        <v>1</v>
+      </c>
+      <c r="L56" s="10"/>
       <c r="M56">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="N56">
-        <v>2</v>
-      </c>
-      <c r="O56">
-        <v>2</v>
-      </c>
-      <c r="P56" s="10">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="O56" s="10">
+        <v>4</v>
+      </c>
+      <c r="P56" s="11">
+        <v>11</v>
       </c>
       <c r="Q56">
-        <v>1</v>
-      </c>
-      <c r="R56" s="12">
-        <v>2</v>
-      </c>
-      <c r="S56"/>
-      <c r="AA56" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="R56" s="14">
+        <v>18</v>
+      </c>
+      <c r="S56" s="11">
+        <v>14</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56" s="14">
+        <v>1</v>
+      </c>
+      <c r="X56" s="10"/>
+      <c r="Z56" s="10"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="10"/>
       <c r="AE56" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" customFormat="1" hidden="1" spans="2:31">
+    <row r="57" customFormat="1" spans="1:31">
+      <c r="A57">
+        <v>58</v>
+      </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
@@ -5241,109 +5451,94 @@
       <c r="F57" t="s">
         <v>47</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="10">
         <v>3</v>
       </c>
-      <c r="H57" s="10">
-        <v>2</v>
-      </c>
-      <c r="I57" s="12">
+      <c r="H57" s="11">
+        <v>2</v>
+      </c>
+      <c r="I57" s="14">
         <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57">
         <v>1</v>
       </c>
-      <c r="M57">
-        <v>45</v>
+      <c r="L57" s="10"/>
+      <c r="M57" s="11">
+        <v>2</v>
       </c>
       <c r="N57">
-        <v>3</v>
-      </c>
-      <c r="O57">
-        <v>4</v>
-      </c>
-      <c r="P57" s="10">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="O57" s="14">
+        <v>6</v>
+      </c>
+      <c r="P57" s="11">
+        <v>2</v>
       </c>
       <c r="Q57">
-        <v>12</v>
-      </c>
-      <c r="R57" s="12">
-        <v>18</v>
-      </c>
-      <c r="S57" s="10">
-        <v>14</v>
-      </c>
-      <c r="T57">
-        <v>1</v>
-      </c>
-      <c r="U57" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="R57" s="14">
+        <v>6</v>
+      </c>
+      <c r="U57" s="10"/>
+      <c r="X57" s="10"/>
+      <c r="Z57" s="10"/>
+      <c r="AB57" s="10"/>
       <c r="AE57" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="58" customFormat="1" hidden="1" spans="2:31">
+    <row r="58" spans="1:31">
+      <c r="A58">
+        <v>59</v>
+      </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" s="10">
+      <c r="G58" s="10"/>
+      <c r="H58">
         <v>3</v>
       </c>
-      <c r="I58" s="12">
-        <v>3</v>
+      <c r="I58" s="10">
+        <v>2</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="M58" s="10">
-        <v>45</v>
-      </c>
-      <c r="N58">
-        <v>2</v>
-      </c>
-      <c r="O58" s="12">
-        <v>3</v>
-      </c>
-      <c r="P58" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q58">
-        <v>2</v>
-      </c>
-      <c r="R58" s="12">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L58" s="10"/>
       <c r="AE58" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" customFormat="1" hidden="1" spans="2:31">
+    <row r="59" spans="1:31">
+      <c r="A59">
+        <v>60</v>
+      </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
         <v>64</v>
@@ -5354,28 +5549,42 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="10">
+      <c r="G59" s="10"/>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59" s="10">
         <v>3</v>
       </c>
-      <c r="I59" s="12">
-        <v>3</v>
-      </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L59" s="10"/>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59">
+        <v>7</v>
+      </c>
+      <c r="O59" s="10">
+        <v>9</v>
       </c>
       <c r="AE59" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="60" customFormat="1" hidden="1" spans="2:31">
+    <row r="60" spans="1:31">
+      <c r="A60">
+        <v>61</v>
+      </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D60" t="s">
         <v>46</v>
@@ -5384,16 +5593,14 @@
         <v>33</v>
       </c>
       <c r="F60" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60">
-        <v>3</v>
-      </c>
-      <c r="H60" s="10">
-        <v>2</v>
-      </c>
-      <c r="I60" s="12">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60" s="10">
+        <v>2</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -5401,35 +5608,65 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="M60" s="10">
-        <v>2</v>
-      </c>
-      <c r="N60">
-        <v>5</v>
-      </c>
-      <c r="O60" s="12">
-        <v>6</v>
-      </c>
-      <c r="P60" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q60">
-        <v>5</v>
-      </c>
-      <c r="R60" s="12">
-        <v>6</v>
-      </c>
+      <c r="L60" s="10"/>
       <c r="AE60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
+    <row r="61" hidden="1" spans="7:31">
+      <c r="G61"/>
+      <c r="I61"/>
+      <c r="L61"/>
+      <c r="O61"/>
+      <c r="R61"/>
+      <c r="U61"/>
+      <c r="X61"/>
+      <c r="Z61"/>
+      <c r="AB61"/>
+      <c r="AE61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" t="s">
+        <v>158</v>
+      </c>
+      <c r="D62" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" t="s">
+        <v>47</v>
+      </c>
+      <c r="G62" s="10">
+        <v>14</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62" s="10">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE61" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="30">
-      <filters>
-        <filter val="F"/>
+      <filters blank="1">
+        <filter val="C"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -5443,7 +5680,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -5471,19 +5708,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:10">
@@ -5491,13 +5728,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -5509,19 +5746,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5532,16 +5769,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" t="s">
         <v>168</v>
       </c>
-      <c r="C4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" t="s">
-        <v>165</v>
-      </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -5552,16 +5789,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -5572,13 +5809,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -5589,16 +5826,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5609,13 +5846,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5629,13 +5866,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5649,13 +5886,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5669,13 +5906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5686,16 +5923,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5706,16 +5943,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5726,19 +5963,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5749,16 +5986,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5769,16 +6006,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5789,13 +6026,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5809,16 +6046,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5829,13 +6066,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5849,13 +6086,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5869,16 +6106,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5889,16 +6126,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5909,13 +6146,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5929,19 +6166,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5952,13 +6189,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5972,16 +6209,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5995,16 +6232,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -6015,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6035,19 +6272,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6061,13 +6298,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C30" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6081,19 +6318,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -6104,19 +6341,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -6127,19 +6364,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -6150,16 +6387,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -6170,16 +6407,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -6190,19 +6427,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6216,13 +6453,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6236,16 +6473,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -6256,13 +6493,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6279,16 +6516,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -6299,13 +6536,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6322,19 +6559,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6348,13 +6585,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6368,13 +6605,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6388,19 +6625,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -6411,16 +6648,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E46" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6431,13 +6668,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C47" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6451,19 +6688,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C48" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D48" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -6474,13 +6711,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D49" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6494,19 +6731,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D50" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -6517,13 +6754,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6537,13 +6774,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6557,13 +6794,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6577,13 +6814,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C54" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D54" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -6600,16 +6837,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C55" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D55" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6623,16 +6860,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D56" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E56" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6646,16 +6883,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C57" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D57" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E57" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6669,16 +6906,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C58" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E58" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6692,16 +6929,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6715,16 +6952,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E60" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6738,19 +6975,22 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>214</v>
+        <v>217</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6761,18 +7001,156 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E62">
         <v>20</v>
       </c>
       <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>260</v>
+      </c>
+      <c r="C63" t="s">
+        <v>260</v>
+      </c>
+      <c r="D63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s">
+        <v>169</v>
+      </c>
+      <c r="G63">
+        <v>7</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" t="s">
+        <v>261</v>
+      </c>
+      <c r="D64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" t="s">
+        <v>173</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>262</v>
+      </c>
+      <c r="C65" t="s">
+        <v>262</v>
+      </c>
+      <c r="D65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E65">
+        <v>14</v>
+      </c>
+      <c r="G65">
+        <v>6</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>263</v>
+      </c>
+      <c r="C66" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" t="s">
+        <v>168</v>
+      </c>
+      <c r="E66" t="s">
+        <v>199</v>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:9">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" t="s">
+        <v>265</v>
+      </c>
+      <c r="D67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>217</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" t="s">
+        <v>266</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68">
+        <v>21</v>
+      </c>
+      <c r="I68">
         <v>-1</v>
       </c>
     </row>
@@ -6786,7 +7164,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.425" customWidth="1"/>
@@ -6809,13 +7187,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -6842,10 +7220,10 @@
         <v>22</v>
       </c>
       <c r="N1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="O1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:9">
@@ -6853,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6882,10 +7260,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6905,10 +7283,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6922,10 +7300,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6957,10 +7335,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6980,10 +7358,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -7003,10 +7381,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7026,10 +7404,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7049,10 +7427,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7072,10 +7450,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7101,10 +7479,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7130,10 +7508,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7153,10 +7531,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7176,10 +7554,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7199,10 +7577,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" t="s">
         <v>273</v>
-      </c>
-      <c r="C16" t="s">
-        <v>263</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7222,10 +7600,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7245,10 +7623,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C18" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7268,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7285,10 +7663,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7302,10 +7680,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7319,10 +7697,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7334,6 +7712,29 @@
         <v>59</v>
       </c>
       <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:7">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>65</v>
+      </c>
+      <c r="G23">
         <v>1</v>
       </c>
     </row>
@@ -7370,16 +7771,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="G1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:6">
@@ -7387,13 +7788,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7407,13 +7808,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -7424,13 +7825,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -7441,13 +7842,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7461,13 +7862,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7481,13 +7882,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7501,13 +7902,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7521,13 +7922,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -7541,13 +7942,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -7594,7 +7995,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7602,19 +8003,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7622,19 +8023,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7642,19 +8043,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7662,16 +8063,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7679,16 +8080,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F6" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7696,16 +8097,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7713,13 +8114,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7727,13 +8128,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7741,13 +8142,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7795,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -7846,7 +8247,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -7855,13 +8256,13 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="J1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7869,13 +8270,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -7887,13 +8288,13 @@
         <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="J2" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7901,13 +8302,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7919,13 +8320,13 @@
         <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="J3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7933,13 +8334,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -7951,13 +8352,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="J4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7965,13 +8366,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7983,13 +8384,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="J5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7997,13 +8398,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -8015,13 +8416,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="J6" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8029,13 +8430,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -8047,13 +8448,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="J7" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8061,10 +8462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8076,13 +8477,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="J8" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8090,10 +8491,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8105,13 +8506,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="J9" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8119,10 +8520,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" t="s">
         <v>341</v>
-      </c>
-      <c r="D10" t="s">
-        <v>330</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8134,13 +8535,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="J10" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="9:9">
@@ -8188,7 +8589,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -8197,25 +8598,25 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K1" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="L1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="M1" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="N1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -8223,13 +8624,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8241,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -8267,13 +8668,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -8285,10 +8686,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -8311,13 +8712,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -8329,10 +8730,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="J4">
         <v>10</v>

--- a/Assets/Resources/Configurations/NewCards.xlsx
+++ b/Assets/Resources/Configurations/NewCards.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="10480" firstSheet="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="391">
   <si>
     <t>ID</t>
   </si>
@@ -957,127 +957,205 @@
     <t>Param</t>
   </si>
   <si>
+    <t>歌力+X</t>
+  </si>
+  <si>
+    <t>VRaisingAddAbilityEffect</t>
+  </si>
+  <si>
+    <t>CASingingAbility</t>
+  </si>
+  <si>
+    <t>游戏力+X</t>
+  </si>
+  <si>
+    <t>CAGamingAbility</t>
+  </si>
+  <si>
+    <t>杂谈力+X</t>
+  </si>
+  <si>
+    <t>CAChattingAbility</t>
+  </si>
+  <si>
+    <t>体力+X</t>
+  </si>
+  <si>
+    <t>VRaisingAddAttributeEffect</t>
+  </si>
+  <si>
+    <t>CAStamina</t>
+  </si>
+  <si>
+    <t>压力+X</t>
+  </si>
+  <si>
+    <t>CAPressure</t>
+  </si>
+  <si>
+    <t>金钱+X</t>
+  </si>
+  <si>
+    <t>CAMoney</t>
+  </si>
+  <si>
+    <t>SkipEvent</t>
+  </si>
+  <si>
+    <t>跳过</t>
+  </si>
+  <si>
+    <t>VRaisingSkipEventEffect</t>
+  </si>
+  <si>
+    <t>ModifySchedule</t>
+  </si>
+  <si>
+    <t>VRaisingModifyScheduleEffect</t>
+  </si>
+  <si>
+    <t>AddRandomM</t>
+  </si>
+  <si>
+    <t>VRaisingAddRandomCardEffect</t>
+  </si>
+  <si>
+    <t>歌力提升率+X%</t>
+  </si>
+  <si>
+    <t>CASingingAbilityConversionRatio</t>
+  </si>
+  <si>
+    <t>游戏力提升率+X%</t>
+  </si>
+  <si>
+    <t>CAGamingAbilityConversionRatio</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+X%</t>
+  </si>
+  <si>
+    <t>CAChattingAbilityConversionRatio</t>
+  </si>
+  <si>
+    <t>歌力提升转化率+X%</t>
+  </si>
+  <si>
+    <t>CASingingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>游戏力转化率+X%</t>
+  </si>
+  <si>
+    <t>CAGamingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>杂谈力转化率+X%</t>
+  </si>
+  <si>
+    <t>CAChattingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>粉丝数+X</t>
+  </si>
+  <si>
+    <t>CAFollowerCount</t>
+  </si>
+  <si>
+    <t>舰长数+X</t>
+  </si>
+  <si>
+    <t>CAMembershipCount</t>
+  </si>
+  <si>
+    <t>粉丝同接转化率+X%</t>
+  </si>
+  <si>
+    <t>CAFollowerToViewerRatio</t>
+  </si>
+  <si>
+    <t>直播分成率+X%</t>
+  </si>
+  <si>
+    <t>BARevenueShareRate</t>
+  </si>
+  <si>
+    <t>Type_M</t>
+  </si>
+  <si>
+    <t>sadf</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>BackGroundColor</t>
+  </si>
+  <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>声乐练习</t>
+  </si>
+  <si>
     <t>AddSinging</t>
   </si>
   <si>
-    <t>safdsafsadfasdf</t>
-  </si>
-  <si>
-    <t>VRaisingAddAbilityEffect</t>
-  </si>
-  <si>
-    <t>CASingingAbility</t>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>游戏练习</t>
   </si>
   <si>
     <t>AddGaming</t>
   </si>
   <si>
-    <t>CAGamingAbility</t>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>对话练习</t>
   </si>
   <si>
     <t>AddChatting</t>
   </si>
   <si>
-    <t>CAChattingAbility</t>
-  </si>
-  <si>
-    <t>AddStamina</t>
-  </si>
-  <si>
-    <t>VRaisingAddAttributeEffect</t>
-  </si>
-  <si>
-    <t>CAStamina</t>
-  </si>
-  <si>
-    <t>AddPressure</t>
-  </si>
-  <si>
-    <t>Add Pressure</t>
-  </si>
-  <si>
-    <t>CAPressure</t>
-  </si>
-  <si>
-    <t>AddMoney</t>
-  </si>
-  <si>
-    <t>Add Money</t>
-  </si>
-  <si>
-    <t>CAMoney</t>
-  </si>
-  <si>
-    <t>SkipEvent</t>
-  </si>
-  <si>
-    <t>VRaisingSkipEventEffect</t>
-  </si>
-  <si>
-    <t>ModifySchedule</t>
-  </si>
-  <si>
-    <t>VRaisingModifyScheduleEffect</t>
-  </si>
-  <si>
-    <t>AddRandomM</t>
-  </si>
-  <si>
-    <t>VRaisingAddRandomCardEffect</t>
-  </si>
-  <si>
-    <t>Type_M</t>
-  </si>
-  <si>
-    <t>sadf</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>BackGroundColor</t>
-  </si>
-  <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
     <t>#FFB200</t>
   </si>
   <si>
+    <t>小睡一会</t>
+  </si>
+  <si>
+    <t>Recover 25 Stamina</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
     <t>Nap</t>
   </si>
   <si>
-    <t>Recover 10 Stamina</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
+    <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>Recover 55 Stamina</t>
   </si>
   <si>
     <t>Break</t>
   </si>
   <si>
-    <t>Recover 20 Stamina</t>
-  </si>
-  <si>
-    <t>DayOff!</t>
-  </si>
-  <si>
-    <t>Recover 30 Stamina</t>
+    <t>休息一天</t>
+  </si>
+  <si>
+    <t>Recover 100 Stamina</t>
   </si>
   <si>
     <t>DayOff</t>
@@ -1119,7 +1197,7 @@
     <t>FailEvent</t>
   </si>
   <si>
-    <t>Stream1</t>
+    <t>歌回</t>
   </si>
   <si>
     <t>Stream</t>
@@ -1128,10 +1206,10 @@
     <t>#AB0580</t>
   </si>
   <si>
-    <t>Stream2</t>
-  </si>
-  <si>
-    <t>Stream3</t>
+    <t>游戏回</t>
+  </si>
+  <si>
+    <t>杂谈回</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1818,7 +1896,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -2207,7 +2284,7 @@
       <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2225,7 +2302,7 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="12" t="s">
@@ -2234,7 +2311,7 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="12" t="s">
@@ -2243,7 +2320,7 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="12" t="s">
@@ -2252,13 +2329,13 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="10" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -2296,7 +2373,7 @@
       <c r="H2" s="12">
         <v>4</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="10">
         <v>3</v>
       </c>
       <c r="J2">
@@ -2311,11 +2388,11 @@
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="10">
         <v>7</v>
       </c>
       <c r="P2"/>
-      <c r="AC2" s="15"/>
+      <c r="AC2" s="14"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
@@ -2342,7 +2419,7 @@
       <c r="H3" s="12">
         <v>0</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="10">
         <v>0</v>
       </c>
       <c r="J3">
@@ -2357,11 +2434,11 @@
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="10">
         <v>4</v>
       </c>
       <c r="P3"/>
-      <c r="AC3" s="15"/>
+      <c r="AC3" s="14"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
@@ -2389,7 +2466,7 @@
       <c r="H4" s="11">
         <v>5</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="10">
         <v>4</v>
       </c>
       <c r="J4">
@@ -2405,7 +2482,7 @@
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="10">
         <v>18</v>
       </c>
       <c r="P4">
@@ -2421,7 +2498,7 @@
       <c r="X4" s="10"/>
       <c r="Z4" s="10"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="15"/>
+      <c r="AC4" s="14"/>
       <c r="AE4" t="s">
         <v>41</v>
       </c>
@@ -2448,7 +2525,7 @@
       <c r="H5" s="12">
         <v>3</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <v>3</v>
       </c>
       <c r="J5">
@@ -2463,7 +2540,7 @@
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="10">
         <v>5</v>
       </c>
       <c r="P5" s="12">
@@ -2472,11 +2549,11 @@
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="10">
         <v>2</v>
       </c>
       <c r="S5"/>
-      <c r="AC5" s="15"/>
+      <c r="AC5" s="14"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
@@ -2506,7 +2583,7 @@
       <c r="H6" s="11">
         <v>1</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="10">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2541,7 +2618,7 @@
       <c r="X6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AB6" s="10"/>
-      <c r="AC6" s="15"/>
+      <c r="AC6" s="14"/>
       <c r="AE6" t="s">
         <v>41</v>
       </c>
@@ -2568,7 +2645,7 @@
       <c r="H7" s="12">
         <v>5</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="10">
         <v>4</v>
       </c>
       <c r="J7">
@@ -2586,7 +2663,7 @@
       <c r="Q7">
         <v>2</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="10">
         <v>2</v>
       </c>
       <c r="S7" s="12">
@@ -2595,11 +2672,11 @@
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7" s="14">
+      <c r="U7" s="10">
         <v>1</v>
       </c>
       <c r="V7"/>
-      <c r="AC7" s="15"/>
+      <c r="AC7" s="14"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
@@ -2629,7 +2706,7 @@
       <c r="H8" s="12">
         <v>1</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2644,7 +2721,7 @@
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="10">
         <v>7</v>
       </c>
       <c r="P8" s="12">
@@ -2653,7 +2730,7 @@
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="10">
         <v>1</v>
       </c>
       <c r="S8" s="12">
@@ -2662,11 +2739,11 @@
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="14">
+      <c r="U8" s="10">
         <v>1</v>
       </c>
       <c r="V8"/>
-      <c r="AC8" s="15"/>
+      <c r="AC8" s="14"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
@@ -2693,7 +2770,7 @@
       <c r="H9" s="12">
         <v>2</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="10">
         <v>2</v>
       </c>
       <c r="J9">
@@ -2708,7 +2785,7 @@
       <c r="N9">
         <v>3</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="10">
         <v>4</v>
       </c>
       <c r="P9" s="12">
@@ -2717,11 +2794,11 @@
       <c r="Q9">
         <v>3</v>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="10">
         <v>4</v>
       </c>
       <c r="S9"/>
-      <c r="AC9" s="15"/>
+      <c r="AC9" s="14"/>
       <c r="AE9" t="s">
         <v>33</v>
       </c>
@@ -2748,7 +2825,7 @@
       <c r="H10" s="12">
         <v>2</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="10">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2763,7 +2840,7 @@
       <c r="N10">
         <v>2</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="10">
         <v>3</v>
       </c>
       <c r="P10" s="12">
@@ -2772,11 +2849,11 @@
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="14">
+      <c r="R10" s="10">
         <v>3</v>
       </c>
       <c r="S10"/>
-      <c r="AC10" s="15"/>
+      <c r="AC10" s="14"/>
       <c r="AE10" t="s">
         <v>52</v>
       </c>
@@ -2804,7 +2881,7 @@
       <c r="H11" s="11">
         <v>2</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="10">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2820,7 +2897,7 @@
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="10">
         <v>3</v>
       </c>
       <c r="P11" s="12">
@@ -2829,7 +2906,7 @@
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="14">
+      <c r="R11" s="10">
         <v>3</v>
       </c>
       <c r="S11"/>
@@ -2837,7 +2914,7 @@
       <c r="X11" s="10"/>
       <c r="Z11" s="10"/>
       <c r="AB11" s="10"/>
-      <c r="AC11" s="15"/>
+      <c r="AC11" s="14"/>
       <c r="AE11" t="s">
         <v>41</v>
       </c>
@@ -2864,7 +2941,7 @@
       <c r="H12" s="12">
         <v>6</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="10">
         <v>6</v>
       </c>
       <c r="J12">
@@ -2879,7 +2956,7 @@
       <c r="N12">
         <v>9</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="10">
         <v>13</v>
       </c>
       <c r="P12" s="12">
@@ -2888,11 +2965,11 @@
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="14">
+      <c r="R12" s="10">
         <v>13</v>
       </c>
       <c r="S12"/>
-      <c r="AC12" s="15"/>
+      <c r="AC12" s="14"/>
       <c r="AD12" t="s">
         <v>61</v>
       </c>
@@ -2922,7 +2999,7 @@
       <c r="H13" s="12">
         <v>5</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="10">
         <v>5</v>
       </c>
       <c r="J13">
@@ -2937,7 +3014,7 @@
       <c r="N13">
         <v>11</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="10">
         <v>15</v>
       </c>
       <c r="P13" s="12">
@@ -2946,11 +3023,11 @@
       <c r="Q13">
         <v>7</v>
       </c>
-      <c r="R13" s="14">
+      <c r="R13" s="10">
         <v>9</v>
       </c>
       <c r="S13"/>
-      <c r="AC13" s="15"/>
+      <c r="AC13" s="14"/>
       <c r="AD13"/>
       <c r="AE13" t="s">
         <v>35</v>
@@ -2978,7 +3055,7 @@
       <c r="H14" s="12">
         <v>5</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="10">
         <v>4</v>
       </c>
       <c r="J14">
@@ -2993,14 +3070,14 @@
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="10">
         <v>8</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14"/>
-      <c r="AC14" s="15"/>
+      <c r="AC14" s="14"/>
       <c r="AE14" t="s">
         <v>33</v>
       </c>
@@ -3027,7 +3104,7 @@
       <c r="H15" s="12">
         <v>4</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="10">
         <v>4</v>
       </c>
       <c r="J15">
@@ -3042,11 +3119,11 @@
       <c r="N15">
         <v>1.4</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="10">
         <v>1.8</v>
       </c>
       <c r="P15"/>
-      <c r="AC15" s="15"/>
+      <c r="AC15" s="14"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
@@ -3073,7 +3150,7 @@
       <c r="H16" s="12">
         <v>6</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="10">
         <v>5</v>
       </c>
       <c r="J16">
@@ -3088,7 +3165,7 @@
       <c r="N16">
         <v>4</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="10">
         <v>5</v>
       </c>
       <c r="P16" s="12">
@@ -3097,11 +3174,11 @@
       <c r="Q16">
         <v>0.8</v>
       </c>
-      <c r="R16" s="14">
+      <c r="R16" s="10">
         <v>1.1</v>
       </c>
       <c r="S16"/>
-      <c r="AC16" s="15"/>
+      <c r="AC16" s="14"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
@@ -3128,7 +3205,7 @@
       <c r="H17" s="12">
         <v>3</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="10">
         <v>3</v>
       </c>
       <c r="J17">
@@ -3143,7 +3220,7 @@
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17" s="14">
+      <c r="O17" s="10">
         <v>1</v>
       </c>
       <c r="P17" s="12">
@@ -3152,7 +3229,7 @@
       <c r="Q17">
         <v>4</v>
       </c>
-      <c r="R17" s="14">
+      <c r="R17" s="10">
         <v>6</v>
       </c>
       <c r="S17" s="12">
@@ -3161,11 +3238,11 @@
       <c r="T17">
         <v>2</v>
       </c>
-      <c r="U17" s="14">
+      <c r="U17" s="10">
         <v>3</v>
       </c>
       <c r="V17"/>
-      <c r="AC17" s="16"/>
+      <c r="AC17" s="15"/>
       <c r="AE17" t="s">
         <v>35</v>
       </c>
@@ -3193,7 +3270,7 @@
       <c r="H18" s="11">
         <v>4</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="10">
         <v>3</v>
       </c>
       <c r="J18">
@@ -3209,7 +3286,7 @@
       <c r="N18">
         <v>5</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="10">
         <v>7</v>
       </c>
       <c r="P18"/>
@@ -3227,7 +3304,7 @@
         <v>1.5</v>
       </c>
       <c r="AB18" s="10"/>
-      <c r="AC18" s="15"/>
+      <c r="AC18" s="14"/>
       <c r="AE18" t="s">
         <v>41</v>
       </c>
@@ -3254,7 +3331,7 @@
       <c r="H19" s="12">
         <v>5</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="10">
         <v>4</v>
       </c>
       <c r="J19">
@@ -3269,7 +3346,7 @@
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="10">
         <v>1</v>
       </c>
       <c r="P19" s="12">
@@ -3278,11 +3355,11 @@
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R19" s="14">
+      <c r="R19" s="10">
         <v>2</v>
       </c>
       <c r="S19"/>
-      <c r="AC19" s="15"/>
+      <c r="AC19" s="14"/>
       <c r="AE19" t="s">
         <v>52</v>
       </c>
@@ -3310,7 +3387,7 @@
       <c r="H20" s="11">
         <v>6</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="10">
         <v>6</v>
       </c>
       <c r="J20">
@@ -3328,7 +3405,7 @@
       <c r="N20">
         <v>24</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="10">
         <v>30</v>
       </c>
       <c r="P20"/>
@@ -3342,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="AB20" s="10"/>
-      <c r="AC20" s="16"/>
+      <c r="AC20" s="15"/>
       <c r="AE20" t="s">
         <v>41</v>
       </c>
@@ -3370,7 +3447,7 @@
       <c r="H21" s="11">
         <v>5</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="10">
         <v>4</v>
       </c>
       <c r="J21">
@@ -3386,7 +3463,7 @@
       <c r="N21">
         <v>2</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="10">
         <v>2</v>
       </c>
       <c r="P21" s="12">
@@ -3395,7 +3472,7 @@
       <c r="Q21">
         <v>30</v>
       </c>
-      <c r="R21" s="14">
+      <c r="R21" s="10">
         <v>42</v>
       </c>
       <c r="S21" s="11">
@@ -3404,14 +3481,14 @@
       <c r="T21">
         <v>5</v>
       </c>
-      <c r="U21" s="14">
+      <c r="U21" s="10">
         <v>7</v>
       </c>
       <c r="V21"/>
       <c r="X21" s="10"/>
       <c r="Z21" s="10"/>
       <c r="AB21" s="10"/>
-      <c r="AC21" s="15"/>
+      <c r="AC21" s="14"/>
       <c r="AE21" t="s">
         <v>41</v>
       </c>
@@ -3438,7 +3515,7 @@
       <c r="H22" s="12">
         <v>4</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="10">
         <v>4</v>
       </c>
       <c r="J22">
@@ -3453,7 +3530,7 @@
       <c r="N22">
         <v>2</v>
       </c>
-      <c r="O22" s="14">
+      <c r="O22" s="10">
         <v>4</v>
       </c>
       <c r="P22" s="12">
@@ -3462,11 +3539,11 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="R22" s="14">
+      <c r="R22" s="10">
         <v>1</v>
       </c>
       <c r="S22"/>
-      <c r="AC22" s="15"/>
+      <c r="AC22" s="14"/>
       <c r="AE22" t="s">
         <v>33</v>
       </c>
@@ -3493,7 +3570,7 @@
       <c r="H23" s="12">
         <v>1</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3508,7 +3585,7 @@
       <c r="N23">
         <v>5</v>
       </c>
-      <c r="O23" s="14">
+      <c r="O23" s="10">
         <v>7</v>
       </c>
       <c r="P23" s="12">
@@ -3517,14 +3594,14 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="R23" s="14">
+      <c r="R23" s="10">
         <v>1</v>
       </c>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
-      <c r="AC23" s="15"/>
+      <c r="AC23" s="14"/>
       <c r="AE23" t="s">
         <v>33</v>
       </c>
@@ -3552,7 +3629,7 @@
       <c r="H24" s="11">
         <v>4</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="10">
         <v>4</v>
       </c>
       <c r="J24">
@@ -3568,7 +3645,7 @@
       <c r="N24">
         <v>3</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O24" s="10">
         <v>4</v>
       </c>
       <c r="P24" s="12">
@@ -3577,7 +3654,7 @@
       <c r="Q24">
         <v>8</v>
       </c>
-      <c r="R24" s="14">
+      <c r="R24" s="10">
         <v>11</v>
       </c>
       <c r="S24"/>
@@ -3590,7 +3667,7 @@
         <v>3</v>
       </c>
       <c r="AB24" s="10"/>
-      <c r="AC24" s="15"/>
+      <c r="AC24" s="14"/>
       <c r="AE24" t="s">
         <v>41</v>
       </c>
@@ -3617,7 +3694,7 @@
       <c r="H25" s="12">
         <v>3</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="10">
         <v>2</v>
       </c>
       <c r="J25">
@@ -3632,14 +3709,14 @@
       <c r="N25">
         <v>3</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O25" s="10">
         <v>5</v>
       </c>
       <c r="P25"/>
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25"/>
-      <c r="AC25" s="15"/>
+      <c r="AC25" s="14"/>
       <c r="AE25" t="s">
         <v>52</v>
       </c>
@@ -3666,7 +3743,7 @@
       <c r="H26" s="12">
         <v>3</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="10">
         <v>2</v>
       </c>
       <c r="J26">
@@ -3681,7 +3758,7 @@
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26" s="10">
         <v>4</v>
       </c>
       <c r="P26" s="12">
@@ -3690,11 +3767,11 @@
       <c r="Q26">
         <v>4</v>
       </c>
-      <c r="R26" s="14">
+      <c r="R26" s="10">
         <v>6</v>
       </c>
       <c r="S26"/>
-      <c r="AC26" s="15"/>
+      <c r="AC26" s="14"/>
       <c r="AE26" t="s">
         <v>52</v>
       </c>
@@ -3722,7 +3799,7 @@
       <c r="H27" s="11">
         <v>8</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="10">
         <v>6</v>
       </c>
       <c r="J27">
@@ -3740,7 +3817,7 @@
       <c r="N27">
         <v>12</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O27" s="10">
         <v>18</v>
       </c>
       <c r="P27" s="12">
@@ -3749,7 +3826,7 @@
       <c r="Q27">
         <v>24</v>
       </c>
-      <c r="R27" s="14">
+      <c r="R27" s="10">
         <v>30</v>
       </c>
       <c r="S27" s="11">
@@ -3758,14 +3835,14 @@
       <c r="T27">
         <v>36</v>
       </c>
-      <c r="U27" s="14">
+      <c r="U27" s="10">
         <v>44</v>
       </c>
       <c r="V27"/>
       <c r="X27" s="10"/>
       <c r="Z27" s="10"/>
       <c r="AB27" s="10"/>
-      <c r="AC27" s="16"/>
+      <c r="AC27" s="15"/>
       <c r="AE27" t="s">
         <v>41</v>
       </c>
@@ -3793,7 +3870,7 @@
       <c r="H28" s="11">
         <v>1</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="10">
         <v>0</v>
       </c>
       <c r="J28">
@@ -3809,7 +3886,7 @@
       <c r="N28">
         <v>6</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O28" s="10">
         <v>8</v>
       </c>
       <c r="P28"/>
@@ -3825,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="AB28" s="10"/>
-      <c r="AC28" s="15"/>
+      <c r="AC28" s="14"/>
       <c r="AE28" t="s">
         <v>41</v>
       </c>
@@ -3852,7 +3929,7 @@
       <c r="H29" s="12">
         <v>5</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="10">
         <v>5</v>
       </c>
       <c r="J29">
@@ -3867,7 +3944,7 @@
       <c r="N29">
         <v>30</v>
       </c>
-      <c r="O29" s="14">
+      <c r="O29" s="10">
         <v>30</v>
       </c>
       <c r="P29" s="12">
@@ -3876,7 +3953,7 @@
       <c r="Q29">
         <v>3</v>
       </c>
-      <c r="R29" s="14">
+      <c r="R29" s="10">
         <v>5</v>
       </c>
       <c r="S29" s="12">
@@ -3885,11 +3962,11 @@
       <c r="T29">
         <v>2</v>
       </c>
-      <c r="U29" s="14">
+      <c r="U29" s="10">
         <v>3</v>
       </c>
       <c r="V29"/>
-      <c r="AC29" s="15"/>
+      <c r="AC29" s="14"/>
       <c r="AE29" t="s">
         <v>35</v>
       </c>
@@ -3916,7 +3993,7 @@
       <c r="H30" s="12">
         <v>4</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="10">
         <v>4</v>
       </c>
       <c r="J30">
@@ -3931,7 +4008,7 @@
       <c r="N30">
         <v>50</v>
       </c>
-      <c r="O30" s="14">
+      <c r="O30" s="10">
         <v>70</v>
       </c>
       <c r="P30" s="12">
@@ -3940,11 +4017,11 @@
       <c r="Q30">
         <v>2</v>
       </c>
-      <c r="R30" s="14">
+      <c r="R30" s="10">
         <v>4</v>
       </c>
       <c r="S30"/>
-      <c r="AC30" s="16"/>
+      <c r="AC30" s="15"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
@@ -3971,7 +4048,7 @@
       <c r="H31" s="12">
         <v>4</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="10">
         <v>3</v>
       </c>
       <c r="J31">
@@ -3986,7 +4063,7 @@
       <c r="N31">
         <v>20</v>
       </c>
-      <c r="O31" s="14">
+      <c r="O31" s="10">
         <v>30</v>
       </c>
       <c r="P31" s="12">
@@ -3995,14 +4072,14 @@
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="R31" s="14">
+      <c r="R31" s="10">
         <v>1</v>
       </c>
       <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31"/>
-      <c r="AC31" s="16"/>
+      <c r="AC31" s="15"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
@@ -4029,7 +4106,7 @@
       <c r="H32" s="12">
         <v>7</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="10">
         <v>6</v>
       </c>
       <c r="J32">
@@ -4065,7 +4142,7 @@
       <c r="H33" s="11">
         <v>8</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="10">
         <v>7</v>
       </c>
       <c r="J33">
@@ -4081,7 +4158,7 @@
       <c r="N33">
         <v>38</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O33" s="10">
         <v>52</v>
       </c>
       <c r="P33"/>
@@ -4124,7 +4201,7 @@
       <c r="H34" s="11">
         <v>3</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="10">
         <v>3</v>
       </c>
       <c r="J34">
@@ -4142,7 +4219,7 @@
       <c r="N34">
         <v>3</v>
       </c>
-      <c r="O34" s="14">
+      <c r="O34" s="10">
         <v>4</v>
       </c>
       <c r="P34"/>
@@ -4180,7 +4257,7 @@
       <c r="H35" s="11">
         <v>3</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="10">
         <v>3</v>
       </c>
       <c r="J35">
@@ -4196,7 +4273,7 @@
       <c r="N35">
         <v>18</v>
       </c>
-      <c r="O35" s="14">
+      <c r="O35" s="10">
         <v>22</v>
       </c>
       <c r="P35"/>
@@ -4232,7 +4309,7 @@
       <c r="H36" s="11">
         <v>3</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="10">
         <v>3</v>
       </c>
       <c r="J36">
@@ -4248,7 +4325,7 @@
       <c r="N36">
         <v>3</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="10">
         <v>4</v>
       </c>
       <c r="P36" s="12">
@@ -4257,7 +4334,7 @@
       <c r="Q36">
         <v>6</v>
       </c>
-      <c r="R36" s="14">
+      <c r="R36" s="10">
         <v>8</v>
       </c>
       <c r="S36"/>
@@ -4291,7 +4368,7 @@
       <c r="H37" s="12">
         <v>3</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="10">
         <v>3</v>
       </c>
       <c r="J37">
@@ -4306,7 +4383,7 @@
       <c r="N37">
         <v>3</v>
       </c>
-      <c r="O37" s="14">
+      <c r="O37" s="10">
         <v>4</v>
       </c>
       <c r="P37" s="12">
@@ -4315,7 +4392,7 @@
       <c r="Q37">
         <v>6</v>
       </c>
-      <c r="R37" s="14">
+      <c r="R37" s="10">
         <v>8</v>
       </c>
       <c r="S37"/>
@@ -4345,7 +4422,7 @@
       <c r="H38" s="12">
         <v>1</v>
       </c>
-      <c r="I38" s="14">
+      <c r="I38" s="10">
         <v>1</v>
       </c>
       <c r="J38">
@@ -4360,7 +4437,7 @@
       <c r="N38">
         <v>4</v>
       </c>
-      <c r="O38" s="14">
+      <c r="O38" s="10">
         <v>5</v>
       </c>
       <c r="P38" s="12">
@@ -4369,7 +4446,7 @@
       <c r="Q38">
         <v>3</v>
       </c>
-      <c r="R38" s="14">
+      <c r="R38" s="10">
         <v>5</v>
       </c>
       <c r="S38"/>
@@ -4399,7 +4476,7 @@
       <c r="H39" s="12">
         <v>1</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="10">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4414,7 +4491,7 @@
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39" s="14">
+      <c r="O39" s="10">
         <v>2</v>
       </c>
       <c r="P39" s="12">
@@ -4423,7 +4500,7 @@
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="14">
+      <c r="R39" s="10">
         <v>7</v>
       </c>
       <c r="S39"/>
@@ -4453,7 +4530,7 @@
       <c r="H40" s="12">
         <v>4</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="10">
         <v>3</v>
       </c>
       <c r="J40">
@@ -4468,7 +4545,7 @@
       <c r="N40">
         <v>4</v>
       </c>
-      <c r="O40" s="14">
+      <c r="O40" s="10">
         <v>5</v>
       </c>
       <c r="P40" s="12">
@@ -4477,7 +4554,7 @@
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="14">
+      <c r="R40" s="10">
         <v>5</v>
       </c>
       <c r="S40"/>
@@ -4507,7 +4584,7 @@
       <c r="H41" s="12">
         <v>2</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="10">
         <v>2</v>
       </c>
       <c r="J41">
@@ -4522,7 +4599,7 @@
       <c r="N41">
         <v>3</v>
       </c>
-      <c r="O41" s="14">
+      <c r="O41" s="10">
         <v>3</v>
       </c>
       <c r="P41" s="12">
@@ -4531,7 +4608,7 @@
       <c r="Q41">
         <v>2</v>
       </c>
-      <c r="R41" s="14">
+      <c r="R41" s="10">
         <v>3</v>
       </c>
       <c r="S41"/>
@@ -4561,7 +4638,7 @@
       <c r="H42" s="12">
         <v>4</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="10">
         <v>3</v>
       </c>
       <c r="J42">
@@ -4576,7 +4653,7 @@
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42" s="14">
+      <c r="O42" s="10">
         <v>3</v>
       </c>
       <c r="P42" s="12">
@@ -4585,7 +4662,7 @@
       <c r="Q42">
         <v>1</v>
       </c>
-      <c r="R42" s="14">
+      <c r="R42" s="10">
         <v>1</v>
       </c>
       <c r="S42"/>
@@ -4615,7 +4692,7 @@
       <c r="H43" s="12">
         <v>7</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="10">
         <v>4</v>
       </c>
       <c r="J43">
@@ -4630,7 +4707,7 @@
       <c r="N43">
         <v>5</v>
       </c>
-      <c r="O43" s="14">
+      <c r="O43" s="10">
         <v>5</v>
       </c>
       <c r="P43" s="12">
@@ -4639,7 +4716,7 @@
       <c r="Q43">
         <v>1</v>
       </c>
-      <c r="R43" s="14">
+      <c r="R43" s="10">
         <v>1</v>
       </c>
       <c r="S43" s="12">
@@ -4648,7 +4725,7 @@
       <c r="T43">
         <v>0.9</v>
       </c>
-      <c r="U43" s="14">
+      <c r="U43" s="10">
         <v>1.2</v>
       </c>
       <c r="V43"/>
@@ -4679,7 +4756,7 @@
       <c r="H44" s="11">
         <v>6</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="10">
         <v>4</v>
       </c>
       <c r="J44">
@@ -4695,7 +4772,7 @@
       <c r="N44">
         <v>2</v>
       </c>
-      <c r="O44" s="14">
+      <c r="O44" s="10">
         <v>2</v>
       </c>
       <c r="P44" s="12">
@@ -4704,7 +4781,7 @@
       <c r="Q44">
         <v>8</v>
       </c>
-      <c r="R44" s="14">
+      <c r="R44" s="10">
         <v>12</v>
       </c>
       <c r="S44"/>
@@ -4738,7 +4815,7 @@
       <c r="H45" s="12">
         <v>5</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="10">
         <v>4</v>
       </c>
       <c r="J45">
@@ -4753,7 +4830,7 @@
       <c r="N45">
         <v>7</v>
       </c>
-      <c r="O45" s="14">
+      <c r="O45" s="10">
         <v>9</v>
       </c>
       <c r="P45" s="12">
@@ -4762,7 +4839,7 @@
       <c r="Q45">
         <v>2</v>
       </c>
-      <c r="R45" s="14">
+      <c r="R45" s="10">
         <v>2</v>
       </c>
       <c r="S45" s="12">
@@ -4771,7 +4848,7 @@
       <c r="T45">
         <v>7</v>
       </c>
-      <c r="U45" s="14">
+      <c r="U45" s="10">
         <v>8</v>
       </c>
       <c r="V45"/>
@@ -4801,7 +4878,7 @@
       <c r="H46" s="12">
         <v>10</v>
       </c>
-      <c r="I46" s="14">
+      <c r="I46" s="10">
         <v>6</v>
       </c>
       <c r="J46">
@@ -4816,7 +4893,7 @@
       <c r="N46">
         <v>40</v>
       </c>
-      <c r="O46" s="14">
+      <c r="O46" s="10">
         <v>40</v>
       </c>
       <c r="P46" s="12">
@@ -4825,7 +4902,7 @@
       <c r="Q46">
         <v>30</v>
       </c>
-      <c r="R46" s="14">
+      <c r="R46" s="10">
         <v>30</v>
       </c>
       <c r="S46" s="12">
@@ -4834,7 +4911,7 @@
       <c r="T46">
         <v>1</v>
       </c>
-      <c r="U46" s="14">
+      <c r="U46" s="10">
         <v>1</v>
       </c>
       <c r="V46"/>
@@ -4864,7 +4941,7 @@
       <c r="H47" s="12">
         <v>2</v>
       </c>
-      <c r="I47" s="14">
+      <c r="I47" s="10">
         <v>1</v>
       </c>
       <c r="J47">
@@ -4879,7 +4956,7 @@
       <c r="N47">
         <v>10</v>
       </c>
-      <c r="O47" s="14">
+      <c r="O47" s="10">
         <v>14</v>
       </c>
       <c r="P47"/>
@@ -4910,7 +4987,7 @@
       <c r="H48" s="12">
         <v>4</v>
       </c>
-      <c r="I48" s="14">
+      <c r="I48" s="10">
         <v>3</v>
       </c>
       <c r="J48">
@@ -4925,7 +5002,7 @@
       <c r="N48">
         <v>8</v>
       </c>
-      <c r="O48" s="14">
+      <c r="O48" s="10">
         <v>11</v>
       </c>
       <c r="P48" s="12">
@@ -4934,7 +5011,7 @@
       <c r="Q48">
         <v>3</v>
       </c>
-      <c r="R48" s="14">
+      <c r="R48" s="10">
         <v>3</v>
       </c>
       <c r="S48"/>
@@ -4968,7 +5045,7 @@
       <c r="H49" s="11">
         <v>4</v>
       </c>
-      <c r="I49" s="14">
+      <c r="I49" s="10">
         <v>3</v>
       </c>
       <c r="J49">
@@ -4984,7 +5061,7 @@
       <c r="N49">
         <v>7</v>
       </c>
-      <c r="O49" s="14">
+      <c r="O49" s="10">
         <v>11</v>
       </c>
       <c r="P49" s="12">
@@ -4993,7 +5070,7 @@
       <c r="Q49">
         <v>2</v>
       </c>
-      <c r="R49" s="14">
+      <c r="R49" s="10">
         <v>3</v>
       </c>
       <c r="S49"/>
@@ -5029,7 +5106,7 @@
       <c r="H50" s="12">
         <v>5</v>
       </c>
-      <c r="I50" s="14">
+      <c r="I50" s="10">
         <v>4</v>
       </c>
       <c r="J50">
@@ -5044,7 +5121,7 @@
       <c r="N50">
         <v>5</v>
       </c>
-      <c r="O50" s="14">
+      <c r="O50" s="10">
         <v>7</v>
       </c>
       <c r="P50" s="12">
@@ -5053,7 +5130,7 @@
       <c r="Q50">
         <v>1.1</v>
       </c>
-      <c r="R50" s="14">
+      <c r="R50" s="10">
         <v>1.7</v>
       </c>
       <c r="S50"/>
@@ -5083,7 +5160,7 @@
       <c r="H51" s="12">
         <v>9</v>
       </c>
-      <c r="I51" s="14">
+      <c r="I51" s="10">
         <v>6</v>
       </c>
       <c r="J51">
@@ -5098,7 +5175,7 @@
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51" s="14">
+      <c r="O51" s="10">
         <v>3</v>
       </c>
       <c r="P51" s="12">
@@ -5107,7 +5184,7 @@
       <c r="Q51">
         <v>1</v>
       </c>
-      <c r="R51" s="14">
+      <c r="R51" s="10">
         <v>1</v>
       </c>
       <c r="S51"/>
@@ -5137,7 +5214,7 @@
       <c r="H52" s="12">
         <v>1</v>
       </c>
-      <c r="I52" s="14">
+      <c r="I52" s="10">
         <v>0</v>
       </c>
       <c r="J52">
@@ -5152,7 +5229,7 @@
       <c r="N52">
         <v>2</v>
       </c>
-      <c r="O52" s="14">
+      <c r="O52" s="10">
         <v>2</v>
       </c>
       <c r="P52" s="12">
@@ -5161,7 +5238,7 @@
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="14">
+      <c r="R52" s="10">
         <v>2</v>
       </c>
       <c r="S52"/>
@@ -5192,7 +5269,7 @@
       <c r="H53" s="11">
         <v>5</v>
       </c>
-      <c r="I53" s="14">
+      <c r="I53" s="10">
         <v>5</v>
       </c>
       <c r="J53">
@@ -5210,7 +5287,7 @@
       <c r="N53">
         <v>3</v>
       </c>
-      <c r="O53" s="14">
+      <c r="O53" s="10">
         <v>4</v>
       </c>
       <c r="P53" s="11">
@@ -5219,7 +5296,7 @@
       <c r="Q53">
         <v>-0.5</v>
       </c>
-      <c r="R53" s="14">
+      <c r="R53" s="10">
         <v>-0.5</v>
       </c>
       <c r="S53"/>
@@ -5256,7 +5333,7 @@
       <c r="H54" s="11">
         <v>2</v>
       </c>
-      <c r="I54" s="14">
+      <c r="I54" s="10">
         <v>1</v>
       </c>
       <c r="J54">
@@ -5272,7 +5349,7 @@
       <c r="N54">
         <v>3</v>
       </c>
-      <c r="O54" s="14">
+      <c r="O54" s="10">
         <v>4</v>
       </c>
       <c r="P54" s="11">
@@ -5281,7 +5358,7 @@
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="14">
+      <c r="R54" s="10">
         <v>1</v>
       </c>
       <c r="S54" s="11">
@@ -5290,7 +5367,7 @@
       <c r="T54">
         <v>3</v>
       </c>
-      <c r="U54" s="14">
+      <c r="U54" s="10">
         <v>5</v>
       </c>
       <c r="V54"/>
@@ -5324,7 +5401,7 @@
       <c r="H55" s="11">
         <v>4</v>
       </c>
-      <c r="I55" s="14">
+      <c r="I55" s="10">
         <v>3</v>
       </c>
       <c r="J55">
@@ -5349,14 +5426,14 @@
       <c r="Q55">
         <v>1</v>
       </c>
-      <c r="R55" s="14">
+      <c r="R55" s="10">
         <v>1</v>
       </c>
       <c r="S55"/>
       <c r="U55" s="10"/>
       <c r="X55" s="10"/>
       <c r="Z55" s="10"/>
-      <c r="AA55" s="14"/>
+      <c r="AA55" s="10"/>
       <c r="AB55" s="10"/>
       <c r="AE55" t="s">
         <v>41</v>
@@ -5387,7 +5464,7 @@
       <c r="H56" s="11">
         <v>2</v>
       </c>
-      <c r="I56" s="14">
+      <c r="I56" s="10">
         <v>1</v>
       </c>
       <c r="J56">
@@ -5412,7 +5489,7 @@
       <c r="Q56">
         <v>12</v>
       </c>
-      <c r="R56" s="14">
+      <c r="R56" s="10">
         <v>18</v>
       </c>
       <c r="S56" s="11">
@@ -5421,12 +5498,12 @@
       <c r="T56">
         <v>1</v>
       </c>
-      <c r="U56" s="14">
+      <c r="U56" s="10">
         <v>1</v>
       </c>
       <c r="X56" s="10"/>
       <c r="Z56" s="10"/>
-      <c r="AA56" s="14"/>
+      <c r="AA56" s="10"/>
       <c r="AB56" s="10"/>
       <c r="AE56" t="s">
         <v>41</v>
@@ -5457,7 +5534,7 @@
       <c r="H57" s="11">
         <v>2</v>
       </c>
-      <c r="I57" s="14">
+      <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57">
@@ -5473,7 +5550,7 @@
       <c r="N57">
         <v>5</v>
       </c>
-      <c r="O57" s="14">
+      <c r="O57" s="10">
         <v>6</v>
       </c>
       <c r="P57" s="11">
@@ -5482,7 +5559,7 @@
       <c r="Q57">
         <v>5</v>
       </c>
-      <c r="R57" s="14">
+      <c r="R57" s="10">
         <v>6</v>
       </c>
       <c r="U57" s="10"/>
@@ -5512,7 +5589,6 @@
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="G58" s="10"/>
       <c r="H58">
         <v>3</v>
       </c>
@@ -5525,7 +5601,6 @@
       <c r="K58">
         <v>0</v>
       </c>
-      <c r="L58" s="10"/>
       <c r="AE58" t="s">
         <v>41</v>
       </c>
@@ -5549,7 +5624,6 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="G59" s="10"/>
       <c r="H59">
         <v>4</v>
       </c>
@@ -5562,7 +5636,6 @@
       <c r="K59">
         <v>0</v>
       </c>
-      <c r="L59" s="10"/>
       <c r="M59">
         <v>2</v>
       </c>
@@ -5595,7 +5668,6 @@
       <c r="F60" t="s">
         <v>34</v>
       </c>
-      <c r="G60" s="10"/>
       <c r="H60">
         <v>2</v>
       </c>
@@ -5608,7 +5680,6 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="L60" s="10"/>
       <c r="AE60" t="s">
         <v>41</v>
       </c>
@@ -5663,11 +5734,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="30">
-      <filters blank="1">
-        <filter val="C"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val=""/>
+        <customFilter operator="equal" val="C"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
@@ -7967,14 +8039,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
     <col min="2" max="2" width="31.425" customWidth="1"/>
     <col min="3" max="3" width="29.425" customWidth="1"/>
     <col min="4" max="4" width="28.425" customWidth="1"/>
     <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="17.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5833333333333" customWidth="1"/>
     <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8006,16 +8079,16 @@
         <v>306</v>
       </c>
       <c r="C2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D2" t="s">
         <v>307</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>308</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8023,19 +8096,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
         <v>310</v>
-      </c>
-      <c r="C3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8043,19 +8116,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>312</v>
-      </c>
-      <c r="C4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8063,16 +8136,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" t="s">
         <v>314</v>
       </c>
-      <c r="C5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>315</v>
-      </c>
-      <c r="F5" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8080,16 +8153,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6" t="s">
         <v>317</v>
-      </c>
-      <c r="C6" t="s">
-        <v>318</v>
-      </c>
-      <c r="D6" t="s">
-        <v>315</v>
-      </c>
-      <c r="F6" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8097,16 +8170,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8114,13 +8187,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8128,13 +8201,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8142,16 +8215,186 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>327</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>327</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" t="s">
         <v>328</v>
       </c>
-      <c r="E10">
-        <v>0</v>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" t="s">
+        <v>335</v>
+      </c>
+      <c r="D15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" t="s">
+        <v>337</v>
+      </c>
+      <c r="D16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>339</v>
+      </c>
+      <c r="C17" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F20" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -8196,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D2" t="s">
         <v>297</v>
@@ -8247,7 +8490,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -8256,13 +8499,13 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="I1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="J1" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -8270,31 +8513,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="J2" t="s">
-        <v>306</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -8302,13 +8545,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -8317,16 +8560,16 @@
         <v>34</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -8334,31 +8577,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="D4" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="J4" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -8366,13 +8609,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8384,13 +8627,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J5" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8398,13 +8641,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="D6" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -8416,13 +8659,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J6" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8430,13 +8673,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="D7" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -8448,13 +8691,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="J7" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8462,10 +8705,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="D8" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8477,13 +8720,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="J8" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8491,10 +8734,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="D9" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8506,13 +8749,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="J9" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8520,10 +8763,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="D10" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8535,13 +8778,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="J10" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="9:9">
@@ -8589,7 +8832,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -8598,25 +8841,25 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="I1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="K1" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="L1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="M1" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="N1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -8624,13 +8867,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -8639,13 +8882,13 @@
         <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -8668,28 +8911,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C3" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -8712,28 +8955,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="J4">
         <v>10</v>
